--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,6724 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129293569</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91533</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>492107</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6764235</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>35. 2 bilder, på granlåga</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129290345</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57722</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>492050</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6764358</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>20. 1 bild</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129271386</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>492097</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6764207</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 50 meter</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129271992</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>492111</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6764274</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129282927</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>492097</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6764193</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129286796</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>492169</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6764315</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129270999</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57722</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>492105</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6764156</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129294088</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>491988</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6764293</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129287686</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>492200</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6764371</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129290261</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>492063</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6764369</v>
+      </c>
+      <c r="S12" t="n">
+        <v>50</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129291402</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91533</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>492107</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6764244</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>25. 4 bilder, granlåga</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129294029</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57885</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>492007</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6764289</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129293927</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>491997</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6764269</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129287945</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>492218</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6764381</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>13. 2 bilder, tallstammar Rikligt till måttligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129290011</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>492099</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6764428</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>18. 1 bild</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129296076</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>492085</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6764296</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129293376</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>492123</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6764202</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129294004</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>491966</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6764290</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>37. 4 bilder, en närbild Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129290547</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>492071</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6764318</v>
+      </c>
+      <c r="S21" t="n">
+        <v>50</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129293152</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>492125</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6764158</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129293473</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>492120</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6764224</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129294398</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57722</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>491957</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6764346</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129271179</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>492113</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6764152</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129290672</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58095</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>492030</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6764294</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129294219</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91818</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>658</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>491922</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6764336</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>39. 2 bild</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129294699</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>491988</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6764346</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129274016</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>492092</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6764410</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1 bild</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129273280</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>492172</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6764333</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 40 meter</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129294905</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>492048</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6764380</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129294335</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>491922</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6764336</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129290087</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>492083</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6764418</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129295250</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>492125</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6764458</v>
+      </c>
+      <c r="S34" t="n">
+        <v>50</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>54. 4 bilder på äldre tallar  Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129294510</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57722</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>491975</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6764342</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>45. 3 bilder, miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129283290</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79658</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>492076</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6764218</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>4. 1 bild, stubbe</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129289310</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>492177</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6764418</v>
+      </c>
+      <c r="S37" t="n">
+        <v>50</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129282976</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57722</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>492100</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6764182</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>2. 1 bild</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129294091</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>491988</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6764293</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129295876</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>492080</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6764357</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>55. 1 bild hängande på gren</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129289434</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91533</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>492159</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6764383</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>16. 2 bild</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129294432</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91533</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>491957</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6764346</v>
+      </c>
+      <c r="S42" t="n">
+        <v>50</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>44. 2 bilder, granlåga</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129293510</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>492107</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6764244</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129294065</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91533</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>491997</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6764302</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>38. 1 bild, granlåga</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129289685</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97540</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>492160</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6764361</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>17. 3 miljöbilder,</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129289411</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57722</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>492157</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6764400</v>
+      </c>
+      <c r="S46" t="n">
+        <v>50</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>15. 1 bild</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129295996</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57722</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>492085</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6764296</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>56. 2 bilder, även svamp på gran</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129293401</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57722</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>492123</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6764202</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>32. 1 bild på låga med hack</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129293744</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>492059</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6764244</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129293719</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>492059</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6764244</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>129290779</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>492030</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6764279</v>
+      </c>
+      <c r="S51" t="n">
+        <v>50</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>129293571</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>492107</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6764235</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>129274000</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>492089</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6764397</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1 bild samt miljöbilder för området</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>129283635</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>492082</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6764245</v>
+      </c>
+      <c r="S54" t="n">
+        <v>50</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>129287728</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>492227</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6764369</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>12. 1 Bild på kolarkoja</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>129283043</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57722</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>492082</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6764210</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>3. 1 bild</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>129294362</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>491956</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6764334</v>
+      </c>
+      <c r="S57" t="n">
+        <v>50</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>129290171</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79658</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>492061</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6764382</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>129296258</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>492091</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6764217</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>129274938</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>492048</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6764380</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>I bild</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>129287751</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>492227</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6764369</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>12. 1 bild</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>129293814</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79039</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>492030</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6764244</v>
+      </c>
+      <c r="S62" t="n">
+        <v>50</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129293569</v>
+        <v>129271386</v>
       </c>
       <c r="B3" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492107</v>
+        <v>492097</v>
       </c>
       <c r="R3" t="n">
-        <v>6764235</v>
+        <v>6764207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,27 +847,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>35. 2 bilder, på granlåga</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129290345</v>
+        <v>129293569</v>
       </c>
       <c r="B4" t="n">
-        <v>57722</v>
+        <v>91540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492050</v>
+        <v>492107</v>
       </c>
       <c r="R4" t="n">
-        <v>6764358</v>
+        <v>6764235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>35. 2 bilder, på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129271386</v>
+        <v>129290345</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,34 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492097</v>
+        <v>492050</v>
       </c>
       <c r="R5" t="n">
-        <v>6764207</v>
+        <v>6764358</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129282927</v>
+        <v>129270999</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,37 +1241,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492097</v>
+        <v>492105</v>
       </c>
       <c r="R7" t="n">
-        <v>6764193</v>
+        <v>6764156</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1295,27 +1300,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129286796</v>
+        <v>129294088</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,13 +1382,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492169</v>
+        <v>491988</v>
       </c>
       <c r="R8" t="n">
-        <v>6764315</v>
+        <v>6764293</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,12 +1427,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129270999</v>
+        <v>129287686</v>
       </c>
       <c r="B9" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1465,42 +1465,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492105</v>
+        <v>492200</v>
       </c>
       <c r="R9" t="n">
-        <v>6764156</v>
+        <v>6764371</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1524,27 +1519,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Bild 1</t>
+          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,32 +1566,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129294088</v>
+        <v>129290261</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,13 +1601,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>491988</v>
+        <v>492063</v>
       </c>
       <c r="R10" t="n">
-        <v>6764293</v>
+        <v>6764369</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1646,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129287686</v>
+        <v>129291402</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,21 +1689,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492200</v>
+        <v>492107</v>
       </c>
       <c r="R11" t="n">
-        <v>6764371</v>
+        <v>6764244</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,7 +1790,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129290261</v>
+        <v>129293927</v>
       </c>
       <c r="B12" t="n">
         <v>79039</v>
@@ -1825,10 +1825,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492063</v>
+        <v>491997</v>
       </c>
       <c r="R12" t="n">
-        <v>6764369</v>
+        <v>6764269</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129291402</v>
+        <v>129294029</v>
       </c>
       <c r="B13" t="n">
-        <v>91533</v>
+        <v>57885</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,37 +1913,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492107</v>
+        <v>492007</v>
       </c>
       <c r="R13" t="n">
-        <v>6764244</v>
+        <v>6764289</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,12 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129294029</v>
+        <v>129287945</v>
       </c>
       <c r="B14" t="n">
-        <v>57885</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2025,39 +2025,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492007</v>
+        <v>492218</v>
       </c>
       <c r="R14" t="n">
-        <v>6764289</v>
+        <v>6764381</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2089,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2099,7 +2094,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>13. 2 bilder, tallstammar Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,7 +2126,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129293927</v>
+        <v>129296076</v>
       </c>
       <c r="B15" t="n">
         <v>79039</v>
@@ -2161,13 +2161,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491997</v>
+        <v>492085</v>
       </c>
       <c r="R15" t="n">
-        <v>6764269</v>
+        <v>6764296</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2207,11 +2207,6 @@
       <c r="AB15" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,7 +2233,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129287945</v>
+        <v>129293376</v>
       </c>
       <c r="B16" t="n">
         <v>79039</v>
@@ -2273,13 +2268,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492218</v>
+        <v>492123</v>
       </c>
       <c r="R16" t="n">
-        <v>6764381</v>
+        <v>6764202</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2308,7 +2303,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2318,12 +2313,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>13. 2 bilder, tallstammar Rikligt till måttligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2350,10 +2340,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129290011</v>
+        <v>129294004</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2361,42 +2351,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492099</v>
+        <v>491966</v>
       </c>
       <c r="R17" t="n">
-        <v>6764428</v>
+        <v>6764290</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2425,7 +2410,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2435,12 +2420,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>18. 1 bild</t>
+          <t>37. 4 bilder, en närbild Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129296076</v>
+        <v>129294398</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2478,37 +2463,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492085</v>
+        <v>491957</v>
       </c>
       <c r="R18" t="n">
-        <v>6764296</v>
+        <v>6764346</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2574,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129293376</v>
+        <v>129271179</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2585,34 +2575,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492123</v>
+        <v>492113</v>
       </c>
       <c r="R19" t="n">
-        <v>6764202</v>
+        <v>6764152</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2639,22 +2634,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2681,7 +2681,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129294004</v>
+        <v>129293473</v>
       </c>
       <c r="B20" t="n">
         <v>79039</v>
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491966</v>
+        <v>492120</v>
       </c>
       <c r="R20" t="n">
-        <v>6764290</v>
+        <v>6764224</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2762,11 +2762,6 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>37. 4 bilder, en närbild Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2793,7 +2788,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129290547</v>
+        <v>129293152</v>
       </c>
       <c r="B21" t="n">
         <v>79039</v>
@@ -2828,13 +2823,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492071</v>
+        <v>492125</v>
       </c>
       <c r="R21" t="n">
-        <v>6764318</v>
+        <v>6764158</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2863,7 +2858,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2873,12 +2868,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2905,7 +2895,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129293152</v>
+        <v>129290547</v>
       </c>
       <c r="B22" t="n">
         <v>79039</v>
@@ -2940,13 +2930,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492125</v>
+        <v>492071</v>
       </c>
       <c r="R22" t="n">
-        <v>6764158</v>
+        <v>6764318</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2975,7 +2965,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2985,7 +2975,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3012,7 +3007,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129293473</v>
+        <v>129273280</v>
       </c>
       <c r="B23" t="n">
         <v>79039</v>
@@ -3047,10 +3042,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492120</v>
+        <v>492172</v>
       </c>
       <c r="R23" t="n">
-        <v>6764224</v>
+        <v>6764333</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3077,22 +3072,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129294398</v>
+        <v>129294219</v>
       </c>
       <c r="B24" t="n">
-        <v>57722</v>
+        <v>91825</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,42 +3130,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491957</v>
+        <v>491922</v>
       </c>
       <c r="R24" t="n">
-        <v>6764346</v>
+        <v>6764336</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3205,6 +3200,11 @@
       <c r="AB24" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129271179</v>
+        <v>129294699</v>
       </c>
       <c r="B25" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,42 +3242,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492113</v>
+        <v>491988</v>
       </c>
       <c r="R25" t="n">
-        <v>6764152</v>
+        <v>6764346</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3301,27 +3296,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,27 +3343,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129290672</v>
+        <v>129274016</v>
       </c>
       <c r="B26" t="n">
-        <v>58095</v>
+        <v>57725</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3379,7 +3374,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3388,13 +3383,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492030</v>
+        <v>492092</v>
       </c>
       <c r="R26" t="n">
-        <v>6764294</v>
+        <v>6764410</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3418,22 +3413,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,48 +3460,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129294219</v>
+        <v>129290672</v>
       </c>
       <c r="B27" t="n">
-        <v>91818</v>
+        <v>58095</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491922</v>
+        <v>492030</v>
       </c>
       <c r="R27" t="n">
-        <v>6764336</v>
+        <v>6764294</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3530,7 +3535,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3540,12 +3545,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>39. 2 bild</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,7 +3572,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129294699</v>
+        <v>129294335</v>
       </c>
       <c r="B28" t="n">
         <v>79039</v>
@@ -3607,13 +3607,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491988</v>
+        <v>491922</v>
       </c>
       <c r="R28" t="n">
-        <v>6764346</v>
+        <v>6764336</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3653,11 +3653,6 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3684,10 +3679,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129274016</v>
+        <v>129294905</v>
       </c>
       <c r="B29" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3695,39 +3690,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492092</v>
+        <v>492048</v>
       </c>
       <c r="R29" t="n">
-        <v>6764410</v>
+        <v>6764380</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3754,27 +3744,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3801,7 +3791,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129273280</v>
+        <v>129290087</v>
       </c>
       <c r="B30" t="n">
         <v>79039</v>
@@ -3836,10 +3826,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492172</v>
+        <v>492083</v>
       </c>
       <c r="R30" t="n">
-        <v>6764333</v>
+        <v>6764418</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3866,27 +3856,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3913,7 +3898,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129294905</v>
+        <v>129295250</v>
       </c>
       <c r="B31" t="n">
         <v>79039</v>
@@ -3948,13 +3933,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492048</v>
+        <v>492125</v>
       </c>
       <c r="R31" t="n">
-        <v>6764380</v>
+        <v>6764458</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3998,7 +3983,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
+          <t>54. 4 bilder på äldre tallar  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4025,7 +4010,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129294335</v>
+        <v>129289310</v>
       </c>
       <c r="B32" t="n">
         <v>79039</v>
@@ -4060,13 +4045,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491922</v>
+        <v>492177</v>
       </c>
       <c r="R32" t="n">
-        <v>6764336</v>
+        <v>6764418</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4095,7 +4080,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4105,7 +4090,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4132,10 +4122,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129290087</v>
+        <v>129294510</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4143,34 +4133,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492083</v>
+        <v>491975</v>
       </c>
       <c r="R33" t="n">
-        <v>6764418</v>
+        <v>6764342</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4202,7 +4197,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4212,7 +4207,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>45. 3 bilder, miljöbilder</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129295250</v>
+        <v>129289434</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,13 +4274,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492125</v>
+        <v>492159</v>
       </c>
       <c r="R34" t="n">
-        <v>6764458</v>
+        <v>6764383</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>54. 4 bilder på äldre tallar  Rikligt i en radie av 50 meter</t>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,10 +4351,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129294510</v>
+        <v>129294091</v>
       </c>
       <c r="B35" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4362,39 +4362,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491975</v>
+        <v>491988</v>
       </c>
       <c r="R35" t="n">
-        <v>6764342</v>
+        <v>6764293</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4437,11 +4432,6 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>45. 3 bilder, miljöbilder</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4468,10 +4458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129283290</v>
+        <v>129295876</v>
       </c>
       <c r="B36" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4479,21 +4469,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4503,10 +4493,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492076</v>
+        <v>492080</v>
       </c>
       <c r="R36" t="n">
-        <v>6764218</v>
+        <v>6764357</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4538,7 +4528,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4548,12 +4538,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>4. 1 bild, stubbe</t>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4580,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129289310</v>
+        <v>129294065</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4591,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4615,13 +4605,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492177</v>
+        <v>491997</v>
       </c>
       <c r="R37" t="n">
-        <v>6764418</v>
+        <v>6764302</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4650,7 +4640,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4660,12 +4650,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4692,10 +4682,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129282976</v>
+        <v>129294432</v>
       </c>
       <c r="B38" t="n">
-        <v>57722</v>
+        <v>91540</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4703,42 +4693,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>492100</v>
+        <v>491957</v>
       </c>
       <c r="R38" t="n">
-        <v>6764182</v>
+        <v>6764346</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4767,7 +4752,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4777,12 +4762,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>2. 1 bild</t>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4809,7 +4794,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129294091</v>
+        <v>129293510</v>
       </c>
       <c r="B39" t="n">
         <v>79039</v>
@@ -4844,10 +4829,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491988</v>
+        <v>492107</v>
       </c>
       <c r="R39" t="n">
-        <v>6764293</v>
+        <v>6764244</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4916,7 +4901,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129295876</v>
+        <v>129290779</v>
       </c>
       <c r="B40" t="n">
         <v>79039</v>
@@ -4951,13 +4936,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492080</v>
+        <v>492030</v>
       </c>
       <c r="R40" t="n">
-        <v>6764357</v>
+        <v>6764279</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4986,7 +4971,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4996,12 +4981,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>55. 1 bild hängande på gren</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5028,10 +5013,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129289434</v>
+        <v>129293401</v>
       </c>
       <c r="B41" t="n">
-        <v>91533</v>
+        <v>57722</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5039,34 +5024,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492159</v>
+        <v>492123</v>
       </c>
       <c r="R41" t="n">
-        <v>6764383</v>
+        <v>6764202</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5098,7 +5088,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5108,12 +5098,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>16. 2 bild</t>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5140,10 +5130,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129294432</v>
+        <v>129295996</v>
       </c>
       <c r="B42" t="n">
-        <v>91533</v>
+        <v>57722</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5151,37 +5141,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>491957</v>
+        <v>492085</v>
       </c>
       <c r="R42" t="n">
-        <v>6764346</v>
+        <v>6764296</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5225,7 +5220,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>44. 2 bilder, granlåga</t>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5252,10 +5247,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129293510</v>
+        <v>129289411</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5263,37 +5258,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492107</v>
+        <v>492157</v>
       </c>
       <c r="R43" t="n">
-        <v>6764244</v>
+        <v>6764400</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5332,7 +5332,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5359,10 +5364,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129294065</v>
+        <v>129293719</v>
       </c>
       <c r="B44" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5370,21 +5375,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5394,10 +5399,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>491997</v>
+        <v>492059</v>
       </c>
       <c r="R44" t="n">
-        <v>6764302</v>
+        <v>6764244</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5440,11 +5445,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5471,10 +5471,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129289685</v>
+        <v>129293744</v>
       </c>
       <c r="B45" t="n">
-        <v>97540</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5482,21 +5482,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5506,10 +5506,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492160</v>
+        <v>492059</v>
       </c>
       <c r="R45" t="n">
-        <v>6764361</v>
+        <v>6764244</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5551,12 +5551,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5583,53 +5578,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289411</v>
+        <v>129289685</v>
       </c>
       <c r="B46" t="n">
-        <v>57722</v>
+        <v>97547</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492157</v>
+        <v>492160</v>
       </c>
       <c r="R46" t="n">
-        <v>6764400</v>
+        <v>6764361</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5673,7 +5663,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5700,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129295996</v>
+        <v>129293571</v>
       </c>
       <c r="B47" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5711,39 +5701,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492085</v>
+        <v>492107</v>
       </c>
       <c r="R47" t="n">
-        <v>6764296</v>
+        <v>6764235</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5786,11 +5771,6 @@
       <c r="AB47" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5817,10 +5797,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129293401</v>
+        <v>129274000</v>
       </c>
       <c r="B48" t="n">
-        <v>57722</v>
+        <v>57725</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5828,16 +5808,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5846,21 +5826,24 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492123</v>
+        <v>492089</v>
       </c>
       <c r="R48" t="n">
-        <v>6764202</v>
+        <v>6764397</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5887,27 +5870,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>1 bild samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5934,32 +5917,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129293744</v>
+        <v>129294362</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5969,13 +5952,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492059</v>
+        <v>491956</v>
       </c>
       <c r="R49" t="n">
-        <v>6764244</v>
+        <v>6764334</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6015,6 +5998,11 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6041,7 +6029,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129293719</v>
+        <v>129296258</v>
       </c>
       <c r="B50" t="n">
         <v>79039</v>
@@ -6076,10 +6064,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492059</v>
+        <v>492091</v>
       </c>
       <c r="R50" t="n">
-        <v>6764244</v>
+        <v>6764217</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6148,10 +6136,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129290779</v>
+        <v>129290171</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6159,21 +6147,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6183,13 +6171,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492030</v>
+        <v>492061</v>
       </c>
       <c r="R51" t="n">
-        <v>6764279</v>
+        <v>6764382</v>
       </c>
       <c r="S51" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6229,11 +6217,6 @@
       <c r="AB51" t="inlineStr">
         <is>
           <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6260,10 +6243,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129293571</v>
+        <v>129274938</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6271,34 +6254,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492107</v>
+        <v>492048</v>
       </c>
       <c r="R52" t="n">
-        <v>6764235</v>
+        <v>6764380</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6325,22 +6313,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>I bild</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6367,10 +6360,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129274000</v>
+        <v>129282981</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>57722</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6378,16 +6371,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6396,24 +6389,21 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492089</v>
+        <v>492100</v>
       </c>
       <c r="R53" t="n">
-        <v>6764397</v>
+        <v>6764182</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6440,27 +6430,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>1 bild samt miljöbilder för området</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6487,7 +6472,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129283635</v>
+        <v>129293814</v>
       </c>
       <c r="B54" t="n">
         <v>79039</v>
@@ -6522,10 +6507,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492082</v>
+        <v>492030</v>
       </c>
       <c r="R54" t="n">
-        <v>6764245</v>
+        <v>6764244</v>
       </c>
       <c r="S54" t="n">
         <v>50</v>
@@ -6557,7 +6542,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6567,12 +6552,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6599,7 +6584,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129287728</v>
+        <v>129286796</v>
       </c>
       <c r="B55" t="n">
         <v>79039</v>
@@ -6634,13 +6619,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492227</v>
+        <v>492169</v>
       </c>
       <c r="R55" t="n">
-        <v>6764369</v>
+        <v>6764315</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6684,7 +6669,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>12. 1 Bild på kolarkoja</t>
+          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6711,10 +6696,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129283043</v>
+        <v>129282927</v>
       </c>
       <c r="B56" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6722,42 +6707,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492082</v>
+        <v>492097</v>
       </c>
       <c r="R56" t="n">
-        <v>6764210</v>
+        <v>6764193</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6801,7 +6781,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>3. 1 bild</t>
+          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6828,10 +6808,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129294362</v>
+        <v>129290011</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6839,37 +6819,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>491956</v>
+        <v>492099</v>
       </c>
       <c r="R57" t="n">
-        <v>6764334</v>
+        <v>6764428</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6898,7 +6883,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6908,12 +6893,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
+          <t>18. 1 bild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6940,7 +6925,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129290171</v>
+        <v>129283290</v>
       </c>
       <c r="B58" t="n">
         <v>79658</v>
@@ -6975,10 +6960,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492061</v>
+        <v>492076</v>
       </c>
       <c r="R58" t="n">
-        <v>6764382</v>
+        <v>6764218</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7010,7 +6995,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7020,7 +7005,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>4. 1 bild, stubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7047,10 +7037,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129296258</v>
+        <v>129283043</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7058,34 +7048,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492091</v>
+        <v>492082</v>
       </c>
       <c r="R59" t="n">
-        <v>6764217</v>
+        <v>6764210</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7117,7 +7112,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7127,7 +7122,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>3. 1 bild</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7154,10 +7154,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129274938</v>
+        <v>129287728</v>
       </c>
       <c r="B60" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7165,39 +7165,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492048</v>
+        <v>492227</v>
       </c>
       <c r="R60" t="n">
-        <v>6764380</v>
+        <v>6764369</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7224,27 +7219,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>I bild</t>
+          <t>12. 1 Bild på kolarkoja</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7271,10 +7266,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129287751</v>
+        <v>129283635</v>
       </c>
       <c r="B61" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7282,42 +7277,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492227</v>
+        <v>492082</v>
       </c>
       <c r="R61" t="n">
-        <v>6764369</v>
+        <v>6764245</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7346,7 +7336,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7356,12 +7346,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>12. 1 bild</t>
+          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7388,10 +7378,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129293814</v>
+        <v>129287751</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7399,37 +7389,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492030</v>
+        <v>492227</v>
       </c>
       <c r="R62" t="n">
-        <v>6764244</v>
+        <v>6764369</v>
       </c>
       <c r="S62" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7458,7 +7453,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7468,12 +7463,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
+          <t>12. 1 bild</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129271130</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129271386</v>
+        <v>129293569</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>91542</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492097</v>
+        <v>492107</v>
       </c>
       <c r="R3" t="n">
-        <v>6764207</v>
+        <v>6764235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,27 +847,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>35. 2 bilder, på granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129293569</v>
+        <v>129271386</v>
       </c>
       <c r="B4" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492107</v>
+        <v>492097</v>
       </c>
       <c r="R4" t="n">
-        <v>6764235</v>
+        <v>6764207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,27 +959,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>35. 2 bilder, på granlåga</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
         <v>129290345</v>
       </c>
       <c r="B5" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129271992</v>
+        <v>129270999</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,34 +1134,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492111</v>
+        <v>492105</v>
       </c>
       <c r="R6" t="n">
-        <v>6764274</v>
+        <v>6764156</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,6 +1209,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129270999</v>
+        <v>129271992</v>
       </c>
       <c r="B7" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,39 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492105</v>
+        <v>492111</v>
       </c>
       <c r="R7" t="n">
-        <v>6764156</v>
+        <v>6764274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,11 +1321,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129287686</v>
+        <v>129290261</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492200</v>
+        <v>492063</v>
       </c>
       <c r="R9" t="n">
-        <v>6764371</v>
+        <v>6764369</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
+          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129290261</v>
+        <v>129287686</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492063</v>
+        <v>492200</v>
       </c>
       <c r="R10" t="n">
-        <v>6764369</v>
+        <v>6764371</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
+          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,7 +1681,7 @@
         <v>129291402</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129293927</v>
+        <v>129294029</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,34 +1801,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491997</v>
+        <v>492007</v>
       </c>
       <c r="R12" t="n">
-        <v>6764269</v>
+        <v>6764289</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1871,11 +1876,6 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129294029</v>
+        <v>129293927</v>
       </c>
       <c r="B13" t="n">
-        <v>57885</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,39 +1913,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492007</v>
+        <v>491997</v>
       </c>
       <c r="R13" t="n">
-        <v>6764289</v>
+        <v>6764269</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1988,6 +1983,11 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,7 +2017,7 @@
         <v>129287945</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129296076</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>129293376</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>129294004</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129294398</v>
+        <v>129293473</v>
       </c>
       <c r="B18" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,42 +2463,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491957</v>
+        <v>492120</v>
       </c>
       <c r="R18" t="n">
-        <v>6764346</v>
+        <v>6764224</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2564,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129271179</v>
+        <v>129290547</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2575,42 +2570,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492113</v>
+        <v>492071</v>
       </c>
       <c r="R19" t="n">
-        <v>6764152</v>
+        <v>6764318</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2634,27 +2624,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2681,10 +2671,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129293473</v>
+        <v>129293152</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,10 +2706,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492120</v>
+        <v>492125</v>
       </c>
       <c r="R20" t="n">
-        <v>6764224</v>
+        <v>6764158</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2788,10 +2778,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129293152</v>
+        <v>129271179</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,34 +2789,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492125</v>
+        <v>492113</v>
       </c>
       <c r="R21" t="n">
-        <v>6764158</v>
+        <v>6764152</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2853,22 +2848,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129290547</v>
+        <v>129294398</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,34 +2906,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492071</v>
+        <v>491957</v>
       </c>
       <c r="R22" t="n">
-        <v>6764318</v>
+        <v>6764346</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2965,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2975,12 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129273280</v>
+        <v>129294219</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>91827</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492172</v>
+        <v>491922</v>
       </c>
       <c r="R23" t="n">
-        <v>6764333</v>
+        <v>6764336</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3072,27 +3072,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129294219</v>
+        <v>129273280</v>
       </c>
       <c r="B24" t="n">
-        <v>91825</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491922</v>
+        <v>492172</v>
       </c>
       <c r="R24" t="n">
-        <v>6764336</v>
+        <v>6764333</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3184,27 +3184,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>39. 2 bild</t>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3234,7 +3234,7 @@
         <v>129294699</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         <v>129274016</v>
       </c>
       <c r="B26" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>129290672</v>
       </c>
       <c r="B27" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129294335</v>
+        <v>129294905</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491922</v>
+        <v>492048</v>
       </c>
       <c r="R28" t="n">
-        <v>6764336</v>
+        <v>6764380</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3653,6 +3653,11 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3679,10 +3684,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129294905</v>
+        <v>129294335</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3714,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492048</v>
+        <v>491922</v>
       </c>
       <c r="R29" t="n">
-        <v>6764380</v>
+        <v>6764336</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3760,11 +3765,6 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3794,7 +3794,7 @@
         <v>129290087</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>129295250</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>129289310</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>129294510</v>
       </c>
       <c r="B33" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129289434</v>
+        <v>129295876</v>
       </c>
       <c r="B34" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492159</v>
+        <v>492080</v>
       </c>
       <c r="R34" t="n">
-        <v>6764383</v>
+        <v>6764357</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>16. 2 bild</t>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4354,7 +4354,7 @@
         <v>129294091</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4458,10 +4458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129295876</v>
+        <v>129289434</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>91542</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4469,21 +4469,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492080</v>
+        <v>492159</v>
       </c>
       <c r="R36" t="n">
-        <v>6764357</v>
+        <v>6764383</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>55. 1 bild hängande på gren</t>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129294065</v>
+        <v>129293510</v>
       </c>
       <c r="B37" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491997</v>
+        <v>492107</v>
       </c>
       <c r="R37" t="n">
-        <v>6764302</v>
+        <v>6764244</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4651,11 +4651,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4682,10 +4677,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294432</v>
+        <v>129294065</v>
       </c>
       <c r="B38" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4717,13 +4712,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491957</v>
+        <v>491997</v>
       </c>
       <c r="R38" t="n">
-        <v>6764346</v>
+        <v>6764302</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4767,7 +4762,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>44. 2 bilder, granlåga</t>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4794,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129293510</v>
+        <v>129294432</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>91542</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4805,21 +4800,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4829,13 +4824,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492107</v>
+        <v>491957</v>
       </c>
       <c r="R39" t="n">
-        <v>6764244</v>
+        <v>6764346</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4875,6 +4870,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,32 +4901,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129290779</v>
+        <v>129293744</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4936,13 +4936,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492030</v>
+        <v>492059</v>
       </c>
       <c r="R40" t="n">
-        <v>6764279</v>
+        <v>6764244</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4981,12 +4981,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5013,10 +5008,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129293401</v>
+        <v>129290779</v>
       </c>
       <c r="B41" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5024,42 +5019,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492123</v>
+        <v>492030</v>
       </c>
       <c r="R41" t="n">
-        <v>6764202</v>
+        <v>6764279</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5088,7 +5078,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5098,12 +5088,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5130,10 +5120,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129295996</v>
+        <v>129293719</v>
       </c>
       <c r="B42" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5141,39 +5131,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R42" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5216,11 +5201,6 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5247,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129289411</v>
+        <v>129293401</v>
       </c>
       <c r="B43" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5287,13 +5267,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492157</v>
+        <v>492123</v>
       </c>
       <c r="R43" t="n">
-        <v>6764400</v>
+        <v>6764202</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5322,7 +5302,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5332,12 +5312,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5364,10 +5344,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293719</v>
+        <v>129295996</v>
       </c>
       <c r="B44" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5375,34 +5355,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492059</v>
+        <v>492085</v>
       </c>
       <c r="R44" t="n">
-        <v>6764244</v>
+        <v>6764296</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5445,6 +5430,11 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5471,48 +5461,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129293744</v>
+        <v>129289411</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492059</v>
+        <v>492157</v>
       </c>
       <c r="R45" t="n">
-        <v>6764244</v>
+        <v>6764400</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5541,7 +5536,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5551,7 +5546,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5581,7 +5581,7 @@
         <v>129289685</v>
       </c>
       <c r="B46" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>129293571</v>
       </c>
       <c r="B47" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>129274000</v>
       </c>
       <c r="B48" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>129294362</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6029,10 +6029,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129296258</v>
+        <v>129290171</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,21 +6040,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492091</v>
+        <v>492061</v>
       </c>
       <c r="R50" t="n">
-        <v>6764217</v>
+        <v>6764382</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6136,10 +6136,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129290171</v>
+        <v>129296258</v>
       </c>
       <c r="B51" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492061</v>
+        <v>492091</v>
       </c>
       <c r="R51" t="n">
-        <v>6764382</v>
+        <v>6764217</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6246,7 +6246,7 @@
         <v>129274938</v>
       </c>
       <c r="B52" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>129282981</v>
       </c>
       <c r="B53" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>129293814</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>129286796</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>129282927</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>129290011</v>
       </c>
       <c r="B57" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>129283290</v>
       </c>
       <c r="B58" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7037,10 +7037,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129283043</v>
+        <v>129287728</v>
       </c>
       <c r="B59" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7048,39 +7048,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492082</v>
+        <v>492227</v>
       </c>
       <c r="R59" t="n">
-        <v>6764210</v>
+        <v>6764369</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7112,7 +7107,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7122,12 +7117,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>3. 1 bild</t>
+          <t>12. 1 Bild på kolarkoja</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7154,10 +7149,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129287728</v>
+        <v>129283635</v>
       </c>
       <c r="B60" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7189,13 +7184,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492227</v>
+        <v>492082</v>
       </c>
       <c r="R60" t="n">
-        <v>6764369</v>
+        <v>6764245</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7224,7 +7219,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7234,12 +7229,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>12. 1 Bild på kolarkoja</t>
+          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7266,10 +7261,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129283635</v>
+        <v>129283043</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7277,24 +7272,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
@@ -7304,10 +7304,10 @@
         <v>492082</v>
       </c>
       <c r="R61" t="n">
-        <v>6764245</v>
+        <v>6764210</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
+          <t>3. 1 bild</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7381,7 +7381,7 @@
         <v>129287751</v>
       </c>
       <c r="B62" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129270999</v>
+        <v>129271992</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,39 +1134,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492105</v>
+        <v>492111</v>
       </c>
       <c r="R6" t="n">
-        <v>6764156</v>
+        <v>6764274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,11 +1204,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,32 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129271992</v>
+        <v>129294088</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492111</v>
+        <v>491988</v>
       </c>
       <c r="R7" t="n">
-        <v>6764274</v>
+        <v>6764293</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,22 +1295,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,45 +1337,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129294088</v>
+        <v>129270999</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491988</v>
+        <v>492105</v>
       </c>
       <c r="R8" t="n">
-        <v>6764293</v>
+        <v>6764156</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,22 +1407,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129291402</v>
+        <v>129293927</v>
       </c>
       <c r="B11" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,21 +1689,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R11" t="n">
-        <v>6764244</v>
+        <v>6764269</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129293927</v>
+        <v>129291402</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,21 +1913,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491997</v>
+        <v>492107</v>
       </c>
       <c r="R13" t="n">
-        <v>6764269</v>
+        <v>6764244</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129293473</v>
+        <v>129294398</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,37 +2463,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492120</v>
+        <v>491957</v>
       </c>
       <c r="R18" t="n">
-        <v>6764224</v>
+        <v>6764346</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2559,7 +2564,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129290547</v>
+        <v>129293473</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2594,13 +2599,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492071</v>
+        <v>492120</v>
       </c>
       <c r="R19" t="n">
-        <v>6764318</v>
+        <v>6764224</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2634,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,12 +2644,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,7 +2671,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129293152</v>
+        <v>129290547</v>
       </c>
       <c r="B20" t="n">
         <v>79041</v>
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492125</v>
+        <v>492071</v>
       </c>
       <c r="R20" t="n">
-        <v>6764158</v>
+        <v>6764318</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2751,7 +2751,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2778,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129271179</v>
+        <v>129293152</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,39 +2794,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492113</v>
+        <v>492125</v>
       </c>
       <c r="R21" t="n">
-        <v>6764152</v>
+        <v>6764158</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2848,27 +2848,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,10 +2890,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129294398</v>
+        <v>129271179</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,16 +2901,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2926,7 +2921,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2930,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491957</v>
+        <v>492113</v>
       </c>
       <c r="R22" t="n">
-        <v>6764346</v>
+        <v>6764152</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2965,22 +2960,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129294219</v>
+        <v>129274016</v>
       </c>
       <c r="B23" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,34 +3018,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491922</v>
+        <v>492092</v>
       </c>
       <c r="R23" t="n">
-        <v>6764336</v>
+        <v>6764410</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3072,27 +3077,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>39. 2 bild</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,10 +3124,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129273280</v>
+        <v>129294219</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>91827</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,21 +3135,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3154,10 +3159,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492172</v>
+        <v>491922</v>
       </c>
       <c r="R24" t="n">
-        <v>6764333</v>
+        <v>6764336</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3184,27 +3189,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,7 +3236,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129294699</v>
+        <v>129273280</v>
       </c>
       <c r="B25" t="n">
         <v>79041</v>
@@ -3266,13 +3271,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491988</v>
+        <v>492172</v>
       </c>
       <c r="R25" t="n">
-        <v>6764346</v>
+        <v>6764333</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3296,27 +3301,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3343,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129274016</v>
+        <v>129294699</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,42 +3359,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492092</v>
+        <v>491988</v>
       </c>
       <c r="R26" t="n">
-        <v>6764410</v>
+        <v>6764346</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3413,27 +3413,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129289310</v>
+        <v>129294510</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4021,37 +4021,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492177</v>
+        <v>491975</v>
       </c>
       <c r="R32" t="n">
-        <v>6764418</v>
+        <v>6764342</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4080,7 +4085,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4090,12 +4095,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
+          <t>45. 3 bilder, miljöbilder</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4122,10 +4127,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129294510</v>
+        <v>129289310</v>
       </c>
       <c r="B33" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4133,42 +4138,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491975</v>
+        <v>492177</v>
       </c>
       <c r="R33" t="n">
-        <v>6764342</v>
+        <v>6764418</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>45. 3 bilder, miljöbilder</t>
+          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129293510</v>
+        <v>129294065</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R37" t="n">
-        <v>6764244</v>
+        <v>6764302</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4651,6 +4651,11 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4677,7 +4682,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294065</v>
+        <v>129294432</v>
       </c>
       <c r="B38" t="n">
         <v>91542</v>
@@ -4712,13 +4717,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491997</v>
+        <v>491957</v>
       </c>
       <c r="R38" t="n">
-        <v>6764302</v>
+        <v>6764346</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4762,7 +4767,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>38. 1 bild, granlåga</t>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4789,10 +4794,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129294432</v>
+        <v>129293510</v>
       </c>
       <c r="B39" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,21 +4805,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4824,13 +4829,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491957</v>
+        <v>492107</v>
       </c>
       <c r="R39" t="n">
-        <v>6764346</v>
+        <v>6764244</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4870,11 +4875,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,45 +4901,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129293744</v>
+        <v>129293401</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492059</v>
+        <v>492123</v>
       </c>
       <c r="R40" t="n">
-        <v>6764244</v>
+        <v>6764202</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4982,6 +4987,11 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5008,10 +5018,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129290779</v>
+        <v>129295996</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5019,37 +5029,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492030</v>
+        <v>492085</v>
       </c>
       <c r="R41" t="n">
-        <v>6764279</v>
+        <v>6764296</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5078,7 +5093,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5088,12 +5103,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,10 +5135,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129293719</v>
+        <v>129289411</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5131,37 +5146,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492059</v>
+        <v>492157</v>
       </c>
       <c r="R42" t="n">
-        <v>6764244</v>
+        <v>6764400</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5190,7 +5210,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5200,7 +5220,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5227,10 +5252,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129293401</v>
+        <v>129290779</v>
       </c>
       <c r="B43" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,42 +5263,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492123</v>
+        <v>492030</v>
       </c>
       <c r="R43" t="n">
-        <v>6764202</v>
+        <v>6764279</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5302,7 +5322,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5312,12 +5332,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5344,10 +5364,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129295996</v>
+        <v>129293719</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,39 +5375,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R44" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5430,11 +5445,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5461,53 +5471,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129289411</v>
+        <v>129293744</v>
       </c>
       <c r="B45" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492157</v>
+        <v>492059</v>
       </c>
       <c r="R45" t="n">
-        <v>6764400</v>
+        <v>6764244</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5536,7 +5541,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5546,12 +5551,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>15. 1 bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -7037,10 +7037,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129287728</v>
+        <v>129283043</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7048,34 +7048,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492227</v>
+        <v>492082</v>
       </c>
       <c r="R59" t="n">
-        <v>6764369</v>
+        <v>6764210</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7107,7 +7112,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7117,12 +7122,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>12. 1 Bild på kolarkoja</t>
+          <t>3. 1 bild</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7149,7 +7154,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129283635</v>
+        <v>129287728</v>
       </c>
       <c r="B60" t="n">
         <v>79041</v>
@@ -7184,13 +7189,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492082</v>
+        <v>492227</v>
       </c>
       <c r="R60" t="n">
-        <v>6764245</v>
+        <v>6764369</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7219,7 +7224,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7229,12 +7234,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
+          <t>12. 1 Bild på kolarkoja</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7261,10 +7266,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129283043</v>
+        <v>129283635</v>
       </c>
       <c r="B61" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7272,29 +7277,24 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
@@ -7304,10 +7304,10 @@
         <v>492082</v>
       </c>
       <c r="R61" t="n">
-        <v>6764210</v>
+        <v>6764245</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>3. 1 bild</t>
+          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129293569</v>
+        <v>129290345</v>
       </c>
       <c r="B3" t="n">
-        <v>91542</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492107</v>
+        <v>492050</v>
       </c>
       <c r="R3" t="n">
-        <v>6764235</v>
+        <v>6764358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>35. 2 bilder, på granlåga</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129271386</v>
+        <v>129293569</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492097</v>
+        <v>492107</v>
       </c>
       <c r="R4" t="n">
-        <v>6764207</v>
+        <v>6764235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,27 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>35. 2 bilder, på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129290345</v>
+        <v>129271386</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,39 +1022,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492050</v>
+        <v>492097</v>
       </c>
       <c r="R5" t="n">
-        <v>6764358</v>
+        <v>6764207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129293927</v>
+        <v>129291402</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,21 +1689,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491997</v>
+        <v>492107</v>
       </c>
       <c r="R11" t="n">
-        <v>6764269</v>
+        <v>6764244</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129294029</v>
+        <v>129293927</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,39 +1801,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492007</v>
+        <v>491997</v>
       </c>
       <c r="R12" t="n">
-        <v>6764289</v>
+        <v>6764269</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1876,6 +1871,11 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129291402</v>
+        <v>129294029</v>
       </c>
       <c r="B13" t="n">
-        <v>91542</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,37 +1913,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492107</v>
+        <v>492007</v>
       </c>
       <c r="R13" t="n">
-        <v>6764244</v>
+        <v>6764289</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,12 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129294398</v>
+        <v>129293473</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,42 +2463,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491957</v>
+        <v>492120</v>
       </c>
       <c r="R18" t="n">
-        <v>6764346</v>
+        <v>6764224</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2564,7 +2559,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129293473</v>
+        <v>129290547</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2599,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492120</v>
+        <v>492071</v>
       </c>
       <c r="R19" t="n">
-        <v>6764224</v>
+        <v>6764318</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2634,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2644,7 +2639,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,7 +2671,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129290547</v>
+        <v>129293152</v>
       </c>
       <c r="B20" t="n">
         <v>79041</v>
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492071</v>
+        <v>492125</v>
       </c>
       <c r="R20" t="n">
-        <v>6764318</v>
+        <v>6764158</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2751,12 +2751,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,10 +2778,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129293152</v>
+        <v>129271179</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2794,34 +2789,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492125</v>
+        <v>492113</v>
       </c>
       <c r="R21" t="n">
-        <v>6764158</v>
+        <v>6764152</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2848,22 +2848,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129271179</v>
+        <v>129294398</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2901,16 +2906,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2921,7 +2926,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2930,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492113</v>
+        <v>491957</v>
       </c>
       <c r="R22" t="n">
-        <v>6764152</v>
+        <v>6764346</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2960,27 +2965,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4901,10 +4901,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129293401</v>
+        <v>129290779</v>
       </c>
       <c r="B40" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4912,42 +4912,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492123</v>
+        <v>492030</v>
       </c>
       <c r="R40" t="n">
-        <v>6764202</v>
+        <v>6764279</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4976,7 +4971,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4986,12 +4981,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5018,10 +5013,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129295996</v>
+        <v>129293719</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5029,39 +5024,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R41" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5104,11 +5094,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5135,7 +5120,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129289411</v>
+        <v>129293401</v>
       </c>
       <c r="B42" t="n">
         <v>57724</v>
@@ -5175,13 +5160,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492157</v>
+        <v>492123</v>
       </c>
       <c r="R42" t="n">
-        <v>6764400</v>
+        <v>6764202</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5210,7 +5195,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5220,12 +5205,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5252,10 +5237,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129290779</v>
+        <v>129289411</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5263,34 +5248,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492030</v>
+        <v>492157</v>
       </c>
       <c r="R43" t="n">
-        <v>6764279</v>
+        <v>6764400</v>
       </c>
       <c r="S43" t="n">
         <v>50</v>
@@ -5337,7 +5327,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5364,10 +5354,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293719</v>
+        <v>129295996</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5375,34 +5365,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492059</v>
+        <v>492085</v>
       </c>
       <c r="R44" t="n">
-        <v>6764244</v>
+        <v>6764296</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5445,6 +5440,11 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129290345</v>
+        <v>129293569</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>91540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492050</v>
+        <v>492107</v>
       </c>
       <c r="R3" t="n">
-        <v>6764358</v>
+        <v>6764235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>35. 2 bilder, på granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129293569</v>
+        <v>129290345</v>
       </c>
       <c r="B4" t="n">
-        <v>91542</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492107</v>
+        <v>492050</v>
       </c>
       <c r="R4" t="n">
-        <v>6764235</v>
+        <v>6764358</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>35. 2 bilder, på granlåga</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129271992</v>
+        <v>129270999</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,34 +1134,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492111</v>
+        <v>492105</v>
       </c>
       <c r="R6" t="n">
-        <v>6764274</v>
+        <v>6764156</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,6 +1209,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,32 +1240,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129294088</v>
+        <v>129271992</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491988</v>
+        <v>492111</v>
       </c>
       <c r="R7" t="n">
-        <v>6764293</v>
+        <v>6764274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,22 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,50 +1347,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129270999</v>
+        <v>129294088</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492105</v>
+        <v>491988</v>
       </c>
       <c r="R8" t="n">
-        <v>6764156</v>
+        <v>6764293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,27 +1412,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1681,7 +1681,7 @@
         <v>129291402</v>
       </c>
       <c r="B11" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129293473</v>
+        <v>129293152</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492120</v>
+        <v>492125</v>
       </c>
       <c r="R18" t="n">
-        <v>6764224</v>
+        <v>6764158</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2559,7 +2559,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129290547</v>
+        <v>129293473</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492071</v>
+        <v>492120</v>
       </c>
       <c r="R19" t="n">
-        <v>6764318</v>
+        <v>6764224</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,12 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,7 +2666,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129293152</v>
+        <v>129290547</v>
       </c>
       <c r="B20" t="n">
         <v>79041</v>
@@ -2706,13 +2701,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492125</v>
+        <v>492071</v>
       </c>
       <c r="R20" t="n">
-        <v>6764158</v>
+        <v>6764318</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2751,7 +2746,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2778,10 +2778,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129271179</v>
+        <v>129294398</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,16 +2789,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2809,7 +2809,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492113</v>
+        <v>491957</v>
       </c>
       <c r="R21" t="n">
-        <v>6764152</v>
+        <v>6764346</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2848,27 +2848,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,10 +2890,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129294398</v>
+        <v>129271179</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,16 +2901,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2926,7 +2921,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2930,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491957</v>
+        <v>492113</v>
       </c>
       <c r="R22" t="n">
-        <v>6764346</v>
+        <v>6764152</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2965,22 +2960,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129274016</v>
+        <v>129273280</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,39 +3018,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492092</v>
+        <v>492172</v>
       </c>
       <c r="R23" t="n">
-        <v>6764410</v>
+        <v>6764333</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3097,7 +3092,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3124,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129294219</v>
+        <v>129294699</v>
       </c>
       <c r="B24" t="n">
-        <v>91827</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3135,21 +3130,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3159,13 +3154,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491922</v>
+        <v>491988</v>
       </c>
       <c r="R24" t="n">
-        <v>6764336</v>
+        <v>6764346</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3209,7 +3204,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>39. 2 bild</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3236,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129273280</v>
+        <v>129274016</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3247,34 +3242,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492172</v>
+        <v>492092</v>
       </c>
       <c r="R25" t="n">
-        <v>6764333</v>
+        <v>6764410</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,45 +3348,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129294699</v>
+        <v>129290672</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491988</v>
+        <v>492030</v>
       </c>
       <c r="R26" t="n">
-        <v>6764346</v>
+        <v>6764294</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3418,7 +3423,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3428,12 +3433,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,53 +3460,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129290672</v>
+        <v>129294219</v>
       </c>
       <c r="B27" t="n">
-        <v>58097</v>
+        <v>91837</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492030</v>
+        <v>491922</v>
       </c>
       <c r="R27" t="n">
-        <v>6764294</v>
+        <v>6764336</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3535,7 +3530,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3545,7 +3540,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129294510</v>
+        <v>129289310</v>
       </c>
       <c r="B32" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4021,42 +4021,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491975</v>
+        <v>492177</v>
       </c>
       <c r="R32" t="n">
-        <v>6764342</v>
+        <v>6764418</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4085,7 +4080,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4095,12 +4090,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>45. 3 bilder, miljöbilder</t>
+          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4127,10 +4122,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129289310</v>
+        <v>129294510</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4138,37 +4133,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492177</v>
+        <v>491975</v>
       </c>
       <c r="R33" t="n">
-        <v>6764418</v>
+        <v>6764342</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
+          <t>45. 3 bilder, miljöbilder</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4461,7 +4461,7 @@
         <v>129289434</v>
       </c>
       <c r="B36" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129294065</v>
+        <v>129293510</v>
       </c>
       <c r="B37" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491997</v>
+        <v>492107</v>
       </c>
       <c r="R37" t="n">
-        <v>6764302</v>
+        <v>6764244</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4651,11 +4651,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4682,10 +4677,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294432</v>
+        <v>129294065</v>
       </c>
       <c r="B38" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4717,13 +4712,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491957</v>
+        <v>491997</v>
       </c>
       <c r="R38" t="n">
-        <v>6764346</v>
+        <v>6764302</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4767,7 +4762,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>44. 2 bilder, granlåga</t>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4794,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129293510</v>
+        <v>129294432</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4805,21 +4800,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4829,13 +4824,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492107</v>
+        <v>491957</v>
       </c>
       <c r="R39" t="n">
-        <v>6764244</v>
+        <v>6764346</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4875,6 +4870,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5120,50 +5120,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129293401</v>
+        <v>129293744</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492123</v>
+        <v>492059</v>
       </c>
       <c r="R42" t="n">
-        <v>6764202</v>
+        <v>6764244</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5206,11 +5201,6 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5237,53 +5227,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129289411</v>
+        <v>129289685</v>
       </c>
       <c r="B43" t="n">
-        <v>57724</v>
+        <v>97575</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492157</v>
+        <v>492160</v>
       </c>
       <c r="R43" t="n">
-        <v>6764400</v>
+        <v>6764361</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5327,7 +5312,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5354,7 +5339,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129295996</v>
+        <v>129293401</v>
       </c>
       <c r="B44" t="n">
         <v>57724</v>
@@ -5394,10 +5379,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492085</v>
+        <v>492123</v>
       </c>
       <c r="R44" t="n">
-        <v>6764296</v>
+        <v>6764202</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5444,7 +5429,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>56. 2 bilder, även svamp på gran</t>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5471,45 +5456,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129293744</v>
+        <v>129295996</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492059</v>
+        <v>492085</v>
       </c>
       <c r="R45" t="n">
-        <v>6764244</v>
+        <v>6764296</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5552,6 +5542,11 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5578,48 +5573,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289685</v>
+        <v>129289411</v>
       </c>
       <c r="B46" t="n">
-        <v>97549</v>
+        <v>57724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492160</v>
+        <v>492157</v>
       </c>
       <c r="R46" t="n">
-        <v>6764361</v>
+        <v>6764400</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6029,10 +6029,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129290171</v>
+        <v>129296258</v>
       </c>
       <c r="B50" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,21 +6040,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492061</v>
+        <v>492091</v>
       </c>
       <c r="R50" t="n">
-        <v>6764382</v>
+        <v>6764217</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6136,10 +6136,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129296258</v>
+        <v>129290171</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492091</v>
+        <v>492061</v>
       </c>
       <c r="R51" t="n">
-        <v>6764217</v>
+        <v>6764382</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7037,10 +7037,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129283043</v>
+        <v>129287728</v>
       </c>
       <c r="B59" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7048,39 +7048,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492082</v>
+        <v>492227</v>
       </c>
       <c r="R59" t="n">
-        <v>6764210</v>
+        <v>6764369</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7112,7 +7107,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7122,12 +7117,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>3. 1 bild</t>
+          <t>12. 1 Bild på kolarkoja</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7154,7 +7149,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129287728</v>
+        <v>129283635</v>
       </c>
       <c r="B60" t="n">
         <v>79041</v>
@@ -7189,13 +7184,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492227</v>
+        <v>492082</v>
       </c>
       <c r="R60" t="n">
-        <v>6764369</v>
+        <v>6764245</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7224,7 +7219,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7234,12 +7229,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>12. 1 Bild på kolarkoja</t>
+          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7266,10 +7261,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129283635</v>
+        <v>129283043</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7277,24 +7272,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
@@ -7304,10 +7304,10 @@
         <v>492082</v>
       </c>
       <c r="R61" t="n">
-        <v>6764245</v>
+        <v>6764210</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
+          <t>3. 1 bild</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129270999</v>
+        <v>129271992</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,39 +1134,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492105</v>
+        <v>492111</v>
       </c>
       <c r="R6" t="n">
-        <v>6764156</v>
+        <v>6764274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,11 +1204,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,32 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129271992</v>
+        <v>129294088</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492111</v>
+        <v>491988</v>
       </c>
       <c r="R7" t="n">
-        <v>6764274</v>
+        <v>6764293</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,22 +1295,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,45 +1337,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129294088</v>
+        <v>129270999</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491988</v>
+        <v>492105</v>
       </c>
       <c r="R8" t="n">
-        <v>6764293</v>
+        <v>6764156</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,22 +1407,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129291402</v>
+        <v>129293927</v>
       </c>
       <c r="B11" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,21 +1689,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R11" t="n">
-        <v>6764244</v>
+        <v>6764269</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129293927</v>
+        <v>129294029</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,34 +1801,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491997</v>
+        <v>492007</v>
       </c>
       <c r="R12" t="n">
-        <v>6764269</v>
+        <v>6764289</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1871,11 +1876,6 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129294029</v>
+        <v>129291402</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>91540</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,42 +1913,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492007</v>
+        <v>492107</v>
       </c>
       <c r="R13" t="n">
-        <v>6764289</v>
+        <v>6764244</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1982,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129293152</v>
+        <v>129271179</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,34 +2463,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492125</v>
+        <v>492113</v>
       </c>
       <c r="R18" t="n">
-        <v>6764158</v>
+        <v>6764152</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,22 +2522,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129293473</v>
+        <v>129294398</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,37 +2580,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492120</v>
+        <v>491957</v>
       </c>
       <c r="R19" t="n">
-        <v>6764224</v>
+        <v>6764346</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2666,7 +2681,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129290547</v>
+        <v>129293473</v>
       </c>
       <c r="B20" t="n">
         <v>79041</v>
@@ -2701,13 +2716,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492071</v>
+        <v>492120</v>
       </c>
       <c r="R20" t="n">
-        <v>6764318</v>
+        <v>6764224</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2736,7 +2751,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,12 +2761,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2778,10 +2788,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129294398</v>
+        <v>129290547</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,39 +2799,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491957</v>
+        <v>492071</v>
       </c>
       <c r="R21" t="n">
-        <v>6764346</v>
+        <v>6764318</v>
       </c>
       <c r="S21" t="n">
         <v>50</v>
@@ -2853,7 +2858,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2863,7 +2868,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129271179</v>
+        <v>129293152</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2901,39 +2911,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492113</v>
+        <v>492125</v>
       </c>
       <c r="R22" t="n">
-        <v>6764152</v>
+        <v>6764158</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,27 +2965,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3348,53 +3348,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129290672</v>
+        <v>129294219</v>
       </c>
       <c r="B26" t="n">
-        <v>58097</v>
+        <v>91838</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492030</v>
+        <v>491922</v>
       </c>
       <c r="R26" t="n">
-        <v>6764294</v>
+        <v>6764336</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3423,7 +3418,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3433,7 +3428,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,48 +3460,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129294219</v>
+        <v>129290672</v>
       </c>
       <c r="B27" t="n">
-        <v>91837</v>
+        <v>58097</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491922</v>
+        <v>492030</v>
       </c>
       <c r="R27" t="n">
-        <v>6764336</v>
+        <v>6764294</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3530,7 +3535,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3540,12 +3545,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>39. 2 bild</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,7 +3572,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129294905</v>
+        <v>129290087</v>
       </c>
       <c r="B28" t="n">
         <v>79041</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492048</v>
+        <v>492083</v>
       </c>
       <c r="R28" t="n">
-        <v>6764380</v>
+        <v>6764418</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3652,12 +3652,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3684,7 +3679,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129294335</v>
+        <v>129294905</v>
       </c>
       <c r="B29" t="n">
         <v>79041</v>
@@ -3719,10 +3714,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491922</v>
+        <v>492048</v>
       </c>
       <c r="R29" t="n">
-        <v>6764336</v>
+        <v>6764380</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3765,6 +3760,11 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3791,7 +3791,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129290087</v>
+        <v>129294335</v>
       </c>
       <c r="B30" t="n">
         <v>79041</v>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492083</v>
+        <v>491922</v>
       </c>
       <c r="R30" t="n">
-        <v>6764418</v>
+        <v>6764336</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129289310</v>
+        <v>129294510</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4021,37 +4021,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492177</v>
+        <v>491975</v>
       </c>
       <c r="R32" t="n">
-        <v>6764418</v>
+        <v>6764342</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4080,7 +4085,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4090,12 +4095,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
+          <t>45. 3 bilder, miljöbilder</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4122,10 +4127,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129294510</v>
+        <v>129289310</v>
       </c>
       <c r="B33" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4133,42 +4138,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491975</v>
+        <v>492177</v>
       </c>
       <c r="R33" t="n">
-        <v>6764342</v>
+        <v>6764418</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>45. 3 bilder, miljöbilder</t>
+          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129295876</v>
+        <v>129289434</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492080</v>
+        <v>492159</v>
       </c>
       <c r="R34" t="n">
-        <v>6764357</v>
+        <v>6764383</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>55. 1 bild hängande på gren</t>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,7 +4351,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129294091</v>
+        <v>129295876</v>
       </c>
       <c r="B35" t="n">
         <v>79041</v>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491988</v>
+        <v>492080</v>
       </c>
       <c r="R35" t="n">
-        <v>6764293</v>
+        <v>6764357</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4432,6 +4432,11 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4458,10 +4463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129289434</v>
+        <v>129294091</v>
       </c>
       <c r="B36" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4469,21 +4474,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492159</v>
+        <v>491988</v>
       </c>
       <c r="R36" t="n">
-        <v>6764383</v>
+        <v>6764293</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4533,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4538,12 +4543,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>16. 2 bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129293510</v>
+        <v>129294432</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492107</v>
+        <v>491957</v>
       </c>
       <c r="R37" t="n">
-        <v>6764244</v>
+        <v>6764346</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4651,6 +4651,11 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4789,10 +4794,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129294432</v>
+        <v>129293510</v>
       </c>
       <c r="B39" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,21 +4805,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4824,13 +4829,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491957</v>
+        <v>492107</v>
       </c>
       <c r="R39" t="n">
-        <v>6764346</v>
+        <v>6764244</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4870,11 +4875,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,10 +4901,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129290779</v>
+        <v>129293401</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4912,37 +4912,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492030</v>
+        <v>492123</v>
       </c>
       <c r="R40" t="n">
-        <v>6764279</v>
+        <v>6764202</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4971,7 +4976,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4981,12 +4986,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5013,10 +5018,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129293719</v>
+        <v>129295996</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5024,34 +5029,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492059</v>
+        <v>492085</v>
       </c>
       <c r="R41" t="n">
-        <v>6764244</v>
+        <v>6764296</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5094,6 +5104,11 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,48 +5135,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129293744</v>
+        <v>129289411</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492059</v>
+        <v>492157</v>
       </c>
       <c r="R42" t="n">
-        <v>6764244</v>
+        <v>6764400</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5190,7 +5210,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5200,7 +5220,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5227,32 +5252,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129289685</v>
+        <v>129290779</v>
       </c>
       <c r="B43" t="n">
-        <v>97575</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5262,13 +5287,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492160</v>
+        <v>492030</v>
       </c>
       <c r="R43" t="n">
-        <v>6764361</v>
+        <v>6764279</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5312,7 +5337,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5339,10 +5364,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293401</v>
+        <v>129293719</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5350,39 +5375,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492123</v>
+        <v>492059</v>
       </c>
       <c r="R44" t="n">
-        <v>6764202</v>
+        <v>6764244</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5425,11 +5445,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,50 +5471,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129295996</v>
+        <v>129293744</v>
       </c>
       <c r="B45" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R45" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5542,11 +5552,6 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5573,53 +5578,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289411</v>
+        <v>129289685</v>
       </c>
       <c r="B46" t="n">
-        <v>57724</v>
+        <v>97576</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492157</v>
+        <v>492160</v>
       </c>
       <c r="R46" t="n">
-        <v>6764400</v>
+        <v>6764361</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129293571</v>
+        <v>129274000</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,34 +5701,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492107</v>
+        <v>492089</v>
       </c>
       <c r="R47" t="n">
-        <v>6764235</v>
+        <v>6764397</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5755,22 +5763,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 bild samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5797,10 +5810,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129274000</v>
+        <v>129293571</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5808,42 +5821,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492089</v>
+        <v>492107</v>
       </c>
       <c r="R48" t="n">
-        <v>6764397</v>
+        <v>6764235</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5870,27 +5875,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 bild samt miljöbilder för området</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5917,10 +5917,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129294362</v>
+        <v>129290171</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5928,21 +5928,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5952,13 +5952,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491956</v>
+        <v>492061</v>
       </c>
       <c r="R49" t="n">
-        <v>6764334</v>
+        <v>6764382</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5997,12 +5997,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6029,7 +6024,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129296258</v>
+        <v>129294362</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -6064,13 +6059,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492091</v>
+        <v>491956</v>
       </c>
       <c r="R50" t="n">
-        <v>6764217</v>
+        <v>6764334</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6110,6 +6105,11 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6136,10 +6136,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129290171</v>
+        <v>129274938</v>
       </c>
       <c r="B51" t="n">
-        <v>79660</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,34 +6147,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492061</v>
+        <v>492048</v>
       </c>
       <c r="R51" t="n">
-        <v>6764382</v>
+        <v>6764380</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6201,22 +6206,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>I bild</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6243,10 +6253,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129274938</v>
+        <v>129296258</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6254,39 +6264,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492048</v>
+        <v>492091</v>
       </c>
       <c r="R52" t="n">
-        <v>6764380</v>
+        <v>6764217</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6313,27 +6318,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>I bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129290345</v>
+        <v>129271386</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492050</v>
+        <v>492097</v>
       </c>
       <c r="R4" t="n">
-        <v>6764358</v>
+        <v>6764207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,27 +959,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129271386</v>
+        <v>129290345</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,34 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492097</v>
+        <v>492050</v>
       </c>
       <c r="R5" t="n">
-        <v>6764207</v>
+        <v>6764358</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1230,45 +1230,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129294088</v>
+        <v>129270999</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491988</v>
+        <v>492105</v>
       </c>
       <c r="R7" t="n">
-        <v>6764293</v>
+        <v>6764156</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,22 +1300,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,50 +1347,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129270999</v>
+        <v>129294088</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492105</v>
+        <v>491988</v>
       </c>
       <c r="R8" t="n">
-        <v>6764156</v>
+        <v>6764293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,27 +1412,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129294029</v>
+        <v>129291402</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>91540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,42 +1801,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492007</v>
+        <v>492107</v>
       </c>
       <c r="R12" t="n">
-        <v>6764289</v>
+        <v>6764244</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1875,7 +1870,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129291402</v>
+        <v>129294029</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,37 +1913,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492107</v>
+        <v>492007</v>
       </c>
       <c r="R13" t="n">
-        <v>6764244</v>
+        <v>6764289</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,12 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129271179</v>
+        <v>129293473</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,39 +2463,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492113</v>
+        <v>492120</v>
       </c>
       <c r="R18" t="n">
-        <v>6764152</v>
+        <v>6764224</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,27 +2517,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2569,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129294398</v>
+        <v>129290547</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2580,39 +2570,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491957</v>
+        <v>492071</v>
       </c>
       <c r="R19" t="n">
-        <v>6764346</v>
+        <v>6764318</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2644,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2654,7 +2639,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2681,7 +2671,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129293473</v>
+        <v>129293152</v>
       </c>
       <c r="B20" t="n">
         <v>79041</v>
@@ -2716,10 +2706,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492120</v>
+        <v>492125</v>
       </c>
       <c r="R20" t="n">
-        <v>6764224</v>
+        <v>6764158</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2788,10 +2778,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129290547</v>
+        <v>129271179</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,37 +2789,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492071</v>
+        <v>492113</v>
       </c>
       <c r="R21" t="n">
-        <v>6764318</v>
+        <v>6764152</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,27 +2848,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2900,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129293152</v>
+        <v>129294398</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,37 +2906,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492125</v>
+        <v>491957</v>
       </c>
       <c r="R22" t="n">
-        <v>6764158</v>
+        <v>6764346</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129273280</v>
+        <v>129294219</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>91838</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492172</v>
+        <v>491922</v>
       </c>
       <c r="R23" t="n">
-        <v>6764333</v>
+        <v>6764336</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3072,27 +3072,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,7 +3119,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129294699</v>
+        <v>129273280</v>
       </c>
       <c r="B24" t="n">
         <v>79041</v>
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491988</v>
+        <v>492172</v>
       </c>
       <c r="R24" t="n">
-        <v>6764346</v>
+        <v>6764333</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3184,27 +3184,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129274016</v>
+        <v>129294699</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,42 +3242,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492092</v>
+        <v>491988</v>
       </c>
       <c r="R25" t="n">
-        <v>6764410</v>
+        <v>6764346</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3301,27 +3296,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,10 +3343,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129294219</v>
+        <v>129274016</v>
       </c>
       <c r="B26" t="n">
-        <v>91838</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,34 +3354,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491922</v>
+        <v>492092</v>
       </c>
       <c r="R26" t="n">
-        <v>6764336</v>
+        <v>6764410</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3413,27 +3413,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>39. 2 bild</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3572,7 +3572,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129290087</v>
+        <v>129294905</v>
       </c>
       <c r="B28" t="n">
         <v>79041</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492083</v>
+        <v>492048</v>
       </c>
       <c r="R28" t="n">
-        <v>6764418</v>
+        <v>6764380</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3652,7 +3652,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3679,7 +3684,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129294905</v>
+        <v>129294335</v>
       </c>
       <c r="B29" t="n">
         <v>79041</v>
@@ -3714,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492048</v>
+        <v>491922</v>
       </c>
       <c r="R29" t="n">
-        <v>6764380</v>
+        <v>6764336</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3760,11 +3765,6 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3791,7 +3791,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129294335</v>
+        <v>129290087</v>
       </c>
       <c r="B30" t="n">
         <v>79041</v>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491922</v>
+        <v>492083</v>
       </c>
       <c r="R30" t="n">
-        <v>6764336</v>
+        <v>6764418</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129294510</v>
+        <v>129289310</v>
       </c>
       <c r="B32" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4021,42 +4021,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491975</v>
+        <v>492177</v>
       </c>
       <c r="R32" t="n">
-        <v>6764342</v>
+        <v>6764418</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4085,7 +4080,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4095,12 +4090,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>45. 3 bilder, miljöbilder</t>
+          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4127,10 +4122,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129289310</v>
+        <v>129294510</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4138,37 +4133,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492177</v>
+        <v>491975</v>
       </c>
       <c r="R33" t="n">
-        <v>6764418</v>
+        <v>6764342</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
+          <t>45. 3 bilder, miljöbilder</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129289434</v>
+        <v>129295876</v>
       </c>
       <c r="B34" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492159</v>
+        <v>492080</v>
       </c>
       <c r="R34" t="n">
-        <v>6764383</v>
+        <v>6764357</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>16. 2 bild</t>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,7 +4351,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129295876</v>
+        <v>129294091</v>
       </c>
       <c r="B35" t="n">
         <v>79041</v>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492080</v>
+        <v>491988</v>
       </c>
       <c r="R35" t="n">
-        <v>6764357</v>
+        <v>6764293</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4432,11 +4432,6 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4463,10 +4458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129294091</v>
+        <v>129289434</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,21 +4469,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491988</v>
+        <v>492159</v>
       </c>
       <c r="R36" t="n">
-        <v>6764293</v>
+        <v>6764383</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4533,7 +4528,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4543,7 +4538,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129294432</v>
+        <v>129293510</v>
       </c>
       <c r="B37" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491957</v>
+        <v>492107</v>
       </c>
       <c r="R37" t="n">
-        <v>6764346</v>
+        <v>6764244</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4651,11 +4651,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4794,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129293510</v>
+        <v>129294432</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4805,21 +4800,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4829,13 +4824,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492107</v>
+        <v>491957</v>
       </c>
       <c r="R39" t="n">
-        <v>6764244</v>
+        <v>6764346</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4875,6 +4870,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,10 +4901,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129293401</v>
+        <v>129290779</v>
       </c>
       <c r="B40" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4912,42 +4912,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492123</v>
+        <v>492030</v>
       </c>
       <c r="R40" t="n">
-        <v>6764202</v>
+        <v>6764279</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4976,7 +4971,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4986,12 +4981,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5018,10 +5013,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129295996</v>
+        <v>129293719</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5029,39 +5024,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R41" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5104,11 +5094,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5135,53 +5120,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129289411</v>
+        <v>129293744</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492157</v>
+        <v>492059</v>
       </c>
       <c r="R42" t="n">
-        <v>6764400</v>
+        <v>6764244</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5210,7 +5190,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5220,12 +5200,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>15. 1 bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5252,32 +5227,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129290779</v>
+        <v>129289685</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>97577</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5287,13 +5262,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492030</v>
+        <v>492160</v>
       </c>
       <c r="R43" t="n">
-        <v>6764279</v>
+        <v>6764361</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5337,7 +5312,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5364,10 +5339,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293719</v>
+        <v>129293401</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5375,34 +5350,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492059</v>
+        <v>492123</v>
       </c>
       <c r="R44" t="n">
-        <v>6764244</v>
+        <v>6764202</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5445,6 +5425,11 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5471,45 +5456,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129293744</v>
+        <v>129295996</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492059</v>
+        <v>492085</v>
       </c>
       <c r="R45" t="n">
-        <v>6764244</v>
+        <v>6764296</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5552,6 +5542,11 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5578,48 +5573,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289685</v>
+        <v>129289411</v>
       </c>
       <c r="B46" t="n">
-        <v>97576</v>
+        <v>57724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492160</v>
+        <v>492157</v>
       </c>
       <c r="R46" t="n">
-        <v>6764361</v>
+        <v>6764400</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129274000</v>
+        <v>129293571</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,42 +5701,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492089</v>
+        <v>492107</v>
       </c>
       <c r="R47" t="n">
-        <v>6764397</v>
+        <v>6764235</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5763,27 +5755,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>1 bild samt miljöbilder för området</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5810,10 +5797,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129293571</v>
+        <v>129274000</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5821,34 +5808,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492107</v>
+        <v>492089</v>
       </c>
       <c r="R48" t="n">
-        <v>6764235</v>
+        <v>6764397</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5875,22 +5870,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 bild samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5917,10 +5917,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129290171</v>
+        <v>129294362</v>
       </c>
       <c r="B49" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5928,21 +5928,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5952,13 +5952,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492061</v>
+        <v>491956</v>
       </c>
       <c r="R49" t="n">
-        <v>6764382</v>
+        <v>6764334</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5997,7 +5997,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6024,10 +6029,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129294362</v>
+        <v>129290171</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6035,21 +6040,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6059,13 +6064,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491956</v>
+        <v>492061</v>
       </c>
       <c r="R50" t="n">
-        <v>6764334</v>
+        <v>6764382</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6094,7 +6099,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6104,12 +6109,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6136,10 +6136,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129274938</v>
+        <v>129296258</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,39 +6147,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492048</v>
+        <v>492091</v>
       </c>
       <c r="R51" t="n">
-        <v>6764380</v>
+        <v>6764217</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6206,27 +6201,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>I bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6253,10 +6243,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129296258</v>
+        <v>129274938</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6264,34 +6254,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492091</v>
+        <v>492048</v>
       </c>
       <c r="R52" t="n">
-        <v>6764217</v>
+        <v>6764380</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6318,22 +6313,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>I bild</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129271130</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129293569</v>
+        <v>129271386</v>
       </c>
       <c r="B3" t="n">
-        <v>91540</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492107</v>
+        <v>492097</v>
       </c>
       <c r="R3" t="n">
-        <v>6764235</v>
+        <v>6764207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,27 +847,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>35. 2 bilder, på granlåga</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129271386</v>
+        <v>129290345</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492097</v>
+        <v>492050</v>
       </c>
       <c r="R4" t="n">
-        <v>6764207</v>
+        <v>6764358</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,27 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129290345</v>
+        <v>129293569</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>91543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,39 +1022,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492050</v>
+        <v>492107</v>
       </c>
       <c r="R5" t="n">
-        <v>6764358</v>
+        <v>6764235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>35. 2 bilder, på granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
         <v>129271992</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>129290261</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>129287686</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129293927</v>
+        <v>129291402</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>91543</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,21 +1689,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491997</v>
+        <v>492107</v>
       </c>
       <c r="R11" t="n">
-        <v>6764269</v>
+        <v>6764244</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129291402</v>
+        <v>129293927</v>
       </c>
       <c r="B12" t="n">
-        <v>91540</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,13 +1825,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R12" t="n">
-        <v>6764244</v>
+        <v>6764269</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2017,7 +2017,7 @@
         <v>129287945</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129296076</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>129293376</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>129294004</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129293473</v>
+        <v>129294398</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,37 +2463,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492120</v>
+        <v>491957</v>
       </c>
       <c r="R18" t="n">
-        <v>6764224</v>
+        <v>6764346</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2559,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129290547</v>
+        <v>129293473</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,13 +2599,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492071</v>
+        <v>492120</v>
       </c>
       <c r="R19" t="n">
-        <v>6764318</v>
+        <v>6764224</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2634,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,12 +2644,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,10 +2671,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129293152</v>
+        <v>129290547</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492125</v>
+        <v>492071</v>
       </c>
       <c r="R20" t="n">
-        <v>6764158</v>
+        <v>6764318</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2751,7 +2751,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2778,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129271179</v>
+        <v>129293152</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,39 +2794,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492113</v>
+        <v>492125</v>
       </c>
       <c r="R21" t="n">
-        <v>6764152</v>
+        <v>6764158</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2848,27 +2848,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,10 +2890,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129294398</v>
+        <v>129271179</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,16 +2901,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2926,7 +2921,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2930,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491957</v>
+        <v>492113</v>
       </c>
       <c r="R22" t="n">
-        <v>6764346</v>
+        <v>6764152</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2965,22 +2960,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129294219</v>
+        <v>129274016</v>
       </c>
       <c r="B23" t="n">
-        <v>91838</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,34 +3018,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491922</v>
+        <v>492092</v>
       </c>
       <c r="R23" t="n">
-        <v>6764336</v>
+        <v>6764410</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3072,27 +3077,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>39. 2 bild</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,48 +3124,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129273280</v>
+        <v>129290672</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>58097</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492172</v>
+        <v>492030</v>
       </c>
       <c r="R24" t="n">
-        <v>6764333</v>
+        <v>6764294</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3184,27 +3194,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,10 +3236,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129294699</v>
+        <v>129294219</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>91841</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,21 +3247,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3266,13 +3271,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491988</v>
+        <v>491922</v>
       </c>
       <c r="R25" t="n">
-        <v>6764346</v>
+        <v>6764336</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3316,7 +3321,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3343,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129274016</v>
+        <v>129273280</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,39 +3359,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492092</v>
+        <v>492172</v>
       </c>
       <c r="R26" t="n">
-        <v>6764410</v>
+        <v>6764333</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,50 +3460,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129290672</v>
+        <v>129294699</v>
       </c>
       <c r="B27" t="n">
-        <v>58097</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492030</v>
+        <v>491988</v>
       </c>
       <c r="R27" t="n">
-        <v>6764294</v>
+        <v>6764346</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3535,7 +3530,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3545,7 +3540,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3575,7 +3575,7 @@
         <v>129294905</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>129294335</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>129290087</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3901,7 +3901,7 @@
         <v>129295250</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>129289310</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129295876</v>
+        <v>129289434</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>91543</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492080</v>
+        <v>492159</v>
       </c>
       <c r="R34" t="n">
-        <v>6764357</v>
+        <v>6764383</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>55. 1 bild hängande på gren</t>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,10 +4351,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129294091</v>
+        <v>129295876</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491988</v>
+        <v>492080</v>
       </c>
       <c r="R35" t="n">
-        <v>6764293</v>
+        <v>6764357</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4432,6 +4432,11 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4458,10 +4463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129289434</v>
+        <v>129294091</v>
       </c>
       <c r="B36" t="n">
-        <v>91540</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4469,21 +4474,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492159</v>
+        <v>491988</v>
       </c>
       <c r="R36" t="n">
-        <v>6764383</v>
+        <v>6764293</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4533,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4538,12 +4543,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>16. 2 bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129293510</v>
+        <v>129294065</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>91543</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R37" t="n">
-        <v>6764244</v>
+        <v>6764302</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4651,6 +4651,11 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4677,10 +4682,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294065</v>
+        <v>129294432</v>
       </c>
       <c r="B38" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4712,13 +4717,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491997</v>
+        <v>491957</v>
       </c>
       <c r="R38" t="n">
-        <v>6764302</v>
+        <v>6764346</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4762,7 +4767,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>38. 1 bild, granlåga</t>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4789,10 +4794,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129294432</v>
+        <v>129293510</v>
       </c>
       <c r="B39" t="n">
-        <v>91540</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,21 +4805,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4824,13 +4829,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491957</v>
+        <v>492107</v>
       </c>
       <c r="R39" t="n">
-        <v>6764346</v>
+        <v>6764244</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4870,11 +4875,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,10 +4901,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129290779</v>
+        <v>129293401</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4912,37 +4912,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492030</v>
+        <v>492123</v>
       </c>
       <c r="R40" t="n">
-        <v>6764279</v>
+        <v>6764202</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4971,7 +4976,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4981,12 +4986,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5013,10 +5018,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129293719</v>
+        <v>129295996</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5024,34 +5029,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492059</v>
+        <v>492085</v>
       </c>
       <c r="R41" t="n">
-        <v>6764244</v>
+        <v>6764296</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5094,6 +5104,11 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,48 +5135,53 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129293744</v>
+        <v>129289411</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492059</v>
+        <v>492157</v>
       </c>
       <c r="R42" t="n">
-        <v>6764244</v>
+        <v>6764400</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5190,7 +5210,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5200,7 +5220,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5227,10 +5252,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129289685</v>
+        <v>129293744</v>
       </c>
       <c r="B43" t="n">
-        <v>97577</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,21 +5263,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5262,10 +5287,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492160</v>
+        <v>492059</v>
       </c>
       <c r="R43" t="n">
-        <v>6764361</v>
+        <v>6764244</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5297,7 +5322,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5307,12 +5332,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5339,50 +5359,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293401</v>
+        <v>129289685</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>97581</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492123</v>
+        <v>492160</v>
       </c>
       <c r="R44" t="n">
-        <v>6764202</v>
+        <v>6764361</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5414,7 +5429,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5424,12 +5439,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,10 +5471,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129295996</v>
+        <v>129290779</v>
       </c>
       <c r="B45" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5467,42 +5482,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492085</v>
+        <v>492030</v>
       </c>
       <c r="R45" t="n">
-        <v>6764296</v>
+        <v>6764279</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5531,7 +5541,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5541,12 +5551,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>56. 2 bilder, även svamp på gran</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5573,10 +5583,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289411</v>
+        <v>129293719</v>
       </c>
       <c r="B46" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5584,42 +5594,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492157</v>
+        <v>492059</v>
       </c>
       <c r="R46" t="n">
-        <v>6764400</v>
+        <v>6764244</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5648,7 +5653,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5658,12 +5663,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>15. 1 bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5693,7 +5693,7 @@
         <v>129293571</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>129294362</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6029,10 +6029,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129290171</v>
+        <v>129296258</v>
       </c>
       <c r="B50" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,21 +6040,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492061</v>
+        <v>492091</v>
       </c>
       <c r="R50" t="n">
-        <v>6764382</v>
+        <v>6764217</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6136,10 +6136,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129296258</v>
+        <v>129274938</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,34 +6147,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492091</v>
+        <v>492048</v>
       </c>
       <c r="R51" t="n">
-        <v>6764217</v>
+        <v>6764380</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6201,22 +6206,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>I bild</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6243,10 +6253,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129274938</v>
+        <v>129290171</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>79662</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6254,39 +6264,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492048</v>
+        <v>492061</v>
       </c>
       <c r="R52" t="n">
-        <v>6764380</v>
+        <v>6764382</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6313,27 +6318,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>I bild</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6475,7 +6475,7 @@
         <v>129293814</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>129286796</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>129282927</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>129283290</v>
       </c>
       <c r="B58" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>129287728</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>129283635</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129294398</v>
+        <v>129293473</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,42 +2463,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491957</v>
+        <v>492120</v>
       </c>
       <c r="R18" t="n">
-        <v>6764346</v>
+        <v>6764224</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2564,7 +2559,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129293473</v>
+        <v>129290547</v>
       </c>
       <c r="B19" t="n">
         <v>79043</v>
@@ -2599,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492120</v>
+        <v>492071</v>
       </c>
       <c r="R19" t="n">
-        <v>6764224</v>
+        <v>6764318</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2634,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2644,7 +2639,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,7 +2671,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129290547</v>
+        <v>129293152</v>
       </c>
       <c r="B20" t="n">
         <v>79043</v>
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492071</v>
+        <v>492125</v>
       </c>
       <c r="R20" t="n">
-        <v>6764318</v>
+        <v>6764158</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2751,12 +2751,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,10 +2778,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129293152</v>
+        <v>129294398</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2794,37 +2789,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492125</v>
+        <v>491957</v>
       </c>
       <c r="R21" t="n">
-        <v>6764158</v>
+        <v>6764346</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129274016</v>
+        <v>129294219</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,39 +3018,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492092</v>
+        <v>491922</v>
       </c>
       <c r="R23" t="n">
-        <v>6764410</v>
+        <v>6764336</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3077,27 +3072,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3124,53 +3119,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129290672</v>
+        <v>129273280</v>
       </c>
       <c r="B24" t="n">
-        <v>58097</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492030</v>
+        <v>492172</v>
       </c>
       <c r="R24" t="n">
-        <v>6764294</v>
+        <v>6764333</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3194,22 +3184,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3236,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129294219</v>
+        <v>129294699</v>
       </c>
       <c r="B25" t="n">
-        <v>91841</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3247,21 +3242,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3271,13 +3266,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491922</v>
+        <v>491988</v>
       </c>
       <c r="R25" t="n">
-        <v>6764336</v>
+        <v>6764346</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3321,7 +3316,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>39. 2 bild</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,10 +3343,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129273280</v>
+        <v>129274016</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3359,34 +3354,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492172</v>
+        <v>492092</v>
       </c>
       <c r="R26" t="n">
-        <v>6764333</v>
+        <v>6764410</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,45 +3460,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129294699</v>
+        <v>129290672</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>58097</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491988</v>
+        <v>492030</v>
       </c>
       <c r="R27" t="n">
-        <v>6764346</v>
+        <v>6764294</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3530,7 +3535,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3540,12 +3545,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129271130</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129271386</v>
+        <v>129290345</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492097</v>
+        <v>492050</v>
       </c>
       <c r="R3" t="n">
-        <v>6764207</v>
+        <v>6764358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,27 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129290345</v>
+        <v>129293569</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>91545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492050</v>
+        <v>492107</v>
       </c>
       <c r="R4" t="n">
-        <v>6764358</v>
+        <v>6764235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>35. 2 bilder, på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129293569</v>
+        <v>129271386</v>
       </c>
       <c r="B5" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492107</v>
+        <v>492097</v>
       </c>
       <c r="R5" t="n">
-        <v>6764235</v>
+        <v>6764207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>35. 2 bilder, på granlåga</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129271992</v>
+        <v>129270999</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,34 +1134,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492111</v>
+        <v>492105</v>
       </c>
       <c r="R6" t="n">
-        <v>6764274</v>
+        <v>6764156</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,6 +1209,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,50 +1240,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129270999</v>
+        <v>129294088</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492105</v>
+        <v>491988</v>
       </c>
       <c r="R7" t="n">
-        <v>6764156</v>
+        <v>6764293</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,27 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129294088</v>
+        <v>129271992</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491988</v>
+        <v>492111</v>
       </c>
       <c r="R8" t="n">
-        <v>6764293</v>
+        <v>6764274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,22 +1412,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,7 +1457,7 @@
         <v>129290261</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>129287686</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129291402</v>
+        <v>129293927</v>
       </c>
       <c r="B11" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,21 +1689,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R11" t="n">
-        <v>6764244</v>
+        <v>6764269</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129293927</v>
+        <v>129294029</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,34 +1801,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491997</v>
+        <v>492007</v>
       </c>
       <c r="R12" t="n">
-        <v>6764269</v>
+        <v>6764289</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1871,11 +1876,6 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129294029</v>
+        <v>129291402</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>91545</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,42 +1913,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492007</v>
+        <v>492107</v>
       </c>
       <c r="R13" t="n">
-        <v>6764289</v>
+        <v>6764244</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1982,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,7 +2017,7 @@
         <v>129287945</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129296076</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>129293376</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>129294004</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         <v>129293473</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>129290547</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>129293152</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>129294219</v>
       </c>
       <c r="B23" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>129273280</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>129294699</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3572,10 +3572,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129294905</v>
+        <v>129290087</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492048</v>
+        <v>492083</v>
       </c>
       <c r="R28" t="n">
-        <v>6764380</v>
+        <v>6764418</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3652,12 +3652,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3684,10 +3679,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129294335</v>
+        <v>129294905</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3719,10 +3714,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491922</v>
+        <v>492048</v>
       </c>
       <c r="R29" t="n">
-        <v>6764336</v>
+        <v>6764380</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3765,6 +3760,11 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3791,10 +3791,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129290087</v>
+        <v>129294335</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492083</v>
+        <v>491922</v>
       </c>
       <c r="R30" t="n">
-        <v>6764418</v>
+        <v>6764336</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3901,7 +3901,7 @@
         <v>129295250</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>129289310</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>129289434</v>
       </c>
       <c r="B34" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>129295876</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>129294091</v>
       </c>
       <c r="B36" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129294065</v>
+        <v>129293510</v>
       </c>
       <c r="B37" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491997</v>
+        <v>492107</v>
       </c>
       <c r="R37" t="n">
-        <v>6764302</v>
+        <v>6764244</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4651,11 +4651,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4682,10 +4677,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294432</v>
+        <v>129294065</v>
       </c>
       <c r="B38" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4717,13 +4712,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491957</v>
+        <v>491997</v>
       </c>
       <c r="R38" t="n">
-        <v>6764346</v>
+        <v>6764302</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4767,7 +4762,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>44. 2 bilder, granlåga</t>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4794,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129293510</v>
+        <v>129294432</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>91545</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4805,21 +4800,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4829,13 +4824,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492107</v>
+        <v>491957</v>
       </c>
       <c r="R39" t="n">
-        <v>6764244</v>
+        <v>6764346</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4875,6 +4870,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,10 +4901,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129293401</v>
+        <v>129290779</v>
       </c>
       <c r="B40" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4912,42 +4912,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492123</v>
+        <v>492030</v>
       </c>
       <c r="R40" t="n">
-        <v>6764202</v>
+        <v>6764279</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4976,7 +4971,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4986,12 +4981,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5018,10 +5013,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129295996</v>
+        <v>129293719</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5029,39 +5024,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R41" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5104,11 +5094,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5135,7 +5120,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129289411</v>
+        <v>129293401</v>
       </c>
       <c r="B42" t="n">
         <v>57724</v>
@@ -5175,13 +5160,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492157</v>
+        <v>492123</v>
       </c>
       <c r="R42" t="n">
-        <v>6764400</v>
+        <v>6764202</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5210,7 +5195,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5220,12 +5205,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5252,45 +5237,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129293744</v>
+        <v>129295996</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492059</v>
+        <v>492085</v>
       </c>
       <c r="R43" t="n">
-        <v>6764244</v>
+        <v>6764296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5333,6 +5323,11 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5359,48 +5354,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129289685</v>
+        <v>129289411</v>
       </c>
       <c r="B44" t="n">
-        <v>97581</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492160</v>
+        <v>492157</v>
       </c>
       <c r="R44" t="n">
-        <v>6764361</v>
+        <v>6764400</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5471,32 +5471,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129290779</v>
+        <v>129293744</v>
       </c>
       <c r="B45" t="n">
-        <v>79043</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492030</v>
+        <v>492059</v>
       </c>
       <c r="R45" t="n">
-        <v>6764279</v>
+        <v>6764244</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5551,12 +5551,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5583,32 +5578,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129293719</v>
+        <v>129289685</v>
       </c>
       <c r="B46" t="n">
-        <v>79043</v>
+        <v>97583</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5618,10 +5613,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492059</v>
+        <v>492160</v>
       </c>
       <c r="R46" t="n">
-        <v>6764244</v>
+        <v>6764361</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5653,7 +5648,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5663,7 +5658,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5693,7 +5693,7 @@
         <v>129293571</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>129294362</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6029,10 +6029,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129296258</v>
+        <v>129290171</v>
       </c>
       <c r="B50" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,21 +6040,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492091</v>
+        <v>492061</v>
       </c>
       <c r="R50" t="n">
-        <v>6764217</v>
+        <v>6764382</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6136,10 +6136,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129274938</v>
+        <v>129296258</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,39 +6147,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492048</v>
+        <v>492091</v>
       </c>
       <c r="R51" t="n">
-        <v>6764380</v>
+        <v>6764217</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6206,27 +6201,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>I bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6253,10 +6243,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129290171</v>
+        <v>129274938</v>
       </c>
       <c r="B52" t="n">
-        <v>79662</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6264,34 +6254,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492061</v>
+        <v>492048</v>
       </c>
       <c r="R52" t="n">
-        <v>6764382</v>
+        <v>6764380</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6318,22 +6313,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>I bild</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6475,7 +6475,7 @@
         <v>129293814</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>129286796</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>129282927</v>
       </c>
       <c r="B56" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>129283290</v>
       </c>
       <c r="B58" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7040,7 +7040,7 @@
         <v>129287728</v>
       </c>
       <c r="B59" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>129283635</v>
       </c>
       <c r="B60" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129290345</v>
+        <v>129293569</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>91549</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492050</v>
+        <v>492107</v>
       </c>
       <c r="R3" t="n">
-        <v>6764358</v>
+        <v>6764235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>35. 2 bilder, på granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129293569</v>
+        <v>129271386</v>
       </c>
       <c r="B4" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492107</v>
+        <v>492097</v>
       </c>
       <c r="R4" t="n">
-        <v>6764235</v>
+        <v>6764207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,27 +959,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>35. 2 bilder, på granlåga</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129271386</v>
+        <v>129290345</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,34 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492097</v>
+        <v>492050</v>
       </c>
       <c r="R5" t="n">
-        <v>6764207</v>
+        <v>6764358</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129270999</v>
+        <v>129271992</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,39 +1134,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492105</v>
+        <v>492111</v>
       </c>
       <c r="R6" t="n">
-        <v>6764156</v>
+        <v>6764274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,11 +1204,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,45 +1230,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129294088</v>
+        <v>129270999</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491988</v>
+        <v>492105</v>
       </c>
       <c r="R7" t="n">
-        <v>6764293</v>
+        <v>6764156</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,22 +1300,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129271992</v>
+        <v>129294088</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492111</v>
+        <v>491988</v>
       </c>
       <c r="R8" t="n">
-        <v>6764274</v>
+        <v>6764293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,22 +1412,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129293927</v>
+        <v>129291402</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,21 +1689,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,13 +1713,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491997</v>
+        <v>492107</v>
       </c>
       <c r="R11" t="n">
-        <v>6764269</v>
+        <v>6764244</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,12 +1758,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129294029</v>
+        <v>129293927</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,39 +1801,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492007</v>
+        <v>491997</v>
       </c>
       <c r="R12" t="n">
-        <v>6764289</v>
+        <v>6764269</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1876,6 +1871,11 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129291402</v>
+        <v>129294029</v>
       </c>
       <c r="B13" t="n">
-        <v>91545</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,37 +1913,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492107</v>
+        <v>492007</v>
       </c>
       <c r="R13" t="n">
-        <v>6764244</v>
+        <v>6764289</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,12 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129294219</v>
+        <v>129274016</v>
       </c>
       <c r="B23" t="n">
-        <v>91843</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,34 +3018,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491922</v>
+        <v>492092</v>
       </c>
       <c r="R23" t="n">
-        <v>6764336</v>
+        <v>6764410</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3072,27 +3077,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>39. 2 bild</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,48 +3124,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129273280</v>
+        <v>129290672</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492172</v>
+        <v>492030</v>
       </c>
       <c r="R24" t="n">
-        <v>6764333</v>
+        <v>6764294</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3184,27 +3194,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,10 +3236,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129294699</v>
+        <v>129294219</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>91847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,21 +3247,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3266,13 +3271,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491988</v>
+        <v>491922</v>
       </c>
       <c r="R25" t="n">
-        <v>6764346</v>
+        <v>6764336</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3316,7 +3321,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3343,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129274016</v>
+        <v>129273280</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,39 +3359,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492092</v>
+        <v>492172</v>
       </c>
       <c r="R26" t="n">
-        <v>6764410</v>
+        <v>6764333</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,50 +3460,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129290672</v>
+        <v>129294699</v>
       </c>
       <c r="B27" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492030</v>
+        <v>491988</v>
       </c>
       <c r="R27" t="n">
-        <v>6764294</v>
+        <v>6764346</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3535,7 +3530,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3545,7 +3540,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,7 +3572,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129290087</v>
+        <v>129294905</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492083</v>
+        <v>492048</v>
       </c>
       <c r="R28" t="n">
-        <v>6764418</v>
+        <v>6764380</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3652,7 +3652,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3679,7 +3684,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129294905</v>
+        <v>129294335</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3714,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492048</v>
+        <v>491922</v>
       </c>
       <c r="R29" t="n">
-        <v>6764380</v>
+        <v>6764336</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3760,11 +3765,6 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3791,7 +3791,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129294335</v>
+        <v>129290087</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491922</v>
+        <v>492083</v>
       </c>
       <c r="R30" t="n">
-        <v>6764336</v>
+        <v>6764418</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129289434</v>
+        <v>129295876</v>
       </c>
       <c r="B34" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492159</v>
+        <v>492080</v>
       </c>
       <c r="R34" t="n">
-        <v>6764383</v>
+        <v>6764357</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>16. 2 bild</t>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,7 +4351,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129295876</v>
+        <v>129294091</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492080</v>
+        <v>491988</v>
       </c>
       <c r="R35" t="n">
-        <v>6764357</v>
+        <v>6764293</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4432,11 +4432,6 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4463,10 +4458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129294091</v>
+        <v>129289434</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,21 +4469,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491988</v>
+        <v>492159</v>
       </c>
       <c r="R36" t="n">
-        <v>6764293</v>
+        <v>6764383</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4533,7 +4528,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4543,7 +4538,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129293510</v>
+        <v>129294065</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R37" t="n">
-        <v>6764244</v>
+        <v>6764302</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4651,6 +4651,11 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4677,10 +4682,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294065</v>
+        <v>129294432</v>
       </c>
       <c r="B38" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4712,13 +4717,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491997</v>
+        <v>491957</v>
       </c>
       <c r="R38" t="n">
-        <v>6764302</v>
+        <v>6764346</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4762,7 +4767,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>38. 1 bild, granlåga</t>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4789,10 +4794,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129294432</v>
+        <v>129293510</v>
       </c>
       <c r="B39" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,21 +4805,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4824,13 +4829,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491957</v>
+        <v>492107</v>
       </c>
       <c r="R39" t="n">
-        <v>6764346</v>
+        <v>6764244</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4870,11 +4875,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5120,50 +5120,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129293401</v>
+        <v>129289685</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>97587</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492123</v>
+        <v>492160</v>
       </c>
       <c r="R42" t="n">
-        <v>6764202</v>
+        <v>6764361</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5195,7 +5190,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5205,12 +5200,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5237,50 +5232,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129295996</v>
+        <v>129293744</v>
       </c>
       <c r="B43" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R43" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5323,11 +5313,6 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5354,7 +5339,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129289411</v>
+        <v>129293401</v>
       </c>
       <c r="B44" t="n">
         <v>57724</v>
@@ -5394,13 +5379,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492157</v>
+        <v>492123</v>
       </c>
       <c r="R44" t="n">
-        <v>6764400</v>
+        <v>6764202</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5429,7 +5414,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5439,12 +5424,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5471,45 +5456,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129293744</v>
+        <v>129295996</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492059</v>
+        <v>492085</v>
       </c>
       <c r="R45" t="n">
-        <v>6764244</v>
+        <v>6764296</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5552,6 +5542,11 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5578,48 +5573,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289685</v>
+        <v>129289411</v>
       </c>
       <c r="B46" t="n">
-        <v>97583</v>
+        <v>57724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492160</v>
+        <v>492157</v>
       </c>
       <c r="R46" t="n">
-        <v>6764361</v>
+        <v>6764400</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129293569</v>
+        <v>129271386</v>
       </c>
       <c r="B3" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492107</v>
+        <v>492097</v>
       </c>
       <c r="R3" t="n">
-        <v>6764235</v>
+        <v>6764207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,27 +847,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>35. 2 bilder, på granlåga</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129271386</v>
+        <v>129293569</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492097</v>
+        <v>492107</v>
       </c>
       <c r="R4" t="n">
-        <v>6764207</v>
+        <v>6764235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,27 +959,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>35. 2 bilder, på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1123,32 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129271992</v>
+        <v>129294088</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492111</v>
+        <v>491988</v>
       </c>
       <c r="R6" t="n">
-        <v>6764274</v>
+        <v>6764293</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,22 +1188,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129270999</v>
+        <v>129271992</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,39 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492105</v>
+        <v>492111</v>
       </c>
       <c r="R7" t="n">
-        <v>6764156</v>
+        <v>6764274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,11 +1311,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,45 +1337,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129294088</v>
+        <v>129270999</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491988</v>
+        <v>492105</v>
       </c>
       <c r="R8" t="n">
-        <v>6764293</v>
+        <v>6764156</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,22 +1407,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1681,7 +1681,7 @@
         <v>129291402</v>
       </c>
       <c r="B11" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129274016</v>
+        <v>129294219</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,39 +3018,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492092</v>
+        <v>491922</v>
       </c>
       <c r="R23" t="n">
-        <v>6764410</v>
+        <v>6764336</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3077,27 +3072,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3124,27 +3119,27 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129290672</v>
+        <v>129274016</v>
       </c>
       <c r="B24" t="n">
-        <v>58097</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3155,7 +3150,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3164,13 +3159,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492030</v>
+        <v>492092</v>
       </c>
       <c r="R24" t="n">
-        <v>6764294</v>
+        <v>6764410</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3194,22 +3189,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3236,10 +3236,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129294219</v>
+        <v>129273280</v>
       </c>
       <c r="B25" t="n">
-        <v>91847</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3247,21 +3247,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491922</v>
+        <v>492172</v>
       </c>
       <c r="R25" t="n">
-        <v>6764336</v>
+        <v>6764333</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3301,27 +3301,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>39. 2 bild</t>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,7 +3348,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129273280</v>
+        <v>129294699</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3383,13 +3383,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492172</v>
+        <v>491988</v>
       </c>
       <c r="R26" t="n">
-        <v>6764333</v>
+        <v>6764346</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3413,27 +3413,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,45 +3460,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129294699</v>
+        <v>129290672</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491988</v>
+        <v>492030</v>
       </c>
       <c r="R27" t="n">
-        <v>6764346</v>
+        <v>6764294</v>
       </c>
       <c r="S27" t="n">
         <v>50</v>
@@ -3530,7 +3535,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3540,12 +3545,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129295876</v>
+        <v>129289434</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492080</v>
+        <v>492159</v>
       </c>
       <c r="R34" t="n">
-        <v>6764357</v>
+        <v>6764383</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>55. 1 bild hängande på gren</t>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,7 +4351,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129294091</v>
+        <v>129295876</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491988</v>
+        <v>492080</v>
       </c>
       <c r="R35" t="n">
-        <v>6764293</v>
+        <v>6764357</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4432,6 +4432,11 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4458,10 +4463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129289434</v>
+        <v>129294091</v>
       </c>
       <c r="B36" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4469,21 +4474,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492159</v>
+        <v>491988</v>
       </c>
       <c r="R36" t="n">
-        <v>6764383</v>
+        <v>6764293</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4533,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4538,12 +4543,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>16. 2 bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4573,7 +4573,7 @@
         <v>129294065</v>
       </c>
       <c r="B37" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>129294432</v>
       </c>
       <c r="B38" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4901,32 +4901,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129290779</v>
+        <v>129293744</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4936,13 +4936,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492030</v>
+        <v>492059</v>
       </c>
       <c r="R40" t="n">
-        <v>6764279</v>
+        <v>6764244</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4981,12 +4981,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5013,32 +5008,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129293719</v>
+        <v>129289685</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>97595</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5048,10 +5043,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492059</v>
+        <v>492160</v>
       </c>
       <c r="R41" t="n">
-        <v>6764244</v>
+        <v>6764361</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5083,7 +5078,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5093,7 +5088,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,32 +5120,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129289685</v>
+        <v>129290779</v>
       </c>
       <c r="B42" t="n">
-        <v>97587</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5155,13 +5155,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492160</v>
+        <v>492030</v>
       </c>
       <c r="R42" t="n">
-        <v>6764361</v>
+        <v>6764279</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5232,32 +5232,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129293744</v>
+        <v>129293719</v>
       </c>
       <c r="B43" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129271386</v>
+        <v>129293569</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492097</v>
+        <v>492107</v>
       </c>
       <c r="R3" t="n">
-        <v>6764207</v>
+        <v>6764235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,27 +847,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>35. 2 bilder, på granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129293569</v>
+        <v>129290345</v>
       </c>
       <c r="B4" t="n">
-        <v>91550</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492107</v>
+        <v>492050</v>
       </c>
       <c r="R4" t="n">
-        <v>6764235</v>
+        <v>6764358</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,12 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>35. 2 bilder, på granlåga</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129290345</v>
+        <v>129271386</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,39 +1022,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492050</v>
+        <v>492097</v>
       </c>
       <c r="R5" t="n">
-        <v>6764358</v>
+        <v>6764207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,32 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129294088</v>
+        <v>129271992</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491988</v>
+        <v>492111</v>
       </c>
       <c r="R6" t="n">
-        <v>6764293</v>
+        <v>6764274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,22 +1188,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129271992</v>
+        <v>129270999</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,34 +1241,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492111</v>
+        <v>492105</v>
       </c>
       <c r="R7" t="n">
-        <v>6764274</v>
+        <v>6764156</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,6 +1316,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,50 +1347,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129270999</v>
+        <v>129294088</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492105</v>
+        <v>491988</v>
       </c>
       <c r="R8" t="n">
-        <v>6764156</v>
+        <v>6764293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,27 +1412,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129291402</v>
+        <v>129294029</v>
       </c>
       <c r="B11" t="n">
-        <v>91550</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,37 +1689,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492107</v>
+        <v>492007</v>
       </c>
       <c r="R11" t="n">
-        <v>6764244</v>
+        <v>6764289</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,12 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129294029</v>
+        <v>129291402</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>91550</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,42 +1913,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492007</v>
+        <v>492107</v>
       </c>
       <c r="R13" t="n">
-        <v>6764289</v>
+        <v>6764244</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1982,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,7 +2014,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129287945</v>
+        <v>129296076</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492218</v>
+        <v>492085</v>
       </c>
       <c r="R14" t="n">
-        <v>6764381</v>
+        <v>6764296</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,12 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>13. 2 bilder, tallstammar Rikligt till måttligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129296076</v>
+        <v>129287945</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2161,13 +2156,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492085</v>
+        <v>492218</v>
       </c>
       <c r="R15" t="n">
-        <v>6764296</v>
+        <v>6764381</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2196,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2206,7 +2201,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>13. 2 bilder, tallstammar Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2671,10 +2671,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129293152</v>
+        <v>129271179</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2682,34 +2682,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492125</v>
+        <v>492113</v>
       </c>
       <c r="R20" t="n">
-        <v>6764158</v>
+        <v>6764152</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2736,22 +2741,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2778,10 +2788,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129294398</v>
+        <v>129293152</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,42 +2799,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491957</v>
+        <v>492125</v>
       </c>
       <c r="R21" t="n">
-        <v>6764346</v>
+        <v>6764158</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2890,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129271179</v>
+        <v>129294398</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2901,16 +2906,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2921,7 +2926,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2930,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492113</v>
+        <v>491957</v>
       </c>
       <c r="R22" t="n">
-        <v>6764152</v>
+        <v>6764346</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2960,27 +2965,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129294219</v>
+        <v>129294699</v>
       </c>
       <c r="B23" t="n">
-        <v>91848</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3042,13 +3042,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491922</v>
+        <v>491988</v>
       </c>
       <c r="R23" t="n">
-        <v>6764336</v>
+        <v>6764346</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>39. 2 bild</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129274016</v>
+        <v>129273280</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,39 +3130,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492092</v>
+        <v>492172</v>
       </c>
       <c r="R24" t="n">
-        <v>6764410</v>
+        <v>6764333</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3209,7 +3204,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3236,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129273280</v>
+        <v>129274016</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3247,34 +3242,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492172</v>
+        <v>492092</v>
       </c>
       <c r="R25" t="n">
-        <v>6764333</v>
+        <v>6764410</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,45 +3348,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129294699</v>
+        <v>129290672</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491988</v>
+        <v>492030</v>
       </c>
       <c r="R26" t="n">
-        <v>6764346</v>
+        <v>6764294</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3418,7 +3423,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3428,12 +3433,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,53 +3460,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129290672</v>
+        <v>129294219</v>
       </c>
       <c r="B27" t="n">
-        <v>58097</v>
+        <v>91848</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492030</v>
+        <v>491922</v>
       </c>
       <c r="R27" t="n">
-        <v>6764294</v>
+        <v>6764336</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3535,7 +3530,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3545,7 +3540,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,7 +3572,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129294905</v>
+        <v>129294335</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492048</v>
+        <v>491922</v>
       </c>
       <c r="R28" t="n">
-        <v>6764380</v>
+        <v>6764336</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3653,11 +3653,6 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3684,7 +3679,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129294335</v>
+        <v>129290087</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3719,10 +3714,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491922</v>
+        <v>492083</v>
       </c>
       <c r="R29" t="n">
-        <v>6764336</v>
+        <v>6764418</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3754,7 +3749,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3764,7 +3759,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3791,7 +3786,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129290087</v>
+        <v>129294905</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3826,10 +3821,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492083</v>
+        <v>492048</v>
       </c>
       <c r="R30" t="n">
-        <v>6764418</v>
+        <v>6764380</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3861,7 +3856,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3871,7 +3866,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129289434</v>
+        <v>129294091</v>
       </c>
       <c r="B34" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492159</v>
+        <v>491988</v>
       </c>
       <c r="R34" t="n">
-        <v>6764383</v>
+        <v>6764293</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,12 +4319,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>16. 2 bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4463,10 +4458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129294091</v>
+        <v>129289434</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,21 +4469,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491988</v>
+        <v>492159</v>
       </c>
       <c r="R36" t="n">
-        <v>6764293</v>
+        <v>6764383</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4533,7 +4528,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4543,7 +4538,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4901,32 +4901,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129293744</v>
+        <v>129293719</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5008,32 +5008,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129289685</v>
+        <v>129290779</v>
       </c>
       <c r="B41" t="n">
-        <v>97595</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5043,13 +5043,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492160</v>
+        <v>492030</v>
       </c>
       <c r="R41" t="n">
-        <v>6764361</v>
+        <v>6764279</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,10 +5120,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129290779</v>
+        <v>129293401</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5131,37 +5131,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492030</v>
+        <v>492123</v>
       </c>
       <c r="R42" t="n">
-        <v>6764279</v>
+        <v>6764202</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5190,7 +5195,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5200,12 +5205,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5232,10 +5237,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129293719</v>
+        <v>129295996</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5243,34 +5248,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492059</v>
+        <v>492085</v>
       </c>
       <c r="R43" t="n">
-        <v>6764244</v>
+        <v>6764296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5313,6 +5323,11 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5339,7 +5354,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293401</v>
+        <v>129289411</v>
       </c>
       <c r="B44" t="n">
         <v>57724</v>
@@ -5379,13 +5394,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492123</v>
+        <v>492157</v>
       </c>
       <c r="R44" t="n">
-        <v>6764202</v>
+        <v>6764400</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5414,7 +5429,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5424,12 +5439,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,50 +5471,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129295996</v>
+        <v>129293744</v>
       </c>
       <c r="B45" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R45" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5542,11 +5552,6 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5573,53 +5578,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289411</v>
+        <v>129289685</v>
       </c>
       <c r="B46" t="n">
-        <v>57724</v>
+        <v>97595</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492157</v>
+        <v>492160</v>
       </c>
       <c r="R46" t="n">
-        <v>6764400</v>
+        <v>6764361</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5917,10 +5917,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129294362</v>
+        <v>129274938</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5928,37 +5928,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491956</v>
+        <v>492048</v>
       </c>
       <c r="R49" t="n">
-        <v>6764334</v>
+        <v>6764380</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5982,27 +5987,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
+          <t>I bild</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6029,10 +6034,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129290171</v>
+        <v>129294362</v>
       </c>
       <c r="B50" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,21 +6045,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6064,13 +6069,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492061</v>
+        <v>491956</v>
       </c>
       <c r="R50" t="n">
-        <v>6764382</v>
+        <v>6764334</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6099,7 +6104,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6109,7 +6114,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6243,10 +6253,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129274938</v>
+        <v>129290171</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>79663</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6254,39 +6264,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492048</v>
+        <v>492061</v>
       </c>
       <c r="R52" t="n">
-        <v>6764380</v>
+        <v>6764382</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6313,27 +6318,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>I bild</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6584,7 +6584,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129286796</v>
+        <v>129282927</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492169</v>
+        <v>492097</v>
       </c>
       <c r="R55" t="n">
-        <v>6764315</v>
+        <v>6764193</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
+          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6696,7 +6696,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129282927</v>
+        <v>129286796</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492097</v>
+        <v>492169</v>
       </c>
       <c r="R56" t="n">
-        <v>6764193</v>
+        <v>6764315</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
+          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7037,10 +7037,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129287728</v>
+        <v>129283043</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7048,34 +7048,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492227</v>
+        <v>492082</v>
       </c>
       <c r="R59" t="n">
-        <v>6764369</v>
+        <v>6764210</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7107,7 +7112,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7117,12 +7122,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>12. 1 Bild på kolarkoja</t>
+          <t>3. 1 bild</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7261,10 +7266,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129283043</v>
+        <v>129287728</v>
       </c>
       <c r="B61" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7272,39 +7277,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492082</v>
+        <v>492227</v>
       </c>
       <c r="R61" t="n">
-        <v>6764210</v>
+        <v>6764369</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>3. 1 bild</t>
+          <t>12. 1 Bild på kolarkoja</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129293473</v>
+        <v>129294398</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,37 +2463,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492120</v>
+        <v>491957</v>
       </c>
       <c r="R18" t="n">
-        <v>6764224</v>
+        <v>6764346</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2559,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129290547</v>
+        <v>129271179</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,37 +2575,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492071</v>
+        <v>492113</v>
       </c>
       <c r="R19" t="n">
-        <v>6764318</v>
+        <v>6764152</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2624,27 +2634,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,10 +2681,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129271179</v>
+        <v>129293152</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2682,39 +2692,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492113</v>
+        <v>492125</v>
       </c>
       <c r="R20" t="n">
-        <v>6764152</v>
+        <v>6764158</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2741,27 +2746,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2788,7 +2788,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129293152</v>
+        <v>129293473</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2823,10 +2823,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492125</v>
+        <v>492120</v>
       </c>
       <c r="R21" t="n">
-        <v>6764158</v>
+        <v>6764224</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129294398</v>
+        <v>129290547</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,39 +2906,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491957</v>
+        <v>492071</v>
       </c>
       <c r="R22" t="n">
-        <v>6764346</v>
+        <v>6764318</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2970,7 +2965,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2980,7 +2975,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129294699</v>
+        <v>129294219</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>91848</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3042,13 +3042,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491988</v>
+        <v>491922</v>
       </c>
       <c r="R23" t="n">
-        <v>6764346</v>
+        <v>6764336</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,7 +3119,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129273280</v>
+        <v>129294699</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492172</v>
+        <v>491988</v>
       </c>
       <c r="R24" t="n">
-        <v>6764333</v>
+        <v>6764346</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3184,27 +3184,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129274016</v>
+        <v>129273280</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,39 +3242,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492092</v>
+        <v>492172</v>
       </c>
       <c r="R25" t="n">
-        <v>6764410</v>
+        <v>6764333</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3321,7 +3316,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,27 +3343,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129290672</v>
+        <v>129274016</v>
       </c>
       <c r="B26" t="n">
-        <v>58097</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3379,7 +3374,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3388,13 +3383,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492030</v>
+        <v>492092</v>
       </c>
       <c r="R26" t="n">
-        <v>6764294</v>
+        <v>6764410</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3418,22 +3413,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,48 +3460,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129294219</v>
+        <v>129290672</v>
       </c>
       <c r="B27" t="n">
-        <v>91848</v>
+        <v>58097</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491922</v>
+        <v>492030</v>
       </c>
       <c r="R27" t="n">
-        <v>6764336</v>
+        <v>6764294</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3530,7 +3535,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3540,12 +3545,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>39. 2 bild</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129293571</v>
+        <v>129274000</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,34 +5701,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492107</v>
+        <v>492089</v>
       </c>
       <c r="R47" t="n">
-        <v>6764235</v>
+        <v>6764397</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5755,22 +5763,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 bild samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5797,10 +5810,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129274000</v>
+        <v>129293571</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5808,42 +5821,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492089</v>
+        <v>492107</v>
       </c>
       <c r="R48" t="n">
-        <v>6764397</v>
+        <v>6764235</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5870,27 +5875,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 bild samt miljöbilder för området</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129293569</v>
+        <v>129290345</v>
       </c>
       <c r="B3" t="n">
-        <v>91550</v>
+        <v>57724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492107</v>
+        <v>492050</v>
       </c>
       <c r="R3" t="n">
-        <v>6764235</v>
+        <v>6764358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>35. 2 bilder, på granlåga</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129290345</v>
+        <v>129271386</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492050</v>
+        <v>492097</v>
       </c>
       <c r="R4" t="n">
-        <v>6764358</v>
+        <v>6764207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,27 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129271386</v>
+        <v>129293569</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492097</v>
+        <v>492107</v>
       </c>
       <c r="R5" t="n">
-        <v>6764207</v>
+        <v>6764235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>35. 2 bilder, på granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129271992</v>
+        <v>129270999</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,34 +1134,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492111</v>
+        <v>492105</v>
       </c>
       <c r="R6" t="n">
-        <v>6764274</v>
+        <v>6764156</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,6 +1209,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129270999</v>
+        <v>129271992</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,39 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492105</v>
+        <v>492111</v>
       </c>
       <c r="R7" t="n">
-        <v>6764156</v>
+        <v>6764274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,11 +1321,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129293927</v>
+        <v>129291402</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,13 +1825,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491997</v>
+        <v>492107</v>
       </c>
       <c r="R12" t="n">
-        <v>6764269</v>
+        <v>6764244</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129291402</v>
+        <v>129293927</v>
       </c>
       <c r="B13" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,21 +1913,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R13" t="n">
-        <v>6764244</v>
+        <v>6764269</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,7 +2014,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129296076</v>
+        <v>129287945</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492085</v>
+        <v>492218</v>
       </c>
       <c r="R14" t="n">
-        <v>6764296</v>
+        <v>6764381</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2094,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>13. 2 bilder, tallstammar Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,7 +2126,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129287945</v>
+        <v>129296076</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2156,13 +2161,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492218</v>
+        <v>492085</v>
       </c>
       <c r="R15" t="n">
-        <v>6764381</v>
+        <v>6764296</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2191,7 +2196,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,12 +2206,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>13. 2 bilder, tallstammar Rikligt till måttligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129294398</v>
+        <v>129293473</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,42 +2463,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491957</v>
+        <v>492120</v>
       </c>
       <c r="R18" t="n">
-        <v>6764346</v>
+        <v>6764224</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2564,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129271179</v>
+        <v>129290547</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2575,42 +2570,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492113</v>
+        <v>492071</v>
       </c>
       <c r="R19" t="n">
-        <v>6764152</v>
+        <v>6764318</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2634,27 +2624,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2788,10 +2778,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129293473</v>
+        <v>129271179</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,34 +2789,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492120</v>
+        <v>492113</v>
       </c>
       <c r="R21" t="n">
-        <v>6764224</v>
+        <v>6764152</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2853,22 +2848,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129290547</v>
+        <v>129294398</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,34 +2906,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492071</v>
+        <v>491957</v>
       </c>
       <c r="R22" t="n">
-        <v>6764318</v>
+        <v>6764346</v>
       </c>
       <c r="S22" t="n">
         <v>50</v>
@@ -2965,7 +2970,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2975,12 +2980,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,10 +3007,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129294219</v>
+        <v>129273280</v>
       </c>
       <c r="B23" t="n">
-        <v>91848</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3018,21 +3018,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3042,10 +3042,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491922</v>
+        <v>492172</v>
       </c>
       <c r="R23" t="n">
-        <v>6764336</v>
+        <v>6764333</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3072,27 +3072,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>39. 2 bild</t>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3231,48 +3231,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129273280</v>
+        <v>129290672</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492172</v>
+        <v>492030</v>
       </c>
       <c r="R25" t="n">
-        <v>6764333</v>
+        <v>6764294</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3296,27 +3301,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3343,10 +3343,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129274016</v>
+        <v>129294219</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,39 +3354,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492092</v>
+        <v>491922</v>
       </c>
       <c r="R26" t="n">
-        <v>6764410</v>
+        <v>6764336</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3413,27 +3408,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,27 +3455,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129290672</v>
+        <v>129274016</v>
       </c>
       <c r="B27" t="n">
-        <v>58097</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3491,7 +3486,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3500,13 +3495,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492030</v>
+        <v>492092</v>
       </c>
       <c r="R27" t="n">
-        <v>6764294</v>
+        <v>6764410</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3530,22 +3525,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,7 +3572,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129294335</v>
+        <v>129294905</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491922</v>
+        <v>492048</v>
       </c>
       <c r="R28" t="n">
-        <v>6764336</v>
+        <v>6764380</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3653,6 +3653,11 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3679,7 +3684,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129290087</v>
+        <v>129294335</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3714,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492083</v>
+        <v>491922</v>
       </c>
       <c r="R29" t="n">
-        <v>6764418</v>
+        <v>6764336</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3749,7 +3754,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3759,7 +3764,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3786,7 +3791,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129294905</v>
+        <v>129290087</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3821,10 +3826,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492048</v>
+        <v>492083</v>
       </c>
       <c r="R30" t="n">
-        <v>6764380</v>
+        <v>6764418</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3856,7 +3861,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3866,12 +3871,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129289310</v>
+        <v>129294510</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4021,37 +4021,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492177</v>
+        <v>491975</v>
       </c>
       <c r="R32" t="n">
-        <v>6764418</v>
+        <v>6764342</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4080,7 +4085,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4090,12 +4095,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
+          <t>45. 3 bilder, miljöbilder</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4122,10 +4127,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129294510</v>
+        <v>129289310</v>
       </c>
       <c r="B33" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4133,42 +4138,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491975</v>
+        <v>492177</v>
       </c>
       <c r="R33" t="n">
-        <v>6764342</v>
+        <v>6764418</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>45. 3 bilder, miljöbilder</t>
+          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129294091</v>
+        <v>129289434</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491988</v>
+        <v>492159</v>
       </c>
       <c r="R34" t="n">
-        <v>6764293</v>
+        <v>6764383</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,7 +4319,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4458,10 +4463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129289434</v>
+        <v>129294091</v>
       </c>
       <c r="B36" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4469,21 +4474,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492159</v>
+        <v>491988</v>
       </c>
       <c r="R36" t="n">
-        <v>6764383</v>
+        <v>6764293</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4533,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4538,12 +4543,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>16. 2 bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4573,7 +4573,7 @@
         <v>129294065</v>
       </c>
       <c r="B37" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>129294432</v>
       </c>
       <c r="B38" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4901,10 +4901,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129293719</v>
+        <v>129293401</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4912,34 +4912,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492059</v>
+        <v>492123</v>
       </c>
       <c r="R40" t="n">
-        <v>6764244</v>
+        <v>6764202</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4982,6 +4987,11 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5008,10 +5018,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129290779</v>
+        <v>129295996</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5019,37 +5029,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492030</v>
+        <v>492085</v>
       </c>
       <c r="R41" t="n">
-        <v>6764279</v>
+        <v>6764296</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5078,7 +5093,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5088,12 +5103,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,7 +5135,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129293401</v>
+        <v>129289411</v>
       </c>
       <c r="B42" t="n">
         <v>57724</v>
@@ -5160,13 +5175,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492123</v>
+        <v>492157</v>
       </c>
       <c r="R42" t="n">
-        <v>6764202</v>
+        <v>6764400</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5195,7 +5210,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5205,12 +5220,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5237,10 +5252,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129295996</v>
+        <v>129290779</v>
       </c>
       <c r="B43" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5248,42 +5263,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492085</v>
+        <v>492030</v>
       </c>
       <c r="R43" t="n">
-        <v>6764296</v>
+        <v>6764279</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5312,7 +5322,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5322,12 +5332,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>56. 2 bilder, även svamp på gran</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5354,10 +5364,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129289411</v>
+        <v>129293719</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5365,42 +5375,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492157</v>
+        <v>492059</v>
       </c>
       <c r="R44" t="n">
-        <v>6764400</v>
+        <v>6764244</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5429,7 +5434,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5439,12 +5444,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>15. 1 bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5581,7 +5581,7 @@
         <v>129289685</v>
       </c>
       <c r="B46" t="n">
-        <v>97595</v>
+        <v>97598</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5690,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129274000</v>
+        <v>129293571</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,42 +5701,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492089</v>
+        <v>492107</v>
       </c>
       <c r="R47" t="n">
-        <v>6764397</v>
+        <v>6764235</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5763,27 +5755,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>1 bild samt miljöbilder för området</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5810,10 +5797,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129293571</v>
+        <v>129274000</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5821,34 +5808,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492107</v>
+        <v>492089</v>
       </c>
       <c r="R48" t="n">
-        <v>6764235</v>
+        <v>6764397</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5875,22 +5870,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 bild samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6146,10 +6146,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129296258</v>
+        <v>129290171</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6157,21 +6157,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6181,10 +6181,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492091</v>
+        <v>492061</v>
       </c>
       <c r="R51" t="n">
-        <v>6764217</v>
+        <v>6764382</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6253,10 +6253,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129290171</v>
+        <v>129296258</v>
       </c>
       <c r="B52" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6264,21 +6264,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492061</v>
+        <v>492091</v>
       </c>
       <c r="R52" t="n">
-        <v>6764382</v>
+        <v>6764217</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6584,7 +6584,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129282927</v>
+        <v>129286796</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492097</v>
+        <v>492169</v>
       </c>
       <c r="R55" t="n">
-        <v>6764193</v>
+        <v>6764315</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
+          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6696,7 +6696,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129286796</v>
+        <v>129282927</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492169</v>
+        <v>492097</v>
       </c>
       <c r="R56" t="n">
-        <v>6764315</v>
+        <v>6764193</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
+          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7154,7 +7154,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129283635</v>
+        <v>129287728</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -7189,13 +7189,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492082</v>
+        <v>492227</v>
       </c>
       <c r="R60" t="n">
-        <v>6764245</v>
+        <v>6764369</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
+          <t>12. 1 Bild på kolarkoja</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7266,7 +7266,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129287728</v>
+        <v>129283635</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -7301,13 +7301,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492227</v>
+        <v>492082</v>
       </c>
       <c r="R61" t="n">
-        <v>6764369</v>
+        <v>6764245</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>12. 1 Bild på kolarkoja</t>
+          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129290345</v>
+        <v>129271386</v>
       </c>
       <c r="B3" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492050</v>
+        <v>492097</v>
       </c>
       <c r="R3" t="n">
-        <v>6764358</v>
+        <v>6764207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,27 +847,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129271386</v>
+        <v>129290345</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492097</v>
+        <v>492050</v>
       </c>
       <c r="R4" t="n">
-        <v>6764207</v>
+        <v>6764358</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,27 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129270999</v>
+        <v>129271992</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,39 +1134,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492105</v>
+        <v>492111</v>
       </c>
       <c r="R6" t="n">
-        <v>6764156</v>
+        <v>6764274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,11 +1204,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129271992</v>
+        <v>129270999</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,34 +1241,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492111</v>
+        <v>492105</v>
       </c>
       <c r="R7" t="n">
-        <v>6764274</v>
+        <v>6764156</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,6 +1316,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,7 +1454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129290261</v>
+        <v>129287686</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492063</v>
+        <v>492200</v>
       </c>
       <c r="R9" t="n">
-        <v>6764369</v>
+        <v>6764371</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
+          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129287686</v>
+        <v>129290261</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492200</v>
+        <v>492063</v>
       </c>
       <c r="R10" t="n">
-        <v>6764371</v>
+        <v>6764369</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
+          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129294029</v>
+        <v>129291402</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>91553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,42 +1689,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492007</v>
+        <v>492107</v>
       </c>
       <c r="R11" t="n">
-        <v>6764289</v>
+        <v>6764244</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1758,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129291402</v>
+        <v>129293927</v>
       </c>
       <c r="B12" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,21 +1801,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1825,13 +1825,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R12" t="n">
-        <v>6764244</v>
+        <v>6764269</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129293927</v>
+        <v>129294029</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,34 +1913,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491997</v>
+        <v>492007</v>
       </c>
       <c r="R13" t="n">
-        <v>6764269</v>
+        <v>6764289</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1983,11 +1988,6 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129293473</v>
+        <v>129294398</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,37 +2463,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492120</v>
+        <v>491957</v>
       </c>
       <c r="R18" t="n">
-        <v>6764224</v>
+        <v>6764346</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2559,7 +2564,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129290547</v>
+        <v>129293473</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2594,13 +2599,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492071</v>
+        <v>492120</v>
       </c>
       <c r="R19" t="n">
-        <v>6764318</v>
+        <v>6764224</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2634,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,12 +2644,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,7 +2671,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129293152</v>
+        <v>129290547</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2706,13 +2706,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492125</v>
+        <v>492071</v>
       </c>
       <c r="R20" t="n">
-        <v>6764158</v>
+        <v>6764318</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2751,7 +2751,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2778,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129271179</v>
+        <v>129293152</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,39 +2794,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492113</v>
+        <v>492125</v>
       </c>
       <c r="R21" t="n">
-        <v>6764152</v>
+        <v>6764158</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2848,27 +2848,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,10 +2890,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129294398</v>
+        <v>129271179</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,16 +2901,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2926,7 +2921,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2930,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491957</v>
+        <v>492113</v>
       </c>
       <c r="R22" t="n">
-        <v>6764346</v>
+        <v>6764152</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2965,22 +2960,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,48 +3007,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129273280</v>
+        <v>129290672</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492172</v>
+        <v>492030</v>
       </c>
       <c r="R23" t="n">
-        <v>6764333</v>
+        <v>6764294</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3072,27 +3077,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129294699</v>
+        <v>129294219</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491988</v>
+        <v>491922</v>
       </c>
       <c r="R24" t="n">
-        <v>6764346</v>
+        <v>6764336</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,53 +3231,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129290672</v>
+        <v>129273280</v>
       </c>
       <c r="B25" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492030</v>
+        <v>492172</v>
       </c>
       <c r="R25" t="n">
-        <v>6764294</v>
+        <v>6764333</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3301,22 +3296,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3343,10 +3343,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129294219</v>
+        <v>129294699</v>
       </c>
       <c r="B26" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,21 +3354,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491922</v>
+        <v>491988</v>
       </c>
       <c r="R26" t="n">
-        <v>6764336</v>
+        <v>6764346</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>39. 2 bild</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3572,7 +3572,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129294905</v>
+        <v>129294335</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492048</v>
+        <v>491922</v>
       </c>
       <c r="R28" t="n">
-        <v>6764380</v>
+        <v>6764336</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3653,11 +3653,6 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3684,7 +3679,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129294335</v>
+        <v>129290087</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3719,10 +3714,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491922</v>
+        <v>492083</v>
       </c>
       <c r="R29" t="n">
-        <v>6764336</v>
+        <v>6764418</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3754,7 +3749,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3764,7 +3759,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3791,7 +3786,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129290087</v>
+        <v>129294905</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3826,10 +3821,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492083</v>
+        <v>492048</v>
       </c>
       <c r="R30" t="n">
-        <v>6764418</v>
+        <v>6764380</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3861,7 +3856,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3871,7 +3866,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129294510</v>
+        <v>129289310</v>
       </c>
       <c r="B32" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4021,42 +4021,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491975</v>
+        <v>492177</v>
       </c>
       <c r="R32" t="n">
-        <v>6764342</v>
+        <v>6764418</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4085,7 +4080,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4095,12 +4090,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>45. 3 bilder, miljöbilder</t>
+          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4127,10 +4122,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129289310</v>
+        <v>129294510</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4138,37 +4133,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492177</v>
+        <v>491975</v>
       </c>
       <c r="R33" t="n">
-        <v>6764418</v>
+        <v>6764342</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
+          <t>45. 3 bilder, miljöbilder</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129294065</v>
+        <v>129293510</v>
       </c>
       <c r="B37" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491997</v>
+        <v>492107</v>
       </c>
       <c r="R37" t="n">
-        <v>6764302</v>
+        <v>6764244</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4651,11 +4651,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4682,7 +4677,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294432</v>
+        <v>129294065</v>
       </c>
       <c r="B38" t="n">
         <v>91553</v>
@@ -4717,13 +4712,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491957</v>
+        <v>491997</v>
       </c>
       <c r="R38" t="n">
-        <v>6764346</v>
+        <v>6764302</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4767,7 +4762,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>44. 2 bilder, granlåga</t>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4794,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129293510</v>
+        <v>129294432</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4805,21 +4800,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4829,13 +4824,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492107</v>
+        <v>491957</v>
       </c>
       <c r="R39" t="n">
-        <v>6764244</v>
+        <v>6764346</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4875,6 +4870,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,50 +4901,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129293401</v>
+        <v>129289685</v>
       </c>
       <c r="B40" t="n">
-        <v>57724</v>
+        <v>97598</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492123</v>
+        <v>492160</v>
       </c>
       <c r="R40" t="n">
-        <v>6764202</v>
+        <v>6764361</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4976,7 +4971,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4986,12 +4981,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5018,10 +5013,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129295996</v>
+        <v>129293719</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5029,39 +5024,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R41" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5104,11 +5094,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5135,10 +5120,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129289411</v>
+        <v>129290779</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5146,39 +5131,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492157</v>
+        <v>492030</v>
       </c>
       <c r="R42" t="n">
-        <v>6764400</v>
+        <v>6764279</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5225,7 +5205,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5252,10 +5232,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129290779</v>
+        <v>129293401</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5263,37 +5243,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492030</v>
+        <v>492123</v>
       </c>
       <c r="R43" t="n">
-        <v>6764279</v>
+        <v>6764202</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5322,7 +5307,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5332,12 +5317,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5364,10 +5349,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293719</v>
+        <v>129295996</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5375,34 +5360,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492059</v>
+        <v>492085</v>
       </c>
       <c r="R44" t="n">
-        <v>6764244</v>
+        <v>6764296</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5445,6 +5435,11 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5471,48 +5466,53 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129293744</v>
+        <v>129289411</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492059</v>
+        <v>492157</v>
       </c>
       <c r="R45" t="n">
-        <v>6764244</v>
+        <v>6764400</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5551,7 +5551,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5578,10 +5583,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289685</v>
+        <v>129293744</v>
       </c>
       <c r="B46" t="n">
-        <v>97598</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5589,21 +5594,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5613,10 +5618,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492160</v>
+        <v>492059</v>
       </c>
       <c r="R46" t="n">
-        <v>6764361</v>
+        <v>6764244</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5648,7 +5653,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5658,12 +5663,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129293571</v>
+        <v>129274000</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,34 +5701,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492107</v>
+        <v>492089</v>
       </c>
       <c r="R47" t="n">
-        <v>6764235</v>
+        <v>6764397</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5755,22 +5763,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 bild samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5797,10 +5810,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129274000</v>
+        <v>129293571</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5808,42 +5821,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492089</v>
+        <v>492107</v>
       </c>
       <c r="R48" t="n">
-        <v>6764397</v>
+        <v>6764235</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5870,27 +5875,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 bild samt miljöbilder för området</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5917,10 +5917,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129274938</v>
+        <v>129294362</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5928,42 +5928,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492048</v>
+        <v>491956</v>
       </c>
       <c r="R49" t="n">
-        <v>6764380</v>
+        <v>6764334</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5987,27 +5982,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>I bild</t>
+          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6034,7 +6029,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129294362</v>
+        <v>129296258</v>
       </c>
       <c r="B50" t="n">
         <v>79044</v>
@@ -6069,13 +6064,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491956</v>
+        <v>492091</v>
       </c>
       <c r="R50" t="n">
-        <v>6764334</v>
+        <v>6764217</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6115,11 +6110,6 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6253,10 +6243,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129296258</v>
+        <v>129274938</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6264,34 +6254,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492091</v>
+        <v>492048</v>
       </c>
       <c r="R52" t="n">
-        <v>6764217</v>
+        <v>6764380</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6318,22 +6313,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>I bild</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6584,7 +6584,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129286796</v>
+        <v>129282927</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492169</v>
+        <v>492097</v>
       </c>
       <c r="R55" t="n">
-        <v>6764315</v>
+        <v>6764193</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
+          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6696,7 +6696,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129282927</v>
+        <v>129286796</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492097</v>
+        <v>492169</v>
       </c>
       <c r="R56" t="n">
-        <v>6764193</v>
+        <v>6764315</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
+          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7037,10 +7037,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129283043</v>
+        <v>129287728</v>
       </c>
       <c r="B59" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7048,39 +7048,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492082</v>
+        <v>492227</v>
       </c>
       <c r="R59" t="n">
-        <v>6764210</v>
+        <v>6764369</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7112,7 +7107,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7122,12 +7117,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>3. 1 bild</t>
+          <t>12. 1 Bild på kolarkoja</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7154,7 +7149,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129287728</v>
+        <v>129283635</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -7189,13 +7184,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492227</v>
+        <v>492082</v>
       </c>
       <c r="R60" t="n">
-        <v>6764369</v>
+        <v>6764245</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7224,7 +7219,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7234,12 +7229,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>12. 1 Bild på kolarkoja</t>
+          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7266,10 +7261,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129283635</v>
+        <v>129283043</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7277,24 +7272,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
@@ -7304,10 +7304,10 @@
         <v>492082</v>
       </c>
       <c r="R61" t="n">
-        <v>6764245</v>
+        <v>6764210</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
+          <t>3. 1 bild</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129271386</v>
+        <v>129293569</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492097</v>
+        <v>492107</v>
       </c>
       <c r="R3" t="n">
-        <v>6764207</v>
+        <v>6764235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,27 +847,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>35. 2 bilder, på granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129290345</v>
+        <v>129271386</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492050</v>
+        <v>492097</v>
       </c>
       <c r="R4" t="n">
-        <v>6764358</v>
+        <v>6764207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,27 +959,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129293569</v>
+        <v>129290345</v>
       </c>
       <c r="B5" t="n">
-        <v>91553</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,34 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492107</v>
+        <v>492050</v>
       </c>
       <c r="R5" t="n">
-        <v>6764235</v>
+        <v>6764358</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>35. 2 bilder, på granlåga</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1454,7 +1454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129287686</v>
+        <v>129290261</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492200</v>
+        <v>492063</v>
       </c>
       <c r="R9" t="n">
-        <v>6764371</v>
+        <v>6764369</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
+          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129290261</v>
+        <v>129287686</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492063</v>
+        <v>492200</v>
       </c>
       <c r="R10" t="n">
-        <v>6764369</v>
+        <v>6764371</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
+          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129291402</v>
+        <v>129294029</v>
       </c>
       <c r="B11" t="n">
-        <v>91553</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,37 +1689,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492107</v>
+        <v>492007</v>
       </c>
       <c r="R11" t="n">
-        <v>6764244</v>
+        <v>6764289</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,12 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129294029</v>
+        <v>129291402</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>91553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,42 +1913,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492007</v>
+        <v>492107</v>
       </c>
       <c r="R13" t="n">
-        <v>6764289</v>
+        <v>6764244</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1982,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129294398</v>
+        <v>129271179</v>
       </c>
       <c r="B18" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,16 +2463,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2483,7 +2483,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491957</v>
+        <v>492113</v>
       </c>
       <c r="R18" t="n">
-        <v>6764346</v>
+        <v>6764152</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,22 +2522,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2890,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129271179</v>
+        <v>129294398</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2901,16 +2906,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2921,7 +2926,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2930,13 +2935,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492113</v>
+        <v>491957</v>
       </c>
       <c r="R22" t="n">
-        <v>6764152</v>
+        <v>6764346</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2960,27 +2965,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,53 +3007,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129290672</v>
+        <v>129273280</v>
       </c>
       <c r="B23" t="n">
-        <v>58097</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492030</v>
+        <v>492172</v>
       </c>
       <c r="R23" t="n">
-        <v>6764294</v>
+        <v>6764333</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3077,22 +3072,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129294219</v>
+        <v>129294699</v>
       </c>
       <c r="B24" t="n">
-        <v>91851</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491922</v>
+        <v>491988</v>
       </c>
       <c r="R24" t="n">
-        <v>6764336</v>
+        <v>6764346</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>39. 2 bild</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129273280</v>
+        <v>129274016</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,34 +3242,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492172</v>
+        <v>492092</v>
       </c>
       <c r="R25" t="n">
-        <v>6764333</v>
+        <v>6764410</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3316,7 +3321,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3343,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129294699</v>
+        <v>129294219</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>91851</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,21 +3359,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3378,13 +3383,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491988</v>
+        <v>491922</v>
       </c>
       <c r="R26" t="n">
-        <v>6764346</v>
+        <v>6764336</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3428,7 +3433,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3455,27 +3460,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129274016</v>
+        <v>129290672</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>58097</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3486,7 +3491,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3495,13 +3500,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492092</v>
+        <v>492030</v>
       </c>
       <c r="R27" t="n">
-        <v>6764410</v>
+        <v>6764294</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3525,27 +3530,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 bild</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,7 +3572,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129294335</v>
+        <v>129294905</v>
       </c>
       <c r="B28" t="n">
         <v>79044</v>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491922</v>
+        <v>492048</v>
       </c>
       <c r="R28" t="n">
-        <v>6764336</v>
+        <v>6764380</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3653,6 +3653,11 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3679,7 +3684,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129290087</v>
+        <v>129294335</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3714,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492083</v>
+        <v>491922</v>
       </c>
       <c r="R29" t="n">
-        <v>6764418</v>
+        <v>6764336</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3749,7 +3754,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3759,7 +3764,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3786,7 +3791,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129294905</v>
+        <v>129290087</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3821,10 +3826,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492048</v>
+        <v>492083</v>
       </c>
       <c r="R30" t="n">
-        <v>6764380</v>
+        <v>6764418</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3856,7 +3861,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3866,12 +3871,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129289434</v>
+        <v>129295876</v>
       </c>
       <c r="B34" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492159</v>
+        <v>492080</v>
       </c>
       <c r="R34" t="n">
-        <v>6764383</v>
+        <v>6764357</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>16. 2 bild</t>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,7 +4351,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129295876</v>
+        <v>129294091</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492080</v>
+        <v>491988</v>
       </c>
       <c r="R35" t="n">
-        <v>6764357</v>
+        <v>6764293</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4432,11 +4432,6 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4463,10 +4458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129294091</v>
+        <v>129289434</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,21 +4469,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491988</v>
+        <v>492159</v>
       </c>
       <c r="R36" t="n">
-        <v>6764293</v>
+        <v>6764383</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4533,7 +4528,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4543,7 +4538,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4901,10 +4901,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129289685</v>
+        <v>129293744</v>
       </c>
       <c r="B40" t="n">
-        <v>97598</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4912,21 +4912,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4936,10 +4936,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492160</v>
+        <v>492059</v>
       </c>
       <c r="R40" t="n">
-        <v>6764361</v>
+        <v>6764244</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4981,12 +4981,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5013,7 +5008,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129293719</v>
+        <v>129290779</v>
       </c>
       <c r="B41" t="n">
         <v>79044</v>
@@ -5048,13 +5043,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492059</v>
+        <v>492030</v>
       </c>
       <c r="R41" t="n">
-        <v>6764244</v>
+        <v>6764279</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5083,7 +5078,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5093,7 +5088,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,7 +5120,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129290779</v>
+        <v>129293719</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -5155,13 +5155,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492030</v>
+        <v>492059</v>
       </c>
       <c r="R42" t="n">
-        <v>6764279</v>
+        <v>6764244</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5200,12 +5200,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5583,10 +5578,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129293744</v>
+        <v>129289685</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>97598</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5594,21 +5589,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5618,10 +5613,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492059</v>
+        <v>492160</v>
       </c>
       <c r="R46" t="n">
-        <v>6764244</v>
+        <v>6764361</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5653,7 +5648,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5663,7 +5658,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129274000</v>
+        <v>129293571</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,42 +5701,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492089</v>
+        <v>492107</v>
       </c>
       <c r="R47" t="n">
-        <v>6764397</v>
+        <v>6764235</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5763,27 +5755,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>1 bild samt miljöbilder för området</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5810,10 +5797,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129293571</v>
+        <v>129274000</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5821,34 +5808,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492107</v>
+        <v>492089</v>
       </c>
       <c r="R48" t="n">
-        <v>6764235</v>
+        <v>6764397</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5875,22 +5870,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 bild samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6029,10 +6029,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129296258</v>
+        <v>129290171</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,21 +6040,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492091</v>
+        <v>492061</v>
       </c>
       <c r="R50" t="n">
-        <v>6764217</v>
+        <v>6764382</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6099,7 +6099,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6136,10 +6136,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129290171</v>
+        <v>129296258</v>
       </c>
       <c r="B51" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492061</v>
+        <v>492091</v>
       </c>
       <c r="R51" t="n">
-        <v>6764382</v>
+        <v>6764217</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6206,7 +6206,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6216,7 +6216,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6584,7 +6584,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129282927</v>
+        <v>129286796</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492097</v>
+        <v>492169</v>
       </c>
       <c r="R55" t="n">
-        <v>6764193</v>
+        <v>6764315</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
+          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6696,7 +6696,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129286796</v>
+        <v>129282927</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492169</v>
+        <v>492097</v>
       </c>
       <c r="R56" t="n">
-        <v>6764315</v>
+        <v>6764193</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
+          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129271386</v>
+        <v>129290345</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492097</v>
+        <v>492050</v>
       </c>
       <c r="R4" t="n">
-        <v>6764207</v>
+        <v>6764358</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,27 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129290345</v>
+        <v>129271386</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,39 +1022,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492050</v>
+        <v>492097</v>
       </c>
       <c r="R5" t="n">
-        <v>6764358</v>
+        <v>6764207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129271992</v>
+        <v>129270999</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,34 +1134,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492111</v>
+        <v>492105</v>
       </c>
       <c r="R6" t="n">
-        <v>6764274</v>
+        <v>6764156</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,6 +1209,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129270999</v>
+        <v>129271992</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,39 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492105</v>
+        <v>492111</v>
       </c>
       <c r="R7" t="n">
-        <v>6764156</v>
+        <v>6764274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,11 +1321,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129294029</v>
+        <v>129291402</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>91553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,42 +1689,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492007</v>
+        <v>492107</v>
       </c>
       <c r="R11" t="n">
-        <v>6764289</v>
+        <v>6764244</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1758,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129293927</v>
+        <v>129294029</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,34 +1801,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491997</v>
+        <v>492007</v>
       </c>
       <c r="R12" t="n">
-        <v>6764269</v>
+        <v>6764289</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1871,11 +1876,6 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129291402</v>
+        <v>129293927</v>
       </c>
       <c r="B13" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,21 +1913,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R13" t="n">
-        <v>6764244</v>
+        <v>6764269</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2569,10 +2569,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129293473</v>
+        <v>129294398</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2580,37 +2580,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492120</v>
+        <v>491957</v>
       </c>
       <c r="R19" t="n">
-        <v>6764224</v>
+        <v>6764346</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2676,7 +2681,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129290547</v>
+        <v>129293473</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2711,13 +2716,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492071</v>
+        <v>492120</v>
       </c>
       <c r="R20" t="n">
-        <v>6764318</v>
+        <v>6764224</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2746,7 +2751,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2756,12 +2761,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2788,7 +2788,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129293152</v>
+        <v>129290547</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492125</v>
+        <v>492071</v>
       </c>
       <c r="R21" t="n">
-        <v>6764158</v>
+        <v>6764318</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2868,7 +2868,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129294398</v>
+        <v>129293152</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,42 +2911,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491957</v>
+        <v>492125</v>
       </c>
       <c r="R22" t="n">
-        <v>6764346</v>
+        <v>6764158</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3348,48 +3348,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129294219</v>
+        <v>129290672</v>
       </c>
       <c r="B26" t="n">
-        <v>91851</v>
+        <v>58097</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491922</v>
+        <v>492030</v>
       </c>
       <c r="R26" t="n">
-        <v>6764336</v>
+        <v>6764294</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3418,7 +3423,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3428,12 +3433,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>39. 2 bild</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,53 +3460,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129290672</v>
+        <v>129294219</v>
       </c>
       <c r="B27" t="n">
-        <v>58097</v>
+        <v>91851</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492030</v>
+        <v>491922</v>
       </c>
       <c r="R27" t="n">
-        <v>6764294</v>
+        <v>6764336</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3535,7 +3530,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3545,7 +3540,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129295876</v>
+        <v>129289434</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492080</v>
+        <v>492159</v>
       </c>
       <c r="R34" t="n">
-        <v>6764357</v>
+        <v>6764383</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>55. 1 bild hängande på gren</t>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,7 +4351,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129294091</v>
+        <v>129295876</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491988</v>
+        <v>492080</v>
       </c>
       <c r="R35" t="n">
-        <v>6764293</v>
+        <v>6764357</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4432,6 +4432,11 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4458,10 +4463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129289434</v>
+        <v>129294091</v>
       </c>
       <c r="B36" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4469,21 +4474,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492159</v>
+        <v>491988</v>
       </c>
       <c r="R36" t="n">
-        <v>6764383</v>
+        <v>6764293</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4533,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4538,12 +4543,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>16. 2 bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129293510</v>
+        <v>129294065</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R37" t="n">
-        <v>6764244</v>
+        <v>6764302</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4651,6 +4651,11 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4677,7 +4682,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294065</v>
+        <v>129294432</v>
       </c>
       <c r="B38" t="n">
         <v>91553</v>
@@ -4712,13 +4717,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491997</v>
+        <v>491957</v>
       </c>
       <c r="R38" t="n">
-        <v>6764302</v>
+        <v>6764346</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4762,7 +4767,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>38. 1 bild, granlåga</t>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4789,10 +4794,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129294432</v>
+        <v>129293510</v>
       </c>
       <c r="B39" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,21 +4805,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4824,13 +4829,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491957</v>
+        <v>492107</v>
       </c>
       <c r="R39" t="n">
-        <v>6764346</v>
+        <v>6764244</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4870,11 +4875,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,45 +4901,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129293744</v>
+        <v>129293401</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492059</v>
+        <v>492123</v>
       </c>
       <c r="R40" t="n">
-        <v>6764244</v>
+        <v>6764202</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4982,6 +4987,11 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5008,10 +5018,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129290779</v>
+        <v>129295996</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5019,37 +5029,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492030</v>
+        <v>492085</v>
       </c>
       <c r="R41" t="n">
-        <v>6764279</v>
+        <v>6764296</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5078,7 +5093,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5088,12 +5103,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,10 +5135,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129293719</v>
+        <v>129289411</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5131,37 +5146,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492059</v>
+        <v>492157</v>
       </c>
       <c r="R42" t="n">
-        <v>6764244</v>
+        <v>6764400</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5190,7 +5210,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5200,7 +5220,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5227,10 +5252,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129293401</v>
+        <v>129290779</v>
       </c>
       <c r="B43" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,42 +5263,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492123</v>
+        <v>492030</v>
       </c>
       <c r="R43" t="n">
-        <v>6764202</v>
+        <v>6764279</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5302,7 +5322,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5312,12 +5332,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5344,10 +5364,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129295996</v>
+        <v>129293719</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5355,39 +5375,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R44" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5430,11 +5445,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5461,53 +5471,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129289411</v>
+        <v>129289685</v>
       </c>
       <c r="B45" t="n">
-        <v>57724</v>
+        <v>97598</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492157</v>
+        <v>492160</v>
       </c>
       <c r="R45" t="n">
-        <v>6764400</v>
+        <v>6764361</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5551,7 +5556,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5578,10 +5583,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289685</v>
+        <v>129293744</v>
       </c>
       <c r="B46" t="n">
-        <v>97598</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5589,21 +5594,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5613,10 +5618,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492160</v>
+        <v>492059</v>
       </c>
       <c r="R46" t="n">
-        <v>6764361</v>
+        <v>6764244</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5648,7 +5653,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5658,12 +5663,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129293569</v>
+        <v>129271386</v>
       </c>
       <c r="B3" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492107</v>
+        <v>492097</v>
       </c>
       <c r="R3" t="n">
-        <v>6764235</v>
+        <v>6764207</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,27 +847,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>35. 2 bilder, på granlåga</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129290345</v>
+        <v>129293569</v>
       </c>
       <c r="B4" t="n">
-        <v>57724</v>
+        <v>91553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492050</v>
+        <v>492107</v>
       </c>
       <c r="R4" t="n">
-        <v>6764358</v>
+        <v>6764235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +974,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>35. 2 bilder, på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129271386</v>
+        <v>129290345</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,34 +1017,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492097</v>
+        <v>492050</v>
       </c>
       <c r="R5" t="n">
-        <v>6764207</v>
+        <v>6764358</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,50 +1123,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129270999</v>
+        <v>129294088</v>
       </c>
       <c r="B6" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492105</v>
+        <v>491988</v>
       </c>
       <c r="R6" t="n">
-        <v>6764156</v>
+        <v>6764293</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,27 +1188,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129271992</v>
+        <v>129270999</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,34 +1241,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492111</v>
+        <v>492105</v>
       </c>
       <c r="R7" t="n">
-        <v>6764274</v>
+        <v>6764156</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1321,6 +1316,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129294088</v>
+        <v>129271992</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491988</v>
+        <v>492111</v>
       </c>
       <c r="R8" t="n">
-        <v>6764293</v>
+        <v>6764274</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,22 +1412,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129291402</v>
+        <v>129294029</v>
       </c>
       <c r="B11" t="n">
-        <v>91553</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,37 +1689,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492107</v>
+        <v>492007</v>
       </c>
       <c r="R11" t="n">
-        <v>6764244</v>
+        <v>6764289</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,12 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129294029</v>
+        <v>129293927</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,39 +1801,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492007</v>
+        <v>491997</v>
       </c>
       <c r="R12" t="n">
-        <v>6764289</v>
+        <v>6764269</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1876,6 +1871,11 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129293927</v>
+        <v>129291402</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,21 +1913,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491997</v>
+        <v>492107</v>
       </c>
       <c r="R13" t="n">
-        <v>6764269</v>
+        <v>6764244</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129271179</v>
+        <v>129293473</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,39 +2463,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492113</v>
+        <v>492120</v>
       </c>
       <c r="R18" t="n">
-        <v>6764152</v>
+        <v>6764224</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2522,27 +2517,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2569,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129294398</v>
+        <v>129290547</v>
       </c>
       <c r="B19" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2580,39 +2570,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491957</v>
+        <v>492071</v>
       </c>
       <c r="R19" t="n">
-        <v>6764346</v>
+        <v>6764318</v>
       </c>
       <c r="S19" t="n">
         <v>50</v>
@@ -2644,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2654,7 +2639,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2681,7 +2671,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129293473</v>
+        <v>129293152</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2716,10 +2706,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492120</v>
+        <v>492125</v>
       </c>
       <c r="R20" t="n">
-        <v>6764224</v>
+        <v>6764158</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2788,10 +2778,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129290547</v>
+        <v>129271179</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2799,37 +2789,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492071</v>
+        <v>492113</v>
       </c>
       <c r="R21" t="n">
-        <v>6764318</v>
+        <v>6764152</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,27 +2848,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2900,10 +2895,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129293152</v>
+        <v>129294398</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,37 +2906,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492125</v>
+        <v>491957</v>
       </c>
       <c r="R22" t="n">
-        <v>6764158</v>
+        <v>6764346</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3348,53 +3348,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129290672</v>
+        <v>129294219</v>
       </c>
       <c r="B26" t="n">
-        <v>58097</v>
+        <v>91851</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492030</v>
+        <v>491922</v>
       </c>
       <c r="R26" t="n">
-        <v>6764294</v>
+        <v>6764336</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3423,7 +3418,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3433,7 +3428,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,48 +3460,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129294219</v>
+        <v>129290672</v>
       </c>
       <c r="B27" t="n">
-        <v>91851</v>
+        <v>58097</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491922</v>
+        <v>492030</v>
       </c>
       <c r="R27" t="n">
-        <v>6764336</v>
+        <v>6764294</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3530,7 +3535,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3540,12 +3545,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>39. 2 bild</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129289434</v>
+        <v>129295876</v>
       </c>
       <c r="B34" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492159</v>
+        <v>492080</v>
       </c>
       <c r="R34" t="n">
-        <v>6764383</v>
+        <v>6764357</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>16. 2 bild</t>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,7 +4351,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129295876</v>
+        <v>129294091</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492080</v>
+        <v>491988</v>
       </c>
       <c r="R35" t="n">
-        <v>6764357</v>
+        <v>6764293</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4432,11 +4432,6 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4463,10 +4458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129294091</v>
+        <v>129289434</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,21 +4469,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491988</v>
+        <v>492159</v>
       </c>
       <c r="R36" t="n">
-        <v>6764293</v>
+        <v>6764383</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4533,7 +4528,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4543,7 +4538,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129294065</v>
+        <v>129293510</v>
       </c>
       <c r="B37" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491997</v>
+        <v>492107</v>
       </c>
       <c r="R37" t="n">
-        <v>6764302</v>
+        <v>6764244</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4651,11 +4651,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4794,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129293510</v>
+        <v>129294065</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4805,21 +4800,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4829,10 +4824,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R39" t="n">
-        <v>6764244</v>
+        <v>6764302</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4875,6 +4870,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,10 +4901,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129293401</v>
+        <v>129290779</v>
       </c>
       <c r="B40" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4912,42 +4912,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492123</v>
+        <v>492030</v>
       </c>
       <c r="R40" t="n">
-        <v>6764202</v>
+        <v>6764279</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4976,7 +4971,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4986,12 +4981,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5018,10 +5013,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129295996</v>
+        <v>129293719</v>
       </c>
       <c r="B41" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5029,39 +5024,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R41" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5104,11 +5094,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5135,53 +5120,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129289411</v>
+        <v>129293744</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492157</v>
+        <v>492059</v>
       </c>
       <c r="R42" t="n">
-        <v>6764400</v>
+        <v>6764244</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5210,7 +5190,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5220,12 +5200,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>15. 1 bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5252,32 +5227,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129290779</v>
+        <v>129289685</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>97598</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5287,13 +5262,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492030</v>
+        <v>492160</v>
       </c>
       <c r="R43" t="n">
-        <v>6764279</v>
+        <v>6764361</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5337,7 +5312,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5364,10 +5339,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293719</v>
+        <v>129293401</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5375,34 +5350,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492059</v>
+        <v>492123</v>
       </c>
       <c r="R44" t="n">
-        <v>6764244</v>
+        <v>6764202</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5445,6 +5425,11 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5471,45 +5456,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129289685</v>
+        <v>129295996</v>
       </c>
       <c r="B45" t="n">
-        <v>97598</v>
+        <v>57724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492160</v>
+        <v>492085</v>
       </c>
       <c r="R45" t="n">
-        <v>6764361</v>
+        <v>6764296</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5541,7 +5531,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5551,12 +5541,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5583,48 +5573,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129293744</v>
+        <v>129289411</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492059</v>
+        <v>492157</v>
       </c>
       <c r="R46" t="n">
-        <v>6764244</v>
+        <v>6764400</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5653,7 +5648,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5663,7 +5658,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129293571</v>
+        <v>129274000</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,34 +5701,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492107</v>
+        <v>492089</v>
       </c>
       <c r="R47" t="n">
-        <v>6764235</v>
+        <v>6764397</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5755,22 +5763,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 bild samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5797,10 +5810,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129274000</v>
+        <v>129293571</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5808,42 +5821,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492089</v>
+        <v>492107</v>
       </c>
       <c r="R48" t="n">
-        <v>6764397</v>
+        <v>6764235</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5870,27 +5875,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 bild samt miljöbilder för området</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5917,10 +5917,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129294362</v>
+        <v>129274938</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5928,37 +5928,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491956</v>
+        <v>492048</v>
       </c>
       <c r="R49" t="n">
-        <v>6764334</v>
+        <v>6764380</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5982,27 +5987,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
+          <t>I bild</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6029,10 +6034,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129290171</v>
+        <v>129294362</v>
       </c>
       <c r="B50" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,21 +6045,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6064,13 +6069,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492061</v>
+        <v>491956</v>
       </c>
       <c r="R50" t="n">
-        <v>6764382</v>
+        <v>6764334</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6099,7 +6104,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6109,7 +6114,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6136,10 +6146,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129296258</v>
+        <v>129290171</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,21 +6157,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6171,10 +6181,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492091</v>
+        <v>492061</v>
       </c>
       <c r="R51" t="n">
-        <v>6764217</v>
+        <v>6764382</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6206,7 +6216,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6216,7 +6226,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6243,10 +6253,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129274938</v>
+        <v>129296258</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6254,39 +6264,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492048</v>
+        <v>492091</v>
       </c>
       <c r="R52" t="n">
-        <v>6764380</v>
+        <v>6764217</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6313,27 +6318,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>I bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -1123,32 +1123,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129294088</v>
+        <v>129271992</v>
       </c>
       <c r="B6" t="n">
-        <v>8450</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>491988</v>
+        <v>492111</v>
       </c>
       <c r="R6" t="n">
-        <v>6764293</v>
+        <v>6764274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,22 +1188,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1347,32 +1347,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129271992</v>
+        <v>129294088</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1382,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492111</v>
+        <v>491988</v>
       </c>
       <c r="R8" t="n">
-        <v>6764274</v>
+        <v>6764293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,22 +1412,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,7 +1454,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129290261</v>
+        <v>129287686</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492063</v>
+        <v>492200</v>
       </c>
       <c r="R9" t="n">
-        <v>6764369</v>
+        <v>6764371</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
+          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,7 +1566,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129287686</v>
+        <v>129290261</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492200</v>
+        <v>492063</v>
       </c>
       <c r="R10" t="n">
-        <v>6764371</v>
+        <v>6764369</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
+          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129294029</v>
+        <v>129291402</v>
       </c>
       <c r="B11" t="n">
-        <v>57887</v>
+        <v>91553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,42 +1689,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492007</v>
+        <v>492107</v>
       </c>
       <c r="R11" t="n">
-        <v>6764289</v>
+        <v>6764244</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1758,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129293927</v>
+        <v>129294029</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,34 +1801,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491997</v>
+        <v>492007</v>
       </c>
       <c r="R12" t="n">
-        <v>6764269</v>
+        <v>6764289</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1871,11 +1876,6 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129291402</v>
+        <v>129293927</v>
       </c>
       <c r="B13" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,21 +1913,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R13" t="n">
-        <v>6764244</v>
+        <v>6764269</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2778,10 +2778,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129271179</v>
+        <v>129294398</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,16 +2789,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2809,7 +2809,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492113</v>
+        <v>491957</v>
       </c>
       <c r="R21" t="n">
-        <v>6764152</v>
+        <v>6764346</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2848,27 +2848,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2895,10 +2890,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129294398</v>
+        <v>129271179</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2906,16 +2901,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2926,7 +2921,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2935,13 +2930,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491957</v>
+        <v>492113</v>
       </c>
       <c r="R22" t="n">
-        <v>6764346</v>
+        <v>6764152</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2965,22 +2960,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,48 +3007,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129273280</v>
+        <v>129290672</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>58097</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492172</v>
+        <v>492030</v>
       </c>
       <c r="R23" t="n">
-        <v>6764333</v>
+        <v>6764294</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3072,27 +3077,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,7 +3119,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129294699</v>
+        <v>129273280</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491988</v>
+        <v>492172</v>
       </c>
       <c r="R24" t="n">
-        <v>6764346</v>
+        <v>6764333</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3184,27 +3184,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129274016</v>
+        <v>129294699</v>
       </c>
       <c r="B25" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,42 +3242,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492092</v>
+        <v>491988</v>
       </c>
       <c r="R25" t="n">
-        <v>6764410</v>
+        <v>6764346</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3301,27 +3296,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3460,27 +3455,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129290672</v>
+        <v>129274016</v>
       </c>
       <c r="B27" t="n">
-        <v>58097</v>
+        <v>57727</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3491,7 +3486,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3500,13 +3495,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492030</v>
+        <v>492092</v>
       </c>
       <c r="R27" t="n">
-        <v>6764294</v>
+        <v>6764410</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3530,22 +3525,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129295876</v>
+        <v>129289434</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492080</v>
+        <v>492159</v>
       </c>
       <c r="R34" t="n">
-        <v>6764357</v>
+        <v>6764383</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>55. 1 bild hängande på gren</t>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,7 +4351,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129294091</v>
+        <v>129295876</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491988</v>
+        <v>492080</v>
       </c>
       <c r="R35" t="n">
-        <v>6764293</v>
+        <v>6764357</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4432,6 +4432,11 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4458,10 +4463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129289434</v>
+        <v>129294091</v>
       </c>
       <c r="B36" t="n">
-        <v>91553</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4469,21 +4474,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492159</v>
+        <v>491988</v>
       </c>
       <c r="R36" t="n">
-        <v>6764383</v>
+        <v>6764293</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4533,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4538,12 +4543,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>16. 2 bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4677,7 +4677,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294432</v>
+        <v>129294065</v>
       </c>
       <c r="B38" t="n">
         <v>91553</v>
@@ -4712,13 +4712,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491957</v>
+        <v>491997</v>
       </c>
       <c r="R38" t="n">
-        <v>6764346</v>
+        <v>6764302</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>44. 2 bilder, granlåga</t>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4789,7 +4789,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129294065</v>
+        <v>129294432</v>
       </c>
       <c r="B39" t="n">
         <v>91553</v>
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491997</v>
+        <v>491957</v>
       </c>
       <c r="R39" t="n">
-        <v>6764302</v>
+        <v>6764346</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>38. 1 bild, granlåga</t>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5120,45 +5120,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129293744</v>
+        <v>129293401</v>
       </c>
       <c r="B42" t="n">
-        <v>8450</v>
+        <v>57724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492059</v>
+        <v>492123</v>
       </c>
       <c r="R42" t="n">
-        <v>6764244</v>
+        <v>6764202</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5201,6 +5206,11 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5227,45 +5237,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129289685</v>
+        <v>129295996</v>
       </c>
       <c r="B43" t="n">
-        <v>97598</v>
+        <v>57724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492160</v>
+        <v>492085</v>
       </c>
       <c r="R43" t="n">
-        <v>6764361</v>
+        <v>6764296</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5297,7 +5312,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5307,12 +5322,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5339,7 +5354,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293401</v>
+        <v>129289411</v>
       </c>
       <c r="B44" t="n">
         <v>57724</v>
@@ -5379,13 +5394,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492123</v>
+        <v>492157</v>
       </c>
       <c r="R44" t="n">
-        <v>6764202</v>
+        <v>6764400</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5414,7 +5429,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5424,12 +5439,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,50 +5471,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129295996</v>
+        <v>129293744</v>
       </c>
       <c r="B45" t="n">
-        <v>57724</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R45" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5542,11 +5552,6 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5573,53 +5578,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289411</v>
+        <v>129289685</v>
       </c>
       <c r="B46" t="n">
-        <v>57724</v>
+        <v>97598</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492157</v>
+        <v>492160</v>
       </c>
       <c r="R46" t="n">
-        <v>6764400</v>
+        <v>6764361</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129274000</v>
+        <v>129293571</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,42 +5701,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492089</v>
+        <v>492107</v>
       </c>
       <c r="R47" t="n">
-        <v>6764397</v>
+        <v>6764235</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5763,27 +5755,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>1 bild samt miljöbilder för området</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5810,10 +5797,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129293571</v>
+        <v>129274000</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5821,34 +5808,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492107</v>
+        <v>492089</v>
       </c>
       <c r="R48" t="n">
-        <v>6764235</v>
+        <v>6764397</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5875,22 +5870,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 bild samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5917,10 +5917,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129274938</v>
+        <v>129294362</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5928,42 +5928,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492048</v>
+        <v>491956</v>
       </c>
       <c r="R49" t="n">
-        <v>6764380</v>
+        <v>6764334</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5987,27 +5982,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>I bild</t>
+          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6034,10 +6029,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129294362</v>
+        <v>129290171</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6045,21 +6040,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6069,13 +6064,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491956</v>
+        <v>492061</v>
       </c>
       <c r="R50" t="n">
-        <v>6764334</v>
+        <v>6764382</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6104,7 +6099,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6114,12 +6109,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6146,10 +6136,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129290171</v>
+        <v>129274938</v>
       </c>
       <c r="B51" t="n">
-        <v>79663</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6157,34 +6147,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492061</v>
+        <v>492048</v>
       </c>
       <c r="R51" t="n">
-        <v>6764382</v>
+        <v>6764380</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6211,22 +6206,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>I bild</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7037,10 +7037,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129287728</v>
+        <v>129283043</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7048,34 +7048,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492227</v>
+        <v>492082</v>
       </c>
       <c r="R59" t="n">
-        <v>6764369</v>
+        <v>6764210</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7107,7 +7112,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7117,12 +7122,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>12. 1 Bild på kolarkoja</t>
+          <t>3. 1 bild</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7149,7 +7154,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129283635</v>
+        <v>129287728</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -7184,13 +7189,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492082</v>
+        <v>492227</v>
       </c>
       <c r="R60" t="n">
-        <v>6764245</v>
+        <v>6764369</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7219,7 +7224,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7229,12 +7234,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
+          <t>12. 1 Bild på kolarkoja</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7261,10 +7266,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129283043</v>
+        <v>129283635</v>
       </c>
       <c r="B61" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7272,29 +7277,24 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
@@ -7304,10 +7304,10 @@
         <v>492082</v>
       </c>
       <c r="R61" t="n">
-        <v>6764210</v>
+        <v>6764245</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>3. 1 bild</t>
+          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129271130</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129271386</v>
+        <v>129293569</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>91581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492097</v>
+        <v>492107</v>
       </c>
       <c r="R3" t="n">
-        <v>6764207</v>
+        <v>6764235</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,27 +847,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>35. 2 bilder, på granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129293569</v>
+        <v>129271386</v>
       </c>
       <c r="B4" t="n">
-        <v>91553</v>
+        <v>79070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492107</v>
+        <v>492097</v>
       </c>
       <c r="R4" t="n">
-        <v>6764235</v>
+        <v>6764207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,27 +959,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>35. 2 bilder, på granlåga</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,7 +1009,7 @@
         <v>129290345</v>
       </c>
       <c r="B5" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>129271992</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>129270999</v>
       </c>
       <c r="B7" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129287686</v>
+        <v>129290261</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492200</v>
+        <v>492063</v>
       </c>
       <c r="R9" t="n">
-        <v>6764371</v>
+        <v>6764369</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
+          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129290261</v>
+        <v>129287686</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492063</v>
+        <v>492200</v>
       </c>
       <c r="R10" t="n">
-        <v>6764369</v>
+        <v>6764371</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
+          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1681,7 +1681,7 @@
         <v>129291402</v>
       </c>
       <c r="B11" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129294029</v>
+        <v>129293927</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>79070</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1801,39 +1801,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492007</v>
+        <v>491997</v>
       </c>
       <c r="R12" t="n">
-        <v>6764289</v>
+        <v>6764269</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1876,6 +1871,11 @@
       <c r="AB12" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129293927</v>
+        <v>129294029</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>57890</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,34 +1913,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491997</v>
+        <v>492007</v>
       </c>
       <c r="R13" t="n">
-        <v>6764269</v>
+        <v>6764289</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1983,11 +1988,6 @@
       <c r="AB13" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129287945</v>
+        <v>129296076</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492218</v>
+        <v>492085</v>
       </c>
       <c r="R14" t="n">
-        <v>6764381</v>
+        <v>6764296</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,12 +2094,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>13. 2 bilder, tallstammar Rikligt till måttligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,10 +2121,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129296076</v>
+        <v>129287945</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,13 +2156,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492085</v>
+        <v>492218</v>
       </c>
       <c r="R15" t="n">
-        <v>6764296</v>
+        <v>6764381</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2196,7 +2191,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2206,7 +2201,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>13. 2 bilder, tallstammar Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,7 +2236,7 @@
         <v>129293376</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>129294004</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129293473</v>
+        <v>129293152</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492120</v>
+        <v>492125</v>
       </c>
       <c r="R18" t="n">
-        <v>6764224</v>
+        <v>6764158</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129290547</v>
+        <v>129293473</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,13 +2594,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492071</v>
+        <v>492120</v>
       </c>
       <c r="R19" t="n">
-        <v>6764318</v>
+        <v>6764224</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2639,12 +2639,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,10 +2666,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129293152</v>
+        <v>129290547</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,13 +2701,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492125</v>
+        <v>492071</v>
       </c>
       <c r="R20" t="n">
-        <v>6764158</v>
+        <v>6764318</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,7 +2736,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2751,7 +2746,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2781,7 +2781,7 @@
         <v>129294398</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>129271179</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3007,53 +3007,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129290672</v>
+        <v>129294219</v>
       </c>
       <c r="B23" t="n">
-        <v>58097</v>
+        <v>91879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492030</v>
+        <v>491922</v>
       </c>
       <c r="R23" t="n">
-        <v>6764294</v>
+        <v>6764336</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3082,7 +3077,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3092,7 +3087,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129273280</v>
+        <v>129294699</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492172</v>
+        <v>491988</v>
       </c>
       <c r="R24" t="n">
-        <v>6764333</v>
+        <v>6764346</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3184,27 +3184,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129294699</v>
+        <v>129273280</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3266,13 +3266,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491988</v>
+        <v>492172</v>
       </c>
       <c r="R25" t="n">
-        <v>6764346</v>
+        <v>6764333</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3296,27 +3296,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3343,10 +3343,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129294219</v>
+        <v>129274016</v>
       </c>
       <c r="B26" t="n">
-        <v>91851</v>
+        <v>57730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,34 +3354,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491922</v>
+        <v>492092</v>
       </c>
       <c r="R26" t="n">
-        <v>6764336</v>
+        <v>6764410</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3408,27 +3413,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>39. 2 bild</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3455,27 +3460,27 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129274016</v>
+        <v>129290672</v>
       </c>
       <c r="B27" t="n">
-        <v>57727</v>
+        <v>58100</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3486,7 +3491,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3495,13 +3500,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492092</v>
+        <v>492030</v>
       </c>
       <c r="R27" t="n">
-        <v>6764410</v>
+        <v>6764294</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3525,27 +3530,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 bild</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,10 +3572,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129294905</v>
+        <v>129294335</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492048</v>
+        <v>491922</v>
       </c>
       <c r="R28" t="n">
-        <v>6764380</v>
+        <v>6764336</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3653,11 +3653,6 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3684,10 +3679,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129294335</v>
+        <v>129290087</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3719,10 +3714,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491922</v>
+        <v>492083</v>
       </c>
       <c r="R29" t="n">
-        <v>6764336</v>
+        <v>6764418</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3754,7 +3749,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3764,7 +3759,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3791,10 +3786,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129290087</v>
+        <v>129294905</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3826,10 +3821,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492083</v>
+        <v>492048</v>
       </c>
       <c r="R30" t="n">
-        <v>6764418</v>
+        <v>6764380</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3861,7 +3856,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3871,7 +3866,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3901,7 +3901,7 @@
         <v>129295250</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>129289310</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4125,7 +4125,7 @@
         <v>129294510</v>
       </c>
       <c r="B33" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>129289434</v>
       </c>
       <c r="B34" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4351,10 +4351,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129295876</v>
+        <v>129294091</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492080</v>
+        <v>491988</v>
       </c>
       <c r="R35" t="n">
-        <v>6764357</v>
+        <v>6764293</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4432,11 +4432,6 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4463,10 +4458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129294091</v>
+        <v>129295876</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491988</v>
+        <v>492080</v>
       </c>
       <c r="R36" t="n">
-        <v>6764293</v>
+        <v>6764357</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4544,6 +4539,11 @@
       <c r="AB36" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129293510</v>
+        <v>129294065</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>91581</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R37" t="n">
-        <v>6764244</v>
+        <v>6764302</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4651,6 +4651,11 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4677,10 +4682,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294065</v>
+        <v>129294432</v>
       </c>
       <c r="B38" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4712,13 +4717,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491997</v>
+        <v>491957</v>
       </c>
       <c r="R38" t="n">
-        <v>6764302</v>
+        <v>6764346</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4762,7 +4767,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>38. 1 bild, granlåga</t>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4789,10 +4794,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129294432</v>
+        <v>129293510</v>
       </c>
       <c r="B39" t="n">
-        <v>91553</v>
+        <v>79070</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,21 +4805,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4824,13 +4829,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491957</v>
+        <v>492107</v>
       </c>
       <c r="R39" t="n">
-        <v>6764346</v>
+        <v>6764244</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4870,11 +4875,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,32 +4901,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129290779</v>
+        <v>129293744</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4936,13 +4936,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492030</v>
+        <v>492059</v>
       </c>
       <c r="R40" t="n">
-        <v>6764279</v>
+        <v>6764244</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4981,12 +4981,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5013,32 +5008,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129293719</v>
+        <v>129289685</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>97627</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5048,10 +5043,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492059</v>
+        <v>492160</v>
       </c>
       <c r="R41" t="n">
-        <v>6764244</v>
+        <v>6764361</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5083,7 +5078,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5093,7 +5088,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,10 +5120,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129293401</v>
+        <v>129293719</v>
       </c>
       <c r="B42" t="n">
-        <v>57724</v>
+        <v>79070</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5131,39 +5131,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492123</v>
+        <v>492059</v>
       </c>
       <c r="R42" t="n">
-        <v>6764202</v>
+        <v>6764244</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5206,11 +5201,6 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5237,10 +5227,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129295996</v>
+        <v>129290779</v>
       </c>
       <c r="B43" t="n">
-        <v>57724</v>
+        <v>79070</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5248,42 +5238,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492085</v>
+        <v>492030</v>
       </c>
       <c r="R43" t="n">
-        <v>6764296</v>
+        <v>6764279</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5312,7 +5297,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5322,12 +5307,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>56. 2 bilder, även svamp på gran</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5354,10 +5339,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129289411</v>
+        <v>129293401</v>
       </c>
       <c r="B44" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5394,13 +5379,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492157</v>
+        <v>492123</v>
       </c>
       <c r="R44" t="n">
-        <v>6764400</v>
+        <v>6764202</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5429,7 +5414,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5439,12 +5424,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5471,45 +5456,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129293744</v>
+        <v>129295996</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492059</v>
+        <v>492085</v>
       </c>
       <c r="R45" t="n">
-        <v>6764244</v>
+        <v>6764296</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5552,6 +5542,11 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5578,48 +5573,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289685</v>
+        <v>129289411</v>
       </c>
       <c r="B46" t="n">
-        <v>97598</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492160</v>
+        <v>492157</v>
       </c>
       <c r="R46" t="n">
-        <v>6764361</v>
+        <v>6764400</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129293571</v>
+        <v>129274000</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,34 +5701,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492107</v>
+        <v>492089</v>
       </c>
       <c r="R47" t="n">
-        <v>6764235</v>
+        <v>6764397</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5755,22 +5763,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 bild samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5797,10 +5810,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129274000</v>
+        <v>129293571</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5808,42 +5821,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492089</v>
+        <v>492107</v>
       </c>
       <c r="R48" t="n">
-        <v>6764397</v>
+        <v>6764235</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5870,27 +5875,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 bild samt miljöbilder för området</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5917,10 +5917,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129294362</v>
+        <v>129290171</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>79689</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5928,21 +5928,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5952,13 +5952,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491956</v>
+        <v>492061</v>
       </c>
       <c r="R49" t="n">
-        <v>6764334</v>
+        <v>6764382</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5997,12 +5997,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6029,10 +6024,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129290171</v>
+        <v>129294362</v>
       </c>
       <c r="B50" t="n">
-        <v>79663</v>
+        <v>79070</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6040,21 +6035,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6064,13 +6059,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492061</v>
+        <v>491956</v>
       </c>
       <c r="R50" t="n">
-        <v>6764382</v>
+        <v>6764334</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6099,7 +6094,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6109,7 +6104,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6136,10 +6136,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129274938</v>
+        <v>129296258</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79070</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,39 +6147,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492048</v>
+        <v>492091</v>
       </c>
       <c r="R51" t="n">
-        <v>6764380</v>
+        <v>6764217</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6206,27 +6201,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>I bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6253,10 +6243,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129296258</v>
+        <v>129274938</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>57730</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6264,34 +6254,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492091</v>
+        <v>492048</v>
       </c>
       <c r="R52" t="n">
-        <v>6764217</v>
+        <v>6764380</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6318,22 +6313,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>I bild</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6363,7 +6363,7 @@
         <v>129282981</v>
       </c>
       <c r="B53" t="n">
-        <v>57724</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>129293814</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6584,10 +6584,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129286796</v>
+        <v>129282927</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492169</v>
+        <v>492097</v>
       </c>
       <c r="R55" t="n">
-        <v>6764315</v>
+        <v>6764193</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
+          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6696,10 +6696,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129282927</v>
+        <v>129286796</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492097</v>
+        <v>492169</v>
       </c>
       <c r="R56" t="n">
-        <v>6764193</v>
+        <v>6764315</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
+          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6811,7 +6811,7 @@
         <v>129290011</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>129283290</v>
       </c>
       <c r="B58" t="n">
-        <v>79663</v>
+        <v>79689</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7037,10 +7037,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129283043</v>
+        <v>129283635</v>
       </c>
       <c r="B59" t="n">
-        <v>57724</v>
+        <v>79070</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7048,29 +7048,24 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
@@ -7080,10 +7075,10 @@
         <v>492082</v>
       </c>
       <c r="R59" t="n">
-        <v>6764210</v>
+        <v>6764245</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7127,7 +7122,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>3. 1 bild</t>
+          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7157,7 +7152,7 @@
         <v>129287728</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7266,10 +7261,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129283635</v>
+        <v>129283043</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7277,24 +7272,29 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
@@ -7304,10 +7304,10 @@
         <v>492082</v>
       </c>
       <c r="R61" t="n">
-        <v>6764245</v>
+        <v>6764210</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
+          <t>3. 1 bild</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7381,7 +7381,7 @@
         <v>129287751</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -1230,50 +1230,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129270999</v>
+        <v>129294088</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492105</v>
+        <v>491988</v>
       </c>
       <c r="R7" t="n">
-        <v>6764156</v>
+        <v>6764293</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,27 +1295,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,45 +1337,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129294088</v>
+        <v>129270999</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491988</v>
+        <v>492105</v>
       </c>
       <c r="R8" t="n">
-        <v>6764293</v>
+        <v>6764156</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,22 +1407,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129294065</v>
+        <v>129293510</v>
       </c>
       <c r="B37" t="n">
-        <v>91581</v>
+        <v>79070</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491997</v>
+        <v>492107</v>
       </c>
       <c r="R37" t="n">
-        <v>6764302</v>
+        <v>6764244</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4651,11 +4651,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4682,7 +4677,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294432</v>
+        <v>129294065</v>
       </c>
       <c r="B38" t="n">
         <v>91581</v>
@@ -4717,13 +4712,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491957</v>
+        <v>491997</v>
       </c>
       <c r="R38" t="n">
-        <v>6764346</v>
+        <v>6764302</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4767,7 +4762,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>44. 2 bilder, granlåga</t>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4794,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129293510</v>
+        <v>129294432</v>
       </c>
       <c r="B39" t="n">
-        <v>79070</v>
+        <v>91581</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4805,21 +4800,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4829,13 +4824,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492107</v>
+        <v>491957</v>
       </c>
       <c r="R39" t="n">
-        <v>6764244</v>
+        <v>6764346</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4875,6 +4870,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,32 +4901,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129293744</v>
+        <v>129293719</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>79070</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5008,32 +5008,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129289685</v>
+        <v>129290779</v>
       </c>
       <c r="B41" t="n">
-        <v>97627</v>
+        <v>79070</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5043,13 +5043,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492160</v>
+        <v>492030</v>
       </c>
       <c r="R41" t="n">
-        <v>6764361</v>
+        <v>6764279</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,10 +5120,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129293719</v>
+        <v>129293401</v>
       </c>
       <c r="B42" t="n">
-        <v>79070</v>
+        <v>57727</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5131,34 +5131,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492059</v>
+        <v>492123</v>
       </c>
       <c r="R42" t="n">
-        <v>6764244</v>
+        <v>6764202</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5201,6 +5206,11 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5227,10 +5237,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129290779</v>
+        <v>129295996</v>
       </c>
       <c r="B43" t="n">
-        <v>79070</v>
+        <v>57727</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5238,37 +5248,42 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492030</v>
+        <v>492085</v>
       </c>
       <c r="R43" t="n">
-        <v>6764279</v>
+        <v>6764296</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5297,7 +5312,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5307,12 +5322,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5339,7 +5354,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293401</v>
+        <v>129289411</v>
       </c>
       <c r="B44" t="n">
         <v>57727</v>
@@ -5379,13 +5394,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492123</v>
+        <v>492157</v>
       </c>
       <c r="R44" t="n">
-        <v>6764202</v>
+        <v>6764400</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5414,7 +5429,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5424,12 +5439,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,50 +5471,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129295996</v>
+        <v>129293744</v>
       </c>
       <c r="B45" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R45" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5542,11 +5552,6 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5573,53 +5578,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289411</v>
+        <v>129289685</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>97627</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492157</v>
+        <v>492160</v>
       </c>
       <c r="R46" t="n">
-        <v>6764400</v>
+        <v>6764361</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5917,10 +5917,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129290171</v>
+        <v>129294362</v>
       </c>
       <c r="B49" t="n">
-        <v>79689</v>
+        <v>79070</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5928,21 +5928,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5952,13 +5952,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492061</v>
+        <v>491956</v>
       </c>
       <c r="R49" t="n">
-        <v>6764382</v>
+        <v>6764334</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5997,7 +5997,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6024,7 +6029,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129294362</v>
+        <v>129296258</v>
       </c>
       <c r="B50" t="n">
         <v>79070</v>
@@ -6059,13 +6064,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491956</v>
+        <v>492091</v>
       </c>
       <c r="R50" t="n">
-        <v>6764334</v>
+        <v>6764217</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6105,11 +6110,6 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6136,10 +6136,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129296258</v>
+        <v>129274938</v>
       </c>
       <c r="B51" t="n">
-        <v>79070</v>
+        <v>57730</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,34 +6147,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492091</v>
+        <v>492048</v>
       </c>
       <c r="R51" t="n">
-        <v>6764217</v>
+        <v>6764380</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6201,22 +6206,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>I bild</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6243,10 +6253,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129274938</v>
+        <v>129290171</v>
       </c>
       <c r="B52" t="n">
-        <v>57730</v>
+        <v>79689</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6254,39 +6264,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492048</v>
+        <v>492061</v>
       </c>
       <c r="R52" t="n">
-        <v>6764380</v>
+        <v>6764382</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6313,27 +6318,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>I bild</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129271130</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129293569</v>
       </c>
       <c r="B3" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129271386</v>
+        <v>129290345</v>
       </c>
       <c r="B4" t="n">
-        <v>79070</v>
+        <v>57732</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,34 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492097</v>
+        <v>492050</v>
       </c>
       <c r="R4" t="n">
-        <v>6764207</v>
+        <v>6764358</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,27 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129290345</v>
+        <v>129271386</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1017,39 +1022,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492050</v>
+        <v>492097</v>
       </c>
       <c r="R5" t="n">
-        <v>6764358</v>
+        <v>6764207</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1126,7 @@
         <v>129271992</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>129270999</v>
       </c>
       <c r="B8" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129290261</v>
+        <v>129287686</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492063</v>
+        <v>492200</v>
       </c>
       <c r="R9" t="n">
-        <v>6764369</v>
+        <v>6764371</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
+          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129287686</v>
+        <v>129290261</v>
       </c>
       <c r="B10" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492200</v>
+        <v>492063</v>
       </c>
       <c r="R10" t="n">
-        <v>6764371</v>
+        <v>6764369</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
+          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129291402</v>
+        <v>129294029</v>
       </c>
       <c r="B11" t="n">
-        <v>91581</v>
+        <v>57895</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,37 +1689,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492107</v>
+        <v>492007</v>
       </c>
       <c r="R11" t="n">
-        <v>6764244</v>
+        <v>6764289</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1748,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1758,12 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,7 +1793,7 @@
         <v>129293927</v>
       </c>
       <c r="B12" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129294029</v>
+        <v>129291402</v>
       </c>
       <c r="B13" t="n">
-        <v>57890</v>
+        <v>91587</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,42 +1913,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492007</v>
+        <v>492107</v>
       </c>
       <c r="R13" t="n">
-        <v>6764289</v>
+        <v>6764244</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,7 +1972,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1987,7 +1982,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129296076</v>
+        <v>129287945</v>
       </c>
       <c r="B14" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2049,13 +2049,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492085</v>
+        <v>492218</v>
       </c>
       <c r="R14" t="n">
-        <v>6764296</v>
+        <v>6764381</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,7 +2094,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>13. 2 bilder, tallstammar Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2121,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129287945</v>
+        <v>129296076</v>
       </c>
       <c r="B15" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2156,13 +2161,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492218</v>
+        <v>492085</v>
       </c>
       <c r="R15" t="n">
-        <v>6764381</v>
+        <v>6764296</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2191,7 +2196,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,12 +2206,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>13. 2 bilder, tallstammar Rikligt till måttligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2236,7 +2236,7 @@
         <v>129293376</v>
       </c>
       <c r="B16" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>129294004</v>
       </c>
       <c r="B17" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129293152</v>
+        <v>129290547</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2487,13 +2487,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492125</v>
+        <v>492071</v>
       </c>
       <c r="R18" t="n">
-        <v>6764158</v>
+        <v>6764318</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,7 +2532,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2559,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129293473</v>
+        <v>129294398</v>
       </c>
       <c r="B19" t="n">
-        <v>79070</v>
+        <v>57732</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2570,37 +2575,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492120</v>
+        <v>491957</v>
       </c>
       <c r="R19" t="n">
-        <v>6764224</v>
+        <v>6764346</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2666,10 +2676,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129290547</v>
+        <v>129271179</v>
       </c>
       <c r="B20" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2677,37 +2687,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492071</v>
+        <v>492113</v>
       </c>
       <c r="R20" t="n">
-        <v>6764318</v>
+        <v>6764152</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2731,27 +2746,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2778,10 +2793,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129294398</v>
+        <v>129293473</v>
       </c>
       <c r="B21" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2789,42 +2804,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491957</v>
+        <v>492120</v>
       </c>
       <c r="R21" t="n">
-        <v>6764346</v>
+        <v>6764224</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2890,10 +2900,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129271179</v>
+        <v>129293152</v>
       </c>
       <c r="B22" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2901,39 +2911,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492113</v>
+        <v>492125</v>
       </c>
       <c r="R22" t="n">
-        <v>6764152</v>
+        <v>6764158</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,27 +2965,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,48 +3007,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129294219</v>
+        <v>129290672</v>
       </c>
       <c r="B23" t="n">
-        <v>91879</v>
+        <v>58105</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491922</v>
+        <v>492030</v>
       </c>
       <c r="R23" t="n">
-        <v>6764336</v>
+        <v>6764294</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3077,7 +3082,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3087,12 +3092,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>39. 2 bild</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129294699</v>
+        <v>129294219</v>
       </c>
       <c r="B24" t="n">
-        <v>79070</v>
+        <v>91885</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491988</v>
+        <v>491922</v>
       </c>
       <c r="R24" t="n">
-        <v>6764346</v>
+        <v>6764336</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,10 +3231,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129273280</v>
+        <v>129274016</v>
       </c>
       <c r="B25" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,34 +3242,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492172</v>
+        <v>492092</v>
       </c>
       <c r="R25" t="n">
-        <v>6764333</v>
+        <v>6764410</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3316,7 +3321,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3343,10 +3348,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129274016</v>
+        <v>129294699</v>
       </c>
       <c r="B26" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3354,42 +3359,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492092</v>
+        <v>491988</v>
       </c>
       <c r="R26" t="n">
-        <v>6764410</v>
+        <v>6764346</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3413,27 +3413,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,53 +3460,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129290672</v>
+        <v>129273280</v>
       </c>
       <c r="B27" t="n">
-        <v>58100</v>
+        <v>79075</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492030</v>
+        <v>492172</v>
       </c>
       <c r="R27" t="n">
-        <v>6764294</v>
+        <v>6764333</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3530,22 +3525,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,10 +3572,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129294335</v>
+        <v>129290087</v>
       </c>
       <c r="B28" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>491922</v>
+        <v>492083</v>
       </c>
       <c r="R28" t="n">
-        <v>6764336</v>
+        <v>6764418</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3679,10 +3679,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129290087</v>
+        <v>129294905</v>
       </c>
       <c r="B29" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492083</v>
+        <v>492048</v>
       </c>
       <c r="R29" t="n">
-        <v>6764418</v>
+        <v>6764380</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3759,7 +3759,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3786,10 +3791,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129294905</v>
+        <v>129294335</v>
       </c>
       <c r="B30" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3821,10 +3826,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492048</v>
+        <v>491922</v>
       </c>
       <c r="R30" t="n">
-        <v>6764380</v>
+        <v>6764336</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3867,11 +3872,6 @@
       <c r="AB30" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3901,7 +3901,7 @@
         <v>129295250</v>
       </c>
       <c r="B31" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129289310</v>
+        <v>129294510</v>
       </c>
       <c r="B32" t="n">
-        <v>79070</v>
+        <v>57732</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4021,37 +4021,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492177</v>
+        <v>491975</v>
       </c>
       <c r="R32" t="n">
-        <v>6764418</v>
+        <v>6764342</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4080,7 +4085,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4090,12 +4095,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
+          <t>45. 3 bilder, miljöbilder</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4122,10 +4127,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129294510</v>
+        <v>129289310</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4133,42 +4138,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>491975</v>
+        <v>492177</v>
       </c>
       <c r="R33" t="n">
-        <v>6764342</v>
+        <v>6764418</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>45. 3 bilder, miljöbilder</t>
+          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4242,7 +4242,7 @@
         <v>129289434</v>
       </c>
       <c r="B34" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4351,10 +4351,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129294091</v>
+        <v>129295876</v>
       </c>
       <c r="B35" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>491988</v>
+        <v>492080</v>
       </c>
       <c r="R35" t="n">
-        <v>6764293</v>
+        <v>6764357</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4432,6 +4432,11 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4458,10 +4463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129295876</v>
+        <v>129294091</v>
       </c>
       <c r="B36" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4493,10 +4498,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492080</v>
+        <v>491988</v>
       </c>
       <c r="R36" t="n">
-        <v>6764357</v>
+        <v>6764293</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4539,11 +4544,6 @@
       <c r="AB36" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129293510</v>
+        <v>129294065</v>
       </c>
       <c r="B37" t="n">
-        <v>79070</v>
+        <v>91587</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492107</v>
+        <v>491997</v>
       </c>
       <c r="R37" t="n">
-        <v>6764244</v>
+        <v>6764302</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4651,6 +4651,11 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4677,10 +4682,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294065</v>
+        <v>129294432</v>
       </c>
       <c r="B38" t="n">
-        <v>91581</v>
+        <v>91587</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4712,13 +4717,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491997</v>
+        <v>491957</v>
       </c>
       <c r="R38" t="n">
-        <v>6764302</v>
+        <v>6764346</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4762,7 +4767,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>38. 1 bild, granlåga</t>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4789,10 +4794,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129294432</v>
+        <v>129293510</v>
       </c>
       <c r="B39" t="n">
-        <v>91581</v>
+        <v>79075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4800,21 +4805,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4824,13 +4829,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491957</v>
+        <v>492107</v>
       </c>
       <c r="R39" t="n">
-        <v>6764346</v>
+        <v>6764244</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4870,11 +4875,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,32 +4901,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129293719</v>
+        <v>129293744</v>
       </c>
       <c r="B40" t="n">
-        <v>79070</v>
+        <v>8450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5008,32 +5008,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129290779</v>
+        <v>129289685</v>
       </c>
       <c r="B41" t="n">
-        <v>79070</v>
+        <v>97639</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5043,13 +5043,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492030</v>
+        <v>492160</v>
       </c>
       <c r="R41" t="n">
-        <v>6764279</v>
+        <v>6764361</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,10 +5120,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129293401</v>
+        <v>129290779</v>
       </c>
       <c r="B42" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5131,42 +5131,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492123</v>
+        <v>492030</v>
       </c>
       <c r="R42" t="n">
-        <v>6764202</v>
+        <v>6764279</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5195,7 +5190,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5205,12 +5200,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5237,10 +5232,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129295996</v>
+        <v>129293719</v>
       </c>
       <c r="B43" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5248,39 +5243,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R43" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5323,11 +5313,6 @@
       <c r="AB43" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5354,10 +5339,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129289411</v>
+        <v>129293401</v>
       </c>
       <c r="B44" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5394,13 +5379,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492157</v>
+        <v>492123</v>
       </c>
       <c r="R44" t="n">
-        <v>6764400</v>
+        <v>6764202</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5429,7 +5414,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5439,12 +5424,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5471,45 +5456,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129293744</v>
+        <v>129295996</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>57732</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492059</v>
+        <v>492085</v>
       </c>
       <c r="R45" t="n">
-        <v>6764244</v>
+        <v>6764296</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5552,6 +5542,11 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5578,48 +5573,53 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289685</v>
+        <v>129289411</v>
       </c>
       <c r="B46" t="n">
-        <v>97627</v>
+        <v>57732</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492160</v>
+        <v>492157</v>
       </c>
       <c r="R46" t="n">
-        <v>6764361</v>
+        <v>6764400</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129274000</v>
+        <v>129293571</v>
       </c>
       <c r="B47" t="n">
-        <v>57730</v>
+        <v>79075</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,42 +5701,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492089</v>
+        <v>492107</v>
       </c>
       <c r="R47" t="n">
-        <v>6764397</v>
+        <v>6764235</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5763,27 +5755,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>1 bild samt miljöbilder för området</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5810,10 +5797,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129293571</v>
+        <v>129274000</v>
       </c>
       <c r="B48" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5821,34 +5808,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492107</v>
+        <v>492089</v>
       </c>
       <c r="R48" t="n">
-        <v>6764235</v>
+        <v>6764397</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5875,22 +5870,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 bild samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5917,10 +5917,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129294362</v>
+        <v>129274938</v>
       </c>
       <c r="B49" t="n">
-        <v>79070</v>
+        <v>57735</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5928,37 +5928,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>491956</v>
+        <v>492048</v>
       </c>
       <c r="R49" t="n">
-        <v>6764334</v>
+        <v>6764380</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5982,27 +5987,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
+          <t>I bild</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6029,10 +6034,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129296258</v>
+        <v>129294362</v>
       </c>
       <c r="B50" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6064,13 +6069,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>492091</v>
+        <v>491956</v>
       </c>
       <c r="R50" t="n">
-        <v>6764217</v>
+        <v>6764334</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6110,6 +6115,11 @@
       <c r="AB50" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6136,10 +6146,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129274938</v>
+        <v>129290171</v>
       </c>
       <c r="B51" t="n">
-        <v>57730</v>
+        <v>79694</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6147,39 +6157,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492048</v>
+        <v>492061</v>
       </c>
       <c r="R51" t="n">
-        <v>6764380</v>
+        <v>6764382</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6206,27 +6211,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>I bild</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6253,10 +6253,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129290171</v>
+        <v>129296258</v>
       </c>
       <c r="B52" t="n">
-        <v>79689</v>
+        <v>79075</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6264,21 +6264,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492061</v>
+        <v>492091</v>
       </c>
       <c r="R52" t="n">
-        <v>6764382</v>
+        <v>6764217</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6333,7 +6333,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6363,7 +6363,7 @@
         <v>129282981</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>57732</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>129293814</v>
       </c>
       <c r="B54" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
         <v>129282927</v>
       </c>
       <c r="B55" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>129286796</v>
       </c>
       <c r="B56" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>129290011</v>
       </c>
       <c r="B57" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>129283290</v>
       </c>
       <c r="B58" t="n">
-        <v>79689</v>
+        <v>79694</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7037,10 +7037,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129283635</v>
+        <v>129287728</v>
       </c>
       <c r="B59" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7072,13 +7072,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492082</v>
+        <v>492227</v>
       </c>
       <c r="R59" t="n">
-        <v>6764245</v>
+        <v>6764369</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
+          <t>12. 1 Bild på kolarkoja</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7149,10 +7149,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129287728</v>
+        <v>129283043</v>
       </c>
       <c r="B60" t="n">
-        <v>79070</v>
+        <v>57732</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7160,34 +7160,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492227</v>
+        <v>492082</v>
       </c>
       <c r="R60" t="n">
-        <v>6764369</v>
+        <v>6764210</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7219,7 +7224,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7229,12 +7234,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>12. 1 Bild på kolarkoja</t>
+          <t>3. 1 bild</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7261,10 +7266,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129283043</v>
+        <v>129283635</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>79075</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7272,29 +7277,24 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
@@ -7304,10 +7304,10 @@
         <v>492082</v>
       </c>
       <c r="R61" t="n">
-        <v>6764210</v>
+        <v>6764245</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>3. 1 bild</t>
+          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7381,7 +7381,7 @@
         <v>129287751</v>
       </c>
       <c r="B62" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129271130</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129293569</v>
       </c>
       <c r="B3" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>129290345</v>
       </c>
       <c r="B4" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>129271386</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129271992</v>
+        <v>129270999</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,34 +1134,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492111</v>
+        <v>492105</v>
       </c>
       <c r="R6" t="n">
-        <v>6764274</v>
+        <v>6764156</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,6 +1209,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,32 +1240,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129294088</v>
+        <v>129271992</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491988</v>
+        <v>492111</v>
       </c>
       <c r="R7" t="n">
-        <v>6764293</v>
+        <v>6764274</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,22 +1305,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,50 +1347,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129270999</v>
+        <v>129294088</v>
       </c>
       <c r="B8" t="n">
-        <v>57732</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492105</v>
+        <v>491988</v>
       </c>
       <c r="R8" t="n">
-        <v>6764156</v>
+        <v>6764293</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,27 +1412,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,10 +1454,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129287686</v>
+        <v>129290261</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,10 +1489,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492200</v>
+        <v>492063</v>
       </c>
       <c r="R9" t="n">
-        <v>6764371</v>
+        <v>6764369</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
+          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1566,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129290261</v>
+        <v>129287686</v>
       </c>
       <c r="B10" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492063</v>
+        <v>492200</v>
       </c>
       <c r="R10" t="n">
-        <v>6764369</v>
+        <v>6764371</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
+          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129294029</v>
+        <v>129291402</v>
       </c>
       <c r="B11" t="n">
-        <v>57895</v>
+        <v>91588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,42 +1689,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492007</v>
+        <v>492107</v>
       </c>
       <c r="R11" t="n">
-        <v>6764289</v>
+        <v>6764244</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1753,7 +1748,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1758,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>25. 4 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,7 +1793,7 @@
         <v>129293927</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1902,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129291402</v>
+        <v>129294029</v>
       </c>
       <c r="B13" t="n">
-        <v>91587</v>
+        <v>57896</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1913,37 +1913,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492107</v>
+        <v>492007</v>
       </c>
       <c r="R13" t="n">
-        <v>6764244</v>
+        <v>6764289</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,7 +1977,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1982,12 +1987,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2017,7 +2017,7 @@
         <v>129287945</v>
       </c>
       <c r="B14" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>129296076</v>
       </c>
       <c r="B15" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>129293376</v>
       </c>
       <c r="B16" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>129294004</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2452,10 +2452,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129290547</v>
+        <v>129294398</v>
       </c>
       <c r="B18" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2463,34 +2463,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492071</v>
+        <v>491957</v>
       </c>
       <c r="R18" t="n">
-        <v>6764318</v>
+        <v>6764346</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2522,7 +2527,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2532,12 +2537,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2564,10 +2564,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129294398</v>
+        <v>129293473</v>
       </c>
       <c r="B19" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2575,42 +2575,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491957</v>
+        <v>492120</v>
       </c>
       <c r="R19" t="n">
-        <v>6764346</v>
+        <v>6764224</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2676,10 +2671,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129271179</v>
+        <v>129290547</v>
       </c>
       <c r="B20" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2687,42 +2682,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492113</v>
+        <v>492071</v>
       </c>
       <c r="R20" t="n">
-        <v>6764152</v>
+        <v>6764318</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2746,27 +2736,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2793,10 +2783,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129293473</v>
+        <v>129293152</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2828,10 +2818,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492120</v>
+        <v>492125</v>
       </c>
       <c r="R21" t="n">
-        <v>6764224</v>
+        <v>6764158</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2900,10 +2890,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129293152</v>
+        <v>129271179</v>
       </c>
       <c r="B22" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,34 +2901,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492125</v>
+        <v>492113</v>
       </c>
       <c r="R22" t="n">
-        <v>6764158</v>
+        <v>6764152</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2965,22 +2960,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,53 +3007,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129290672</v>
+        <v>129273280</v>
       </c>
       <c r="B23" t="n">
-        <v>58105</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492030</v>
+        <v>492172</v>
       </c>
       <c r="R23" t="n">
-        <v>6764294</v>
+        <v>6764333</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3077,22 +3072,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3122,7 +3122,7 @@
         <v>129294219</v>
       </c>
       <c r="B24" t="n">
-        <v>91885</v>
+        <v>91886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>129274016</v>
       </c>
       <c r="B25" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>129294699</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3460,48 +3460,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129273280</v>
+        <v>129290672</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>58106</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492172</v>
+        <v>492030</v>
       </c>
       <c r="R27" t="n">
-        <v>6764333</v>
+        <v>6764294</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3525,27 +3530,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,10 +3572,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129290087</v>
+        <v>129294905</v>
       </c>
       <c r="B28" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492083</v>
+        <v>492048</v>
       </c>
       <c r="R28" t="n">
-        <v>6764418</v>
+        <v>6764380</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3652,7 +3652,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3679,10 +3684,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129294905</v>
+        <v>129294335</v>
       </c>
       <c r="B29" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3714,10 +3719,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492048</v>
+        <v>491922</v>
       </c>
       <c r="R29" t="n">
-        <v>6764380</v>
+        <v>6764336</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3760,11 +3765,6 @@
       <c r="AB29" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3791,10 +3791,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129294335</v>
+        <v>129290087</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3826,10 +3826,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491922</v>
+        <v>492083</v>
       </c>
       <c r="R30" t="n">
-        <v>6764336</v>
+        <v>6764418</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3901,7 +3901,7 @@
         <v>129295250</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>129294510</v>
       </c>
       <c r="B32" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>129289310</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129289434</v>
+        <v>129295876</v>
       </c>
       <c r="B34" t="n">
-        <v>91587</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4250,21 +4250,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4274,10 +4274,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492159</v>
+        <v>492080</v>
       </c>
       <c r="R34" t="n">
-        <v>6764383</v>
+        <v>6764357</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4309,7 +4309,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>16. 2 bild</t>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4351,10 +4351,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129295876</v>
+        <v>129294091</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4386,10 +4386,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492080</v>
+        <v>491988</v>
       </c>
       <c r="R35" t="n">
-        <v>6764357</v>
+        <v>6764293</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4432,11 +4432,6 @@
       <c r="AB35" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4463,10 +4458,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129294091</v>
+        <v>129289434</v>
       </c>
       <c r="B36" t="n">
-        <v>79075</v>
+        <v>91588</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4474,21 +4469,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4498,10 +4493,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491988</v>
+        <v>492159</v>
       </c>
       <c r="R36" t="n">
-        <v>6764293</v>
+        <v>6764383</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4533,7 +4528,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4543,7 +4538,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4573,7 +4573,7 @@
         <v>129294065</v>
       </c>
       <c r="B37" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>129294432</v>
       </c>
       <c r="B38" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>129293510</v>
       </c>
       <c r="B39" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4901,45 +4901,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129293744</v>
+        <v>129293401</v>
       </c>
       <c r="B40" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492059</v>
+        <v>492123</v>
       </c>
       <c r="R40" t="n">
-        <v>6764244</v>
+        <v>6764202</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4982,6 +4987,11 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5008,45 +5018,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129289685</v>
+        <v>129295996</v>
       </c>
       <c r="B41" t="n">
-        <v>97639</v>
+        <v>57733</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492160</v>
+        <v>492085</v>
       </c>
       <c r="R41" t="n">
-        <v>6764361</v>
+        <v>6764296</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5078,7 +5093,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5088,12 +5103,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5120,10 +5135,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129290779</v>
+        <v>129289411</v>
       </c>
       <c r="B42" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5131,34 +5146,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492030</v>
+        <v>492157</v>
       </c>
       <c r="R42" t="n">
-        <v>6764279</v>
+        <v>6764400</v>
       </c>
       <c r="S42" t="n">
         <v>50</v>
@@ -5205,7 +5225,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5232,10 +5252,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129293719</v>
+        <v>129290779</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5267,13 +5287,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492059</v>
+        <v>492030</v>
       </c>
       <c r="R43" t="n">
-        <v>6764244</v>
+        <v>6764279</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5302,7 +5322,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5312,7 +5332,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5339,10 +5364,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293401</v>
+        <v>129293719</v>
       </c>
       <c r="B44" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5350,39 +5375,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492123</v>
+        <v>492059</v>
       </c>
       <c r="R44" t="n">
-        <v>6764202</v>
+        <v>6764244</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5425,11 +5445,6 @@
       <c r="AB44" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5456,50 +5471,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129295996</v>
+        <v>129293744</v>
       </c>
       <c r="B45" t="n">
-        <v>57732</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492085</v>
+        <v>492059</v>
       </c>
       <c r="R45" t="n">
-        <v>6764296</v>
+        <v>6764244</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5542,11 +5552,6 @@
       <c r="AB45" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5573,53 +5578,48 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289411</v>
+        <v>129289685</v>
       </c>
       <c r="B46" t="n">
-        <v>57732</v>
+        <v>97640</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492157</v>
+        <v>492160</v>
       </c>
       <c r="R46" t="n">
-        <v>6764400</v>
+        <v>6764361</v>
       </c>
       <c r="S46" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>15. 1 bild</t>
+          <t>17. 3 miljöbilder,</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5690,10 +5690,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129293571</v>
+        <v>129274000</v>
       </c>
       <c r="B47" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5701,34 +5701,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492107</v>
+        <v>492089</v>
       </c>
       <c r="R47" t="n">
-        <v>6764235</v>
+        <v>6764397</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5755,22 +5763,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1 bild samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5797,10 +5810,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129274000</v>
+        <v>129293571</v>
       </c>
       <c r="B48" t="n">
-        <v>57735</v>
+        <v>79076</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5808,42 +5821,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492089</v>
+        <v>492107</v>
       </c>
       <c r="R48" t="n">
-        <v>6764397</v>
+        <v>6764235</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5870,27 +5875,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 bild samt miljöbilder för området</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5920,7 +5920,7 @@
         <v>129274938</v>
       </c>
       <c r="B49" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>129294362</v>
       </c>
       <c r="B50" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>129290171</v>
       </c>
       <c r="B51" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>129296258</v>
       </c>
       <c r="B52" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6363,7 +6363,7 @@
         <v>129282981</v>
       </c>
       <c r="B53" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         <v>129293814</v>
       </c>
       <c r="B54" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6584,10 +6584,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129282927</v>
+        <v>129286796</v>
       </c>
       <c r="B55" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6619,10 +6619,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492097</v>
+        <v>492169</v>
       </c>
       <c r="R55" t="n">
-        <v>6764193</v>
+        <v>6764315</v>
       </c>
       <c r="S55" t="n">
         <v>50</v>
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
+          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6696,10 +6696,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129286796</v>
+        <v>129282927</v>
       </c>
       <c r="B56" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6731,10 +6731,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492169</v>
+        <v>492097</v>
       </c>
       <c r="R56" t="n">
-        <v>6764315</v>
+        <v>6764193</v>
       </c>
       <c r="S56" t="n">
         <v>50</v>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
+          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6811,7 +6811,7 @@
         <v>129290011</v>
       </c>
       <c r="B57" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>129283290</v>
       </c>
       <c r="B58" t="n">
-        <v>79694</v>
+        <v>79695</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7037,10 +7037,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129287728</v>
+        <v>129283635</v>
       </c>
       <c r="B59" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7072,13 +7072,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492227</v>
+        <v>492082</v>
       </c>
       <c r="R59" t="n">
-        <v>6764369</v>
+        <v>6764245</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>12. 1 Bild på kolarkoja</t>
+          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7152,7 +7152,7 @@
         <v>129283043</v>
       </c>
       <c r="B60" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7266,10 +7266,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129283635</v>
+        <v>129287728</v>
       </c>
       <c r="B61" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7301,13 +7301,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492082</v>
+        <v>492227</v>
       </c>
       <c r="R61" t="n">
-        <v>6764245</v>
+        <v>6764369</v>
       </c>
       <c r="S61" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
+          <t>12. 1 Bild på kolarkoja</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7381,7 +7381,7 @@
         <v>129287751</v>
       </c>
       <c r="B62" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7492,6 +7492,107 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>129764564</v>
+      </c>
+      <c r="B63" t="n">
+        <v>92041</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>492111</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6764260</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129293569</v>
+        <v>129290345</v>
       </c>
       <c r="B3" t="n">
-        <v>91588</v>
+        <v>57733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492107</v>
+        <v>492050</v>
       </c>
       <c r="R3" t="n">
-        <v>6764235</v>
+        <v>6764358</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>35. 2 bilder, på granlåga</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129290345</v>
+        <v>129271386</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492050</v>
+        <v>492097</v>
       </c>
       <c r="R4" t="n">
-        <v>6764358</v>
+        <v>6764207</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,27 +964,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129271386</v>
+        <v>129293569</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>91588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492097</v>
+        <v>492107</v>
       </c>
       <c r="R5" t="n">
-        <v>6764207</v>
+        <v>6764235</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,27 +1076,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>35. 2 bilder, på granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129270999</v>
+        <v>129271992</v>
       </c>
       <c r="B6" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,39 +1134,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492105</v>
+        <v>492111</v>
       </c>
       <c r="R6" t="n">
-        <v>6764156</v>
+        <v>6764274</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1209,11 +1204,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,32 +1230,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129271992</v>
+        <v>129294088</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>8450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492111</v>
+        <v>491988</v>
       </c>
       <c r="R7" t="n">
-        <v>6764274</v>
+        <v>6764293</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,22 +1295,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,45 +1337,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129294088</v>
+        <v>129270999</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491988</v>
+        <v>492105</v>
       </c>
       <c r="R8" t="n">
-        <v>6764293</v>
+        <v>6764156</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,22 +1407,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bild 1</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -3119,10 +3119,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129294219</v>
+        <v>129294699</v>
       </c>
       <c r="B24" t="n">
-        <v>91886</v>
+        <v>79076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3130,21 +3130,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3154,13 +3154,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491922</v>
+        <v>491988</v>
       </c>
       <c r="R24" t="n">
-        <v>6764336</v>
+        <v>6764346</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>39. 2 bild</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3348,45 +3348,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129294699</v>
+        <v>129290672</v>
       </c>
       <c r="B26" t="n">
-        <v>79076</v>
+        <v>58106</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491988</v>
+        <v>492030</v>
       </c>
       <c r="R26" t="n">
-        <v>6764346</v>
+        <v>6764294</v>
       </c>
       <c r="S26" t="n">
         <v>50</v>
@@ -3418,7 +3423,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3428,12 +3433,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,53 +3460,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129290672</v>
+        <v>129294219</v>
       </c>
       <c r="B27" t="n">
-        <v>58106</v>
+        <v>91886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492030</v>
+        <v>491922</v>
       </c>
       <c r="R27" t="n">
-        <v>6764294</v>
+        <v>6764336</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3535,7 +3530,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3545,7 +3540,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4570,10 +4570,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129294065</v>
+        <v>129293510</v>
       </c>
       <c r="B37" t="n">
-        <v>91588</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>491997</v>
+        <v>492107</v>
       </c>
       <c r="R37" t="n">
-        <v>6764302</v>
+        <v>6764244</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4651,11 +4651,6 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4682,7 +4677,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294432</v>
+        <v>129294065</v>
       </c>
       <c r="B38" t="n">
         <v>91588</v>
@@ -4717,13 +4712,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491957</v>
+        <v>491997</v>
       </c>
       <c r="R38" t="n">
-        <v>6764346</v>
+        <v>6764302</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4767,7 +4762,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>44. 2 bilder, granlåga</t>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4794,10 +4789,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129293510</v>
+        <v>129294432</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>91588</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4805,21 +4800,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4829,13 +4824,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>492107</v>
+        <v>491957</v>
       </c>
       <c r="R39" t="n">
-        <v>6764244</v>
+        <v>6764346</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4875,6 +4870,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -6587,7 +6587,7 @@
         <v>129286796</v>
       </c>
       <c r="B55" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>129282927</v>
       </c>
       <c r="B56" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6928,7 +6928,7 @@
         <v>129283290</v>
       </c>
       <c r="B58" t="n">
-        <v>79695</v>
+        <v>79700</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7037,10 +7037,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129283635</v>
+        <v>129287728</v>
       </c>
       <c r="B59" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7072,13 +7072,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492082</v>
+        <v>492227</v>
       </c>
       <c r="R59" t="n">
-        <v>6764245</v>
+        <v>6764369</v>
       </c>
       <c r="S59" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
+          <t>12. 1 Bild på kolarkoja</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7149,10 +7149,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129283043</v>
+        <v>129283635</v>
       </c>
       <c r="B60" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7160,29 +7160,24 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
@@ -7192,10 +7187,10 @@
         <v>492082</v>
       </c>
       <c r="R60" t="n">
-        <v>6764210</v>
+        <v>6764245</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7239,7 +7234,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>3. 1 bild</t>
+          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7266,10 +7261,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129287728</v>
+        <v>129283043</v>
       </c>
       <c r="B61" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7277,34 +7272,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492227</v>
+        <v>492082</v>
       </c>
       <c r="R61" t="n">
-        <v>6764369</v>
+        <v>6764210</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>12. 1 Bild på kolarkoja</t>
+          <t>3. 1 bild</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7498,7 +7498,7 @@
         <v>129764564</v>
       </c>
       <c r="B63" t="n">
-        <v>92041</v>
+        <v>92046</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -7498,7 +7498,7 @@
         <v>129764564</v>
       </c>
       <c r="B63" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -7498,7 +7498,7 @@
         <v>129764564</v>
       </c>
       <c r="B63" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -7498,7 +7498,7 @@
         <v>129764564</v>
       </c>
       <c r="B63" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -7498,7 +7498,7 @@
         <v>129764564</v>
       </c>
       <c r="B63" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -7498,7 +7498,7 @@
         <v>129764564</v>
       </c>
       <c r="B63" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -7498,7 +7498,7 @@
         <v>129764564</v>
       </c>
       <c r="B63" t="n">
-        <v>92059</v>
+        <v>92076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129271130</v>
+        <v>129294219</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492105</v>
+        <v>491922</v>
       </c>
       <c r="R2" t="n">
-        <v>6764156</v>
+        <v>6764336</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,22 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129290345</v>
+        <v>129283566</v>
       </c>
       <c r="B3" t="n">
-        <v>57733</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492050</v>
+        <v>492107</v>
       </c>
       <c r="R3" t="n">
-        <v>6764358</v>
+        <v>6764244</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>20. 1 bild</t>
+          <t>5. 3 bilder på vedsvampar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129271386</v>
+        <v>129289434</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -910,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -934,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492097</v>
+        <v>492159</v>
       </c>
       <c r="R4" t="n">
-        <v>6764207</v>
+        <v>6764383</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,27 +968,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 50 meter</t>
+          <t>16. 2 bild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1018,7 @@
         <v>129293569</v>
       </c>
       <c r="B5" t="n">
-        <v>91588</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,10 +1127,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129271992</v>
+        <v>129294065</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1162,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492111</v>
+        <v>491997</v>
       </c>
       <c r="R6" t="n">
-        <v>6764274</v>
+        <v>6764302</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,22 +1192,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>38. 1 bild, granlåga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,32 +1239,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129294088</v>
+        <v>129294432</v>
       </c>
       <c r="B7" t="n">
-        <v>8450</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491988</v>
+        <v>491957</v>
       </c>
       <c r="R7" t="n">
-        <v>6764293</v>
+        <v>6764346</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,6 +1320,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>44. 2 bilder, granlåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129270999</v>
+        <v>129764564</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,39 +1362,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>492105</v>
+        <v>492111</v>
       </c>
       <c r="R8" t="n">
-        <v>6764156</v>
+        <v>6764260</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,27 +1419,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:35</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Bild 1</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1436,6 +1433,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1454,48 +1452,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129290261</v>
+        <v>129286698</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>492063</v>
+        <v>492202</v>
       </c>
       <c r="R9" t="n">
-        <v>6764369</v>
+        <v>6764306</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1539,7 +1540,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
+          <t>8. 4 bilder på vedsvamp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,6 +1549,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1566,14 +1568,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129287686</v>
+        <v>129271130</v>
       </c>
       <c r="B10" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1601,13 +1603,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492200</v>
+        <v>492105</v>
       </c>
       <c r="R10" t="n">
-        <v>6764371</v>
+        <v>6764156</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1631,27 +1633,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,32 +1675,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129291402</v>
+        <v>129271386</v>
       </c>
       <c r="B11" t="n">
-        <v>91588</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1713,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>492107</v>
+        <v>492097</v>
       </c>
       <c r="R11" t="n">
-        <v>6764244</v>
+        <v>6764207</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,27 +1740,27 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>25. 4 bilder, granlåga</t>
+          <t>Rikligt i en radie av ca 50 meter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1790,14 +1787,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129293927</v>
+        <v>129271992</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1825,13 +1822,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491997</v>
+        <v>492111</v>
       </c>
       <c r="R12" t="n">
-        <v>6764269</v>
+        <v>6764274</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1855,27 +1852,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1902,53 +1894,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129294029</v>
+        <v>129273280</v>
       </c>
       <c r="B13" t="n">
-        <v>57896</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492007</v>
+        <v>492172</v>
       </c>
       <c r="R13" t="n">
-        <v>6764289</v>
+        <v>6764333</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1972,22 +1959,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av ca 40 meter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,14 +2006,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129287945</v>
+        <v>129282927</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2049,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492218</v>
+        <v>492097</v>
       </c>
       <c r="R14" t="n">
-        <v>6764381</v>
+        <v>6764193</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2084,7 +2076,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2094,12 +2086,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>13. 2 bilder, tallstammar Rikligt till måttligt i en radie av 50 meter</t>
+          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2126,14 +2118,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129296076</v>
+        <v>129283635</v>
       </c>
       <c r="B15" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2161,13 +2153,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492085</v>
+        <v>492082</v>
       </c>
       <c r="R15" t="n">
-        <v>6764296</v>
+        <v>6764245</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2196,7 +2188,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2206,7 +2198,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,14 +2230,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129293376</v>
+        <v>129285073</v>
       </c>
       <c r="B16" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2268,10 +2265,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492123</v>
+        <v>492174</v>
       </c>
       <c r="R16" t="n">
-        <v>6764202</v>
+        <v>6764277</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2303,7 +2300,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2313,7 +2310,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>8. 1 bild på stam med yttergräns</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2340,14 +2342,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129294004</v>
+        <v>129286796</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2375,10 +2377,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491966</v>
+        <v>492169</v>
       </c>
       <c r="R17" t="n">
-        <v>6764290</v>
+        <v>6764315</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2410,7 +2412,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2420,12 +2422,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>37. 4 bilder, en närbild Rikligt i en radie av 50 meter</t>
+          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2452,50 +2454,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129294398</v>
+        <v>129287686</v>
       </c>
       <c r="B18" t="n">
-        <v>57733</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491957</v>
+        <v>492200</v>
       </c>
       <c r="R18" t="n">
-        <v>6764346</v>
+        <v>6764371</v>
       </c>
       <c r="S18" t="n">
         <v>50</v>
@@ -2527,7 +2524,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2537,7 +2534,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>11. 6 bilder, första på två tallstammar, sista miljöbilder</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2564,14 +2566,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129293473</v>
+        <v>129287728</v>
       </c>
       <c r="B19" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2599,10 +2601,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492120</v>
+        <v>492227</v>
       </c>
       <c r="R19" t="n">
-        <v>6764224</v>
+        <v>6764369</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2634,7 +2636,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2644,7 +2646,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>12. 1 Bild på kolarkoja</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2671,14 +2678,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129290547</v>
+        <v>129287945</v>
       </c>
       <c r="B20" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2706,10 +2713,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492071</v>
+        <v>492218</v>
       </c>
       <c r="R20" t="n">
-        <v>6764318</v>
+        <v>6764381</v>
       </c>
       <c r="S20" t="n">
         <v>50</v>
@@ -2756,7 +2763,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
+          <t>13. 2 bilder, tallstammar Rikligt till måttligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,14 +2790,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129293152</v>
+        <v>129289310</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2818,13 +2825,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492125</v>
+        <v>492177</v>
       </c>
       <c r="R21" t="n">
-        <v>6764158</v>
+        <v>6764418</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2853,7 +2860,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2863,7 +2870,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2890,50 +2902,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129271179</v>
+        <v>129290087</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492113</v>
+        <v>492083</v>
       </c>
       <c r="R22" t="n">
-        <v>6764152</v>
+        <v>6764418</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2960,27 +2967,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3007,14 +3009,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129273280</v>
+        <v>129290261</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3042,13 +3044,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492172</v>
+        <v>492063</v>
       </c>
       <c r="R23" t="n">
-        <v>6764333</v>
+        <v>6764369</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3072,27 +3074,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av ca 40 meter</t>
+          <t>19. 1 bild med stubbe i förgrund Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3119,14 +3121,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129294699</v>
+        <v>129290547</v>
       </c>
       <c r="B24" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3154,10 +3156,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>491988</v>
+        <v>492071</v>
       </c>
       <c r="R24" t="n">
-        <v>6764346</v>
+        <v>6764318</v>
       </c>
       <c r="S24" t="n">
         <v>50</v>
@@ -3189,7 +3191,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3199,12 +3201,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
+          <t>21. 2 bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3231,53 +3233,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129274016</v>
+        <v>129290779</v>
       </c>
       <c r="B25" t="n">
-        <v>57736</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492092</v>
+        <v>492030</v>
       </c>
       <c r="R25" t="n">
-        <v>6764410</v>
+        <v>6764279</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3301,27 +3298,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1 bild</t>
+          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3348,53 +3345,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129290672</v>
+        <v>129293152</v>
       </c>
       <c r="B26" t="n">
-        <v>58106</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492030</v>
+        <v>492125</v>
       </c>
       <c r="R26" t="n">
-        <v>6764294</v>
+        <v>6764158</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3423,7 +3415,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3433,7 +3425,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3460,32 +3452,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129294219</v>
+        <v>129293376</v>
       </c>
       <c r="B27" t="n">
-        <v>91886</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3495,10 +3487,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491922</v>
+        <v>492123</v>
       </c>
       <c r="R27" t="n">
-        <v>6764336</v>
+        <v>6764202</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3541,11 +3533,6 @@
       <c r="AB27" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>39. 2 bild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3572,14 +3559,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129294905</v>
+        <v>129293473</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3607,10 +3594,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492048</v>
+        <v>492120</v>
       </c>
       <c r="R28" t="n">
-        <v>6764380</v>
+        <v>6764224</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3653,11 +3640,6 @@
       <c r="AB28" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3684,14 +3666,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129294335</v>
+        <v>129293510</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3719,10 +3701,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491922</v>
+        <v>492107</v>
       </c>
       <c r="R29" t="n">
-        <v>6764336</v>
+        <v>6764244</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3791,14 +3773,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129290087</v>
+        <v>129293571</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3826,10 +3808,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492083</v>
+        <v>492107</v>
       </c>
       <c r="R30" t="n">
-        <v>6764418</v>
+        <v>6764235</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3861,7 +3843,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3871,7 +3853,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3898,14 +3880,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129295250</v>
+        <v>129293719</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3933,13 +3915,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492125</v>
+        <v>492059</v>
       </c>
       <c r="R31" t="n">
-        <v>6764458</v>
+        <v>6764244</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3979,11 +3961,6 @@
       <c r="AB31" t="inlineStr">
         <is>
           <t>13:01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>54. 4 bilder på äldre tallar  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4010,53 +3987,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129294510</v>
+        <v>129293814</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491975</v>
+        <v>492030</v>
       </c>
       <c r="R32" t="n">
-        <v>6764342</v>
+        <v>6764244</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4100,7 +4072,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>45. 3 bilder, miljöbilder</t>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4127,14 +4099,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129289310</v>
+        <v>129293927</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4162,10 +4134,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492177</v>
+        <v>491997</v>
       </c>
       <c r="R33" t="n">
-        <v>6764418</v>
+        <v>6764269</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4197,7 +4169,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4207,12 +4179,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>14. 3 bilder  Rikligt i en radie av 50 meter</t>
+          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4239,14 +4211,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129295876</v>
+        <v>129294004</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4274,13 +4246,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492080</v>
+        <v>491966</v>
       </c>
       <c r="R34" t="n">
-        <v>6764357</v>
+        <v>6764290</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4324,7 +4296,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>55. 1 bild hängande på gren</t>
+          <t>37. 4 bilder, en närbild Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4354,11 +4326,11 @@
         <v>129294091</v>
       </c>
       <c r="B35" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4458,32 +4430,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129289434</v>
+        <v>129294335</v>
       </c>
       <c r="B36" t="n">
-        <v>91588</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4493,10 +4465,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492159</v>
+        <v>491922</v>
       </c>
       <c r="R36" t="n">
-        <v>6764383</v>
+        <v>6764336</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4528,7 +4500,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4538,12 +4510,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>16. 2 bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,14 +4537,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129293510</v>
+        <v>129294362</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4605,13 +4572,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>492107</v>
+        <v>491956</v>
       </c>
       <c r="R37" t="n">
-        <v>6764244</v>
+        <v>6764334</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4651,6 +4618,11 @@
       <c r="AB37" t="inlineStr">
         <is>
           <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4677,32 +4649,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129294065</v>
+        <v>129294699</v>
       </c>
       <c r="B38" t="n">
-        <v>91588</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4712,13 +4684,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>491997</v>
+        <v>491988</v>
       </c>
       <c r="R38" t="n">
-        <v>6764302</v>
+        <v>6764346</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4762,7 +4734,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>38. 1 bild, granlåga</t>
+          <t>46. Flera bilder Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4789,32 +4761,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129294432</v>
+        <v>129294905</v>
       </c>
       <c r="B39" t="n">
-        <v>91588</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4824,13 +4796,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>491957</v>
+        <v>492048</v>
       </c>
       <c r="R39" t="n">
-        <v>6764346</v>
+        <v>6764380</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4874,7 +4846,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>44. 2 bilder, granlåga</t>
+          <t>50. 1 bild på granar med garnlav Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4901,53 +4873,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129293401</v>
+        <v>129295250</v>
       </c>
       <c r="B40" t="n">
-        <v>57733</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>492123</v>
+        <v>492125</v>
       </c>
       <c r="R40" t="n">
-        <v>6764202</v>
+        <v>6764458</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4991,7 +4958,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>32. 1 bild på låga med hack</t>
+          <t>54. 4 bilder på äldre tallar  Rikligt i en radie av 50 meter</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5018,50 +4985,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129295996</v>
+        <v>129295876</v>
       </c>
       <c r="B41" t="n">
-        <v>57733</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>492085</v>
+        <v>492080</v>
       </c>
       <c r="R41" t="n">
-        <v>6764296</v>
+        <v>6764357</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5108,7 +5070,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>56. 2 bilder, även svamp på gran</t>
+          <t>55. 1 bild hängande på gren</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5135,53 +5097,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129289411</v>
+        <v>129296076</v>
       </c>
       <c r="B42" t="n">
-        <v>57733</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>492157</v>
+        <v>492085</v>
       </c>
       <c r="R42" t="n">
-        <v>6764400</v>
+        <v>6764296</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5210,7 +5167,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5220,12 +5177,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>15. 1 bild</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5252,14 +5204,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129290779</v>
+        <v>129296258</v>
       </c>
       <c r="B43" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5287,13 +5239,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>492030</v>
+        <v>492091</v>
       </c>
       <c r="R43" t="n">
-        <v>6764279</v>
+        <v>6764217</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5322,7 +5274,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5332,12 +5284,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>23. 2 bilder, tallstammar Rikligt i en radie av 50 meter</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5364,10 +5311,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129293719</v>
+        <v>129283290</v>
       </c>
       <c r="B44" t="n">
-        <v>79076</v>
+        <v>79946</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5375,21 +5322,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5399,10 +5346,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>492059</v>
+        <v>492076</v>
       </c>
       <c r="R44" t="n">
-        <v>6764244</v>
+        <v>6764218</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5434,7 +5381,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5444,7 +5391,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>4. 1 bild, stubbe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5471,32 +5423,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129293744</v>
+        <v>129290171</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>79946</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5506,10 +5458,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>492059</v>
+        <v>492061</v>
       </c>
       <c r="R45" t="n">
-        <v>6764244</v>
+        <v>6764382</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5541,7 +5493,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5551,7 +5503,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5578,10 +5530,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129289685</v>
+        <v>129270937</v>
       </c>
       <c r="B46" t="n">
-        <v>97640</v>
+        <v>57950</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5589,34 +5541,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>492160</v>
+        <v>492105</v>
       </c>
       <c r="R46" t="n">
-        <v>6764361</v>
+        <v>6764156</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5643,27 +5600,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>17. 3 miljöbilder,</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5690,27 +5642,27 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129274000</v>
+        <v>129282976</v>
       </c>
       <c r="B47" t="n">
-        <v>57736</v>
+        <v>57950</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -5719,24 +5671,21 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>492089</v>
+        <v>492100</v>
       </c>
       <c r="R47" t="n">
-        <v>6764397</v>
+        <v>6764182</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5763,27 +5712,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1 bild samt miljöbilder för området</t>
+          <t>2. 1 bild</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5810,45 +5759,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129293571</v>
+        <v>129283043</v>
       </c>
       <c r="B48" t="n">
-        <v>79076</v>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>492107</v>
+        <v>492082</v>
       </c>
       <c r="R48" t="n">
-        <v>6764235</v>
+        <v>6764210</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5880,7 +5834,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5890,7 +5844,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>3. 1 bild</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5917,27 +5876,27 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129274938</v>
+        <v>129289411</v>
       </c>
       <c r="B49" t="n">
-        <v>57736</v>
+        <v>57950</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5948,7 +5907,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5957,13 +5916,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>492048</v>
+        <v>492157</v>
       </c>
       <c r="R49" t="n">
-        <v>6764380</v>
+        <v>6764400</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5987,27 +5946,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>I bild</t>
+          <t>15. 1 bild</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6034,48 +5993,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129294362</v>
+        <v>129290345</v>
       </c>
       <c r="B50" t="n">
-        <v>79076</v>
+        <v>57950</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>491956</v>
+        <v>492050</v>
       </c>
       <c r="R50" t="n">
-        <v>6764334</v>
+        <v>6764358</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6104,7 +6068,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6114,12 +6078,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>42. 2 bilder  Rikligt i en radie av 50 meter</t>
+          <t>20. 1 bild</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6146,45 +6110,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129290171</v>
+        <v>129293401</v>
       </c>
       <c r="B51" t="n">
-        <v>79695</v>
+        <v>57950</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492061</v>
+        <v>492123</v>
       </c>
       <c r="R51" t="n">
-        <v>6764382</v>
+        <v>6764202</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6216,7 +6185,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6226,7 +6195,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>32. 1 bild på låga med hack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6253,48 +6227,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129296258</v>
+        <v>129294398</v>
       </c>
       <c r="B52" t="n">
-        <v>79076</v>
+        <v>57950</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492091</v>
+        <v>491957</v>
       </c>
       <c r="R52" t="n">
-        <v>6764217</v>
+        <v>6764346</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6360,14 +6339,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129282981</v>
+        <v>129294510</v>
       </c>
       <c r="B53" t="n">
-        <v>57733</v>
+        <v>57950</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6391,7 +6370,7 @@
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6400,10 +6379,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492100</v>
+        <v>491975</v>
       </c>
       <c r="R53" t="n">
-        <v>6764182</v>
+        <v>6764342</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6435,7 +6414,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6445,7 +6424,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>45. 3 bilder, miljöbilder</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6472,48 +6456,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129293814</v>
+        <v>129295996</v>
       </c>
       <c r="B54" t="n">
-        <v>79076</v>
+        <v>57950</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492030</v>
+        <v>492085</v>
       </c>
       <c r="R54" t="n">
-        <v>6764244</v>
+        <v>6764296</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6557,7 +6546,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>36. 3 bilder på tall Rikligt i en radie av 50 meter</t>
+          <t>56. 2 bilder, även svamp på gran</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6584,10 +6573,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129286796</v>
+        <v>129271179</v>
       </c>
       <c r="B55" t="n">
-        <v>79081</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6595,37 +6584,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492169</v>
+        <v>492113</v>
       </c>
       <c r="R55" t="n">
-        <v>6764315</v>
+        <v>6764152</v>
       </c>
       <c r="S55" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6649,27 +6643,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt i en radie av 50 meter 9. 2 bilder</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6696,10 +6690,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129282927</v>
+        <v>129274000</v>
       </c>
       <c r="B56" t="n">
-        <v>79081</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6707,37 +6701,45 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492097</v>
+        <v>492089</v>
       </c>
       <c r="R56" t="n">
-        <v>6764193</v>
+        <v>6764397</v>
       </c>
       <c r="S56" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6761,27 +6763,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 1. 4 bilder</t>
+          <t>1 bild samt miljöbilder för området</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6808,10 +6810,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129290011</v>
+        <v>129274016</v>
       </c>
       <c r="B57" t="n">
-        <v>57736</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6839,7 +6841,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6848,10 +6850,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492099</v>
+        <v>492092</v>
       </c>
       <c r="R57" t="n">
-        <v>6764428</v>
+        <v>6764410</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6878,27 +6880,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>18. 1 bild</t>
+          <t>1 bild</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6925,10 +6927,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129283290</v>
+        <v>129274034</v>
       </c>
       <c r="B58" t="n">
-        <v>79700</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6936,34 +6938,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492076</v>
+        <v>492106</v>
       </c>
       <c r="R58" t="n">
-        <v>6764218</v>
+        <v>6764404</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6990,27 +6997,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>4. 1 bild, stubbe</t>
+          <t>2 bilder, kåda</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7037,10 +7044,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129287728</v>
+        <v>129274938</v>
       </c>
       <c r="B59" t="n">
-        <v>79081</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7048,34 +7055,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>492227</v>
+        <v>492048</v>
       </c>
       <c r="R59" t="n">
-        <v>6764369</v>
+        <v>6764380</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7102,27 +7114,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>12. 1 Bild på kolarkoja</t>
+          <t>I bild</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7149,10 +7161,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129283635</v>
+        <v>129287751</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7160,37 +7172,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492082</v>
+        <v>492227</v>
       </c>
       <c r="R60" t="n">
-        <v>6764245</v>
+        <v>6764369</v>
       </c>
       <c r="S60" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7219,7 +7236,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7229,12 +7246,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Rikligt i en radie av 50 meter 6. 3 bilder</t>
+          <t>12. 1 bild</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7261,10 +7278,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129283043</v>
+        <v>129290011</v>
       </c>
       <c r="B61" t="n">
-        <v>57733</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7272,16 +7289,16 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7292,7 +7309,7 @@
       <c r="I61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7301,10 +7318,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492082</v>
+        <v>492099</v>
       </c>
       <c r="R61" t="n">
-        <v>6764210</v>
+        <v>6764428</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7336,7 +7353,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7346,12 +7363,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>3. 1 bild</t>
+          <t>18. 1 bild</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7378,27 +7395,27 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129287751</v>
+        <v>129290672</v>
       </c>
       <c r="B62" t="n">
-        <v>57736</v>
+        <v>58327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -7409,7 +7426,7 @@
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7418,13 +7435,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492227</v>
+        <v>492030</v>
       </c>
       <c r="R62" t="n">
-        <v>6764369</v>
+        <v>6764294</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7464,11 +7481,6 @@
       <c r="AB62" t="inlineStr">
         <is>
           <t>09:32</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>12. 1 bild</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7495,51 +7507,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129764564</v>
+        <v>129294029</v>
       </c>
       <c r="B63" t="n">
-        <v>92092</v>
+        <v>58114</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Siljansleden, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492111</v>
+        <v>492007</v>
       </c>
       <c r="R63" t="n">
-        <v>6764260</v>
+        <v>6764289</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7566,18 +7580,27 @@
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-23</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7593,6 +7616,439 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>129293744</v>
+      </c>
+      <c r="B64" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>492059</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6764244</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>129294088</v>
+      </c>
+      <c r="B65" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>491988</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6764293</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>129289685</v>
+      </c>
+      <c r="B66" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>492160</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6764361</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>17. 3 miljöbilder,</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>129285680</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Siljansleden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>492188</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6764292</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50759-2023 artfynd.xlsx
+++ b/artfynd/A 50759-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294219</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129283566</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129289434</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1124,6 +1144,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293569</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1236,6 +1261,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294065</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1348,6 +1378,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294432</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129764564</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129286698</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1672,6 +1717,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129271130</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1784,6 +1834,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129271386</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1891,6 +1946,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129271992</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2003,6 +2063,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129273280</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129282927</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2227,6 +2297,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129283635</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2339,6 +2414,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129285073</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2451,6 +2531,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129286796</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2563,6 +2648,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129287686</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2675,6 +2765,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129287728</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2787,6 +2882,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129287945</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2899,6 +2999,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129289310</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3006,6 +3111,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290087</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3118,6 +3228,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290261</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3230,6 +3345,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290547</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3342,6 +3462,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290779</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3449,6 +3574,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293152</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3556,6 +3686,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293376</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3663,6 +3798,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293473</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3770,6 +3910,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293510</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3877,6 +4022,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293571</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3984,6 +4134,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293719</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4096,6 +4251,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293814</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4208,6 +4368,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293927</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4320,6 +4485,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294004</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4427,6 +4597,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294091</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4534,6 +4709,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294335</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4646,6 +4826,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294362</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4758,6 +4943,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294699</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4870,6 +5060,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294905</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4982,6 +5177,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295250</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5094,6 +5294,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295876</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5201,6 +5406,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296076</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5308,6 +5518,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129296258</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5420,6 +5635,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129283290</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5527,6 +5747,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290171</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5639,6 +5864,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129270937</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5756,6 +5986,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129282976</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5873,6 +6108,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129283043</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5990,6 +6230,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129289411</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6107,6 +6352,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290345</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6224,6 +6474,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293401</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6336,6 +6591,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294398</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6453,6 +6713,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294510</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6570,6 +6835,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129295996</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6687,6 +6957,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129271179</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6807,6 +7082,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129274000</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6924,6 +7204,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129274016</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7041,6 +7326,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129274034</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7158,6 +7448,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129274938</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7275,6 +7570,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129287751</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7392,6 +7692,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290011</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7504,6 +7809,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129290672</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7616,6 +7926,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294029</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7723,6 +8038,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129293744</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7830,6 +8150,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129294088</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7942,6 +8267,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129289685</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8049,8 +8379,81 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129285680</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>